--- a/wiki/05-backlog/MANI_MODULOS_SERVICIOS_Y_BACKLOG_S5.xlsx
+++ b/wiki/05-backlog/MANI_MODULOS_SERVICIOS_Y_BACKLOG_S5.xlsx
@@ -38,6 +38,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18 Criterios transversales S4" sheetId="29" state="visible" r:id="rId29"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19 Criterios por historia S4" sheetId="30" state="visible" r:id="rId30"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20 Criterios US-02.1.1" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21 Cierre de cobertura" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22 Gestion del sprint" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23 Subtareas de QA" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -91,7 +94,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -131,6 +134,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9D2E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4DFEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
   </fills>
@@ -218,7 +231,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -287,6 +300,18 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1366,7 +1391,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>RF-15 / RF-17</t>
+          <t>RF-34 / RF-15 / RF-17</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1419,7 +1444,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>RNF-03</t>
+          <t>RF-35 / RNF-03</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1676,7 +1701,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CONS-30</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -1776,7 +1801,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>RF-02 / RNF-10</t>
+          <t>RF-33 / RF-02 / RNF-10</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1828,7 +1853,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>RF-18</t>
+          <t>RF-36 / RF-18</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1880,7 +1905,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>RF-18</t>
+          <t>RF-36 / RF-18</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -2033,7 +2058,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CONS-35 · TEC-01</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -2691,7 +2716,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>RF-24</t>
+          <t>RF-24 / REST-03</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -2743,7 +2768,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>RF-24</t>
+          <t>RF-24 / RNF-06 / RNF-11 / REST-03</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -3004,7 +3029,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>RF-25</t>
+          <t>RF-25 / RNF-10 / REST-05</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -12003,7 +12028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -12019,6 +12044,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="88" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -12033,6 +12059,7 @@
       <c r="C3" s="19" t="n"/>
       <c r="D3" s="20" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
@@ -12096,6 +12123,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
@@ -12137,10 +12165,10 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>87</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
@@ -12155,10 +12183,10 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
@@ -12173,98 +12201,117 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="21" t="inlineStr">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>Gestion (SM, PO)</t>
+        </is>
+      </c>
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t>Facilitacion del sprint y validacion final del producto</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="26" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr"/>
-      <c r="C20" s="21" t="n">
-        <v>83</v>
-      </c>
-      <c r="D20" s="21" t="n">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr"/>
+      <c r="C21" s="21" t="n">
+        <v>91</v>
+      </c>
+      <c r="D21" s="21" t="n">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Orden sugerido de ejecucion</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="34" customHeight="1">
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>1. Desbloquear el ambiente: TEC-09, TEC-10, TEC-11 y TEC-16. Sin token real ES256 ni QA sembrada, ningun video vale.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="21" customHeight="1">
       <c r="B24" s="18" t="inlineStr">
         <is>
-          <t>2. Decisiones de Mesa que bloquean codigo: TEC-01, TEC-12, y las salidas de P-5 y P-6.</t>
+          <t>1. Desbloquear el ambiente: TEC-09, TEC-10, TEC-11 y TEC-16. Sin token real ES256 ni QA sembrada, ningun video vale.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="21" customHeight="1">
       <c r="B25" s="18" t="inlineStr">
         <is>
-          <t>3. Arreglar los defectos de despacho antes de grabar: TEC-02, TEC-03, TEC-04, TEC-05, TEC-06.</t>
+          <t>2. Decisiones de Mesa que bloquean codigo: TEC-01, TEC-12, y las salidas de P-5 y P-6.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="21" customHeight="1">
       <c r="B26" s="18" t="inlineStr">
         <is>
-          <t>4. Migrar el front al Gateway: CONS-03 y TEC-18, que habilitan VAL-10 a VAL-14.</t>
+          <t>3. Arreglar los defectos de despacho antes de grabar: TEC-02, TEC-03, TEC-04, TEC-05, TEC-06.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="21" customHeight="1">
       <c r="B27" s="18" t="inlineStr">
         <is>
-          <t>5. Grabar la tanda de validacion VAL-01 a VAL-18, abriendo bug con minuto exacto por cada fallo.</t>
+          <t>4. Migrar el front al Gateway: CONS-03 y TEC-18, que habilitan VAL-10 a VAL-14.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="21" customHeight="1">
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>6. Construir el shell y la sesion: CONS-01, CONS-02, CONS-07 a CONS-09, luego VAL-17.</t>
+          <t>5. Grabar la tanda de validacion VAL-01 a VAL-18, abriendo bug con minuto exacto por cada fallo.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="21" customHeight="1">
       <c r="B29" s="18" t="inlineStr">
         <is>
-          <t>7. Mocks que habilitan front: CONS-35 (notificaciones) y CONS-38 (pasarela).</t>
+          <t>6. Construir el shell y la sesion: CONS-01, CONS-02, CONS-07 a CONS-09, luego VAL-17.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="21" customHeight="1">
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>8. Rules Service: TEC-15 y CONS-18, que desbloquean tarifario, alertas y ranking.</t>
+          <t>7. Mocks que habilitan front: CONS-35 (notificaciones) y CONS-38 (pasarela).</t>
         </is>
       </c>
     </row>
     <row r="31" ht="21" customHeight="1">
       <c r="B31" s="18" t="inlineStr">
         <is>
-          <t>9. Resto del ciclo del servicio: cotizacion, ejecucion, calificacion y comunicacion.</t>
+          <t>8. Rules Service: TEC-15 y CONS-18, que desbloquean tarifario, alertas y ranking.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="21" customHeight="1">
       <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>9. Resto del ciclo del servicio: cotizacion, ejecucion, calificacion y comunicacion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="18" t="inlineStr">
         <is>
           <t>10. Modularizacion CONS-10 y CONS-11 al final, cuando las pruebas ya cubren el comportamiento.</t>
         </is>
@@ -12303,7 +12350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13219,6 +13266,206 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="28" t="inlineStr">
+        <is>
+          <t>VAL-19</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="inlineStr">
+        <is>
+          <t>M-03</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>Validar el contrato del perfil del aliado que consumen Dispatch y Rules</t>
+        </is>
+      </c>
+      <c r="D25" s="26" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+      <c r="E25" s="26" t="inlineStr">
+        <is>
+          <t>Existe en codigo pero nunca se valido como contrato. Pedir el perfil del aliado por el Gateway con token real ES256 y comprobar: responde los campos que Dispatch y Rules declaran consumir, no expone documentos KYC ni datos de otro aliado, y con el token de un aliado del tenant B sobre un aliado del tenant A responde 403 o 404 y nunca 200 con datos. Video desde el front o, si no tiene pantalla, corrida Newman adjunta.</t>
+        </is>
+      </c>
+      <c r="F25" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" s="26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H25" s="26" t="inlineStr">
+        <is>
+          <t>TEC-10 (token real ES256)</t>
+        </is>
+      </c>
+      <c r="I25" s="26" t="inlineStr">
+        <is>
+          <t>CORE, DISPATCH, RULES</t>
+        </is>
+      </c>
+      <c r="J25" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="28" t="inlineStr">
+        <is>
+          <t>VAL-20</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="inlineStr">
+        <is>
+          <t>M-04</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>Validar que el catalogo responde solo las categorias y zonas del tenant del claim</t>
+        </is>
+      </c>
+      <c r="D26" s="26" t="inlineStr">
+        <is>
+          <t>Cliente / Aliado</t>
+        </is>
+      </c>
+      <c r="E26" s="26" t="inlineStr">
+        <is>
+          <t>Implementado y sin validar. Consultar el catalogo por el Gateway con usuarios de dos tenants y comprobar que cada uno ve solo sus categorias activas, que una categoria desactivada no aparece, y que el tenant no se puede forzar por cuerpo ni por cabecera (se toma del claim, T4). El catalogo es pre-auth en nginx: comprobar tambien que sin token no filtra datos de ningun tenant.</t>
+        </is>
+      </c>
+      <c r="F26" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" s="26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H26" s="26" t="inlineStr">
+        <is>
+          <t>TEC-10, TEC-16</t>
+        </is>
+      </c>
+      <c r="I26" s="26" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="J26" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="28" t="inlineStr">
+        <is>
+          <t>VAL-21</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="inlineStr">
+        <is>
+          <t>M-05</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>Validar el contexto de solicitud que Dispatch pide a Core</t>
+        </is>
+      </c>
+      <c r="D27" s="26" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+      <c r="E27" s="26" t="inlineStr">
+        <is>
+          <t>Implementado y sin validar. Comprobar que Dispatch obtiene zona, categoria y estado de la solicitud por HTTP a Core y no por SQL sobre tablas de Core (T1), que si Core no responde Dispatch devuelve 503 y no arma el contexto con logica local (T2), y que el contexto de una solicitud del tenant A nunca se entrega con el token del tenant B.</t>
+        </is>
+      </c>
+      <c r="F27" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" s="26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H27" s="26" t="inlineStr">
+        <is>
+          <t>TEC-02, TEC-10</t>
+        </is>
+      </c>
+      <c r="I27" s="26" t="inlineStr">
+        <is>
+          <t>CORE, DISPATCH</t>
+        </is>
+      </c>
+      <c r="J27" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="28" t="inlineStr">
+        <is>
+          <t>VAL-22</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="inlineStr">
+        <is>
+          <t>M-05</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="inlineStr">
+        <is>
+          <t>Validar idempotencia de la creacion de solicitud y del despacho bajo reintento</t>
+        </is>
+      </c>
+      <c r="D28" s="26" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+      <c r="E28" s="26" t="inlineStr">
+        <is>
+          <t>RNF-03 exige que las operaciones criticas resistan reintentos sin duplicar. Comprobar: reintento con la misma claveIdempotencia no crea una segunda solicitud; reintento de la orquestacion no duplica el broadcast; y tras un corte parcial del broadcast el reintento completa las ofertas que faltan en vez de congelarse, que es el defecto D-4. Requiere TEC-04 desplegado.</t>
+        </is>
+      </c>
+      <c r="F28" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="G28" s="26" t="inlineStr">
+        <is>
+          <t>Highest</t>
+        </is>
+      </c>
+      <c r="H28" s="26" t="inlineStr">
+        <is>
+          <t>TEC-04 (paginar y rehacer la guarda de idempotencia)</t>
+        </is>
+      </c>
+      <c r="I28" s="26" t="inlineStr">
+        <is>
+          <t>CORE, DISPATCH</t>
+        </is>
+      </c>
+      <c r="J28" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
@@ -13234,7 +13481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -15392,6 +15639,56 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="28" t="inlineStr">
+        <is>
+          <t>CONS-46</t>
+        </is>
+      </c>
+      <c r="B52" s="26" t="inlineStr">
+        <is>
+          <t>M-01</t>
+        </is>
+      </c>
+      <c r="C52" s="26" t="inlineStr">
+        <is>
+          <t>Alta y administracion de tenants por el administrador de plataforma</t>
+        </is>
+      </c>
+      <c r="D52" s="26" t="inlineStr">
+        <is>
+          <t>Admin de plataforma</t>
+        </is>
+      </c>
+      <c r="E52" s="26" t="inlineStr">
+        <is>
+          <t>RF-01 es critico y hoy solo existe GET /api/v1/core/tenants: no hay forma de crear un tenant por la aplicacion. End to end desde cero: pantalla de administracion de plataforma, alta del tenant con su slug y sus datos, edicion, y consulta del listado. El alta crea el tenant aislado: sus tablas nacen con tenant_id y su politica por tenant en la misma migracion (T3). Solo el administrador de plataforma puede crear tenants; un admin de tenant que lo intente recibe 403. Queda registrado quien lo creo, cuando y con que correlationId (T10). No incluye el estado del tenant, que es CONS-43.</t>
+        </is>
+      </c>
+      <c r="F52" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="G52" s="26" t="inlineStr">
+        <is>
+          <t>Highest</t>
+        </is>
+      </c>
+      <c r="H52" s="26" t="inlineStr">
+        <is>
+          <t>CONS-07 (shell), TEC-10</t>
+        </is>
+      </c>
+      <c r="I52" s="26" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="J52" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
@@ -15407,7 +15704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16386,6 +16683,51 @@
       <c r="B26" s="12" t="inlineStr">
         <is>
           <t>Total: 20 tareas · 85 story points</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="28" t="inlineStr">
+        <is>
+          <t>TEC-21</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="inlineStr">
+        <is>
+          <t>Retirar BYPASSRLS: Core y Dispatch conectan con un rol de servicio sin privilegio de salto</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>Seguridad / Migracion</t>
+        </is>
+      </c>
+      <c r="D27" s="26" t="inlineStr">
+        <is>
+          <t>BUG-SEC-02, R-09, R-06</t>
+        </is>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" s="26" t="inlineStr">
+        <is>
+          <t>Highest</t>
+        </is>
+      </c>
+      <c r="G27" s="26" t="inlineStr">
+        <is>
+          <t>Core y DevOps</t>
+        </is>
+      </c>
+      <c r="H27" s="26" t="inlineStr">
+        <is>
+          <t>TEC-13 (identidad de servicio)</t>
+        </is>
+      </c>
+      <c r="I27" s="26" t="inlineStr">
+        <is>
+          <t>Hoy Core usa service_role o postgres y Dispatch usa postgres, los tres con BYPASSRLS, asi que ninguna politica RLS se evalua y el aislamiento de RNF-01 descansa solo en el codigo. Cerrar: cada servicio conecta con un rol propio sin BYPASSRLS; las 15 politicas tenant_isolation_* dejan de estar TO public (R-06); y una prueba demuestra que, con el filtro de aplicacion desactivado a proposito, la politica sigue bloqueando el acceso cruzado. Sin esto, VAL-16 no demuestra aislamiento real sino aislamiento por codigo.</t>
         </is>
       </c>
     </row>
@@ -23530,6 +23872,3533 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="92" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>Cierre de cobertura: cada funcionalidad con su historia</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="86" customHeight="1">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>Revision del 24-oct-2026. Las 88 funcionalidades de las hojas M-01 a M-13 tienen ahora una historia asignada: 18 no la tenian. Doce ya estaban cubiertas por un item del Sprint 5 pero sin trazar en la columna Historia; seis necesitaron historia nueva (VAL-19 a VAL-22, CONS-46 y TEC-21). Regla aplicada: lo que no existe se construye end to end desde cero; lo que figura como implementado se valida contra lo pedido, porque un estado Done sin video por el Gateway con token real no acredita nada (SAD §7.5). Ademas se corrigieron 16 etiquetas de requisito: RF-29 a RF-36, RNF-06, RNF-07, RNF-11, REST-03 y REST-05 no aparecian en ninguna fila aunque su funcionalidad si existia. Ahora los 36 RF, los 11 RNF y las 5 REST del SRS estan trazados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>Funcionalidad</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>Modulo</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>RF / RNF</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t>Estado hoy</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="inlineStr">
+        <is>
+          <t>HU que la cubre</t>
+        </is>
+      </c>
+      <c r="G4" s="25" t="inlineStr">
+        <is>
+          <t>Tipo de HU</t>
+        </is>
+      </c>
+      <c r="H4" s="25" t="inlineStr">
+        <is>
+          <t>Que exige esa HU</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>M-01.1</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>Registrar y administrar empresas (tenants)</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>M-01</t>
+        </is>
+      </c>
+      <c r="D5" s="26" t="inlineStr">
+        <is>
+          <t>RF-01</t>
+        </is>
+      </c>
+      <c r="E5" s="26" t="inlineStr">
+        <is>
+          <t>Parcial: solo existe GET /core/tenants</t>
+        </is>
+      </c>
+      <c r="F5" s="29" t="inlineStr">
+        <is>
+          <t>CONS-46</t>
+        </is>
+      </c>
+      <c r="G5" s="26" t="inlineStr">
+        <is>
+          <t>Nueva · construccion desde 0</t>
+        </is>
+      </c>
+      <c r="H5" s="26" t="inlineStr">
+        <is>
+          <t>RF-01 es critico y no hay forma de crear un tenant por la aplicacion. Pantalla de administracion de plataforma con alta, edicion y listado; el alta crea el tenant aislado con tenant_id y politica en la misma migracion (T3); solo el admin de plataforma puede crear y queda registrado quien, cuando y el correlationId (T10).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>M-01.2</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>Aislamiento estricto de datos y archivos por tenant</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
+        <is>
+          <t>M-01</t>
+        </is>
+      </c>
+      <c r="D6" s="26" t="inlineStr">
+        <is>
+          <t>RNF-01 / REST-04</t>
+        </is>
+      </c>
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t>Parcial con defecto abierto</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>VAL-16 · TEC-21</t>
+        </is>
+      </c>
+      <c r="G6" s="26" t="inlineStr">
+        <is>
+          <t>Existente + tarea nueva</t>
+        </is>
+      </c>
+      <c r="H6" s="26" t="inlineStr">
+        <is>
+          <t>VAL-16 ya valida el aislamiento, pero hoy Core y Dispatch conectan con BYPASSRLS y ninguna politica RLS se evalua: el aislamiento descansa solo en el codigo. TEC-21 retira BYPASSRLS y quita el TO public de las 15 politicas, para que VAL-16 demuestre aislamiento real y no aislamiento por codigo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>M-01.3</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>Configurar reglas operativas propias por tenant</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="inlineStr">
+        <is>
+          <t>M-01</t>
+        </is>
+      </c>
+      <c r="D7" s="26" t="inlineStr">
+        <is>
+          <t>RF-02 / RNF-02 / RNF-10 / REST-05</t>
+        </is>
+      </c>
+      <c r="E7" s="26" t="inlineStr">
+        <is>
+          <t>Pendiente: Rules no existe</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t>CONS-44 · TEC-15</t>
+        </is>
+      </c>
+      <c r="G7" s="26" t="inlineStr">
+        <is>
+          <t>Existentes, sin trazar</t>
+        </is>
+      </c>
+      <c r="H7" s="26" t="inlineStr">
+        <is>
+          <t>RF-02 es critico y RNF-02 exige configurar sin nuevo despliegue. TEC-15 crea el repositorio del Rules Service y CONS-44 construye la configuracion por tenant. Hasta entonces ninguna regla es configurable y RNF-02 no se cumple.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>M-01.4</t>
+        </is>
+      </c>
+      <c r="B8" s="26" t="inlineStr">
+        <is>
+          <t>Identificacion de tenant no falsificable</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>M-01</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="inlineStr">
+        <is>
+          <t>RNF-01 / ADR-0018</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t>Implementado con defecto abierto</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="inlineStr">
+        <is>
+          <t>VAL-16 · TEC-09</t>
+        </is>
+      </c>
+      <c r="G8" s="26" t="inlineStr">
+        <is>
+          <t>Existentes, sin trazar</t>
+        </is>
+      </c>
+      <c r="H8" s="26" t="inlineStr">
+        <is>
+          <t>El perimetro resuelve el tenant por auth_request y Core lo revalida, pero dev-token firmaba tenant_id y rol arbitrarios. TEC-09 cierra dev-token y VAL-16 comprueba que el tenant no se puede forzar por cuerpo ni por cabecera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>M-01.5</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>Propiedad del esquema y de las migraciones en un solo servicio</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>M-01</t>
+        </is>
+      </c>
+      <c r="D9" s="26" t="inlineStr">
+        <is>
+          <t>ADR-0030 §1</t>
+        </is>
+      </c>
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>Conforme</t>
+        </is>
+      </c>
+      <c r="F9" s="28" t="inlineStr">
+        <is>
+          <t>TEC-08</t>
+        </is>
+      </c>
+      <c r="G9" s="26" t="inlineStr">
+        <is>
+          <t>Existente, sin trazar</t>
+        </is>
+      </c>
+      <c r="H9" s="26" t="inlineStr">
+        <is>
+          <t>La conformidad esta comprobada: MANI-.NET no versiona DDL. Lo unico abierto es D-10, que la numeracion de migraciones salta de 0010 a 0013 sin registro del motivo, y eso lo cierra TEC-08.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>M-02.1</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>Inicio de sesion</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>M-02</t>
+        </is>
+      </c>
+      <c r="D10" s="26" t="inlineStr">
+        <is>
+          <t>RF-03</t>
+        </is>
+      </c>
+      <c r="E10" s="26" t="inlineStr">
+        <is>
+          <t>Done sin validar en arquitectura vigente</t>
+        </is>
+      </c>
+      <c r="F10" s="28" t="inlineStr">
+        <is>
+          <t>VAL-01 · TEC-10</t>
+        </is>
+      </c>
+      <c r="G10" s="26" t="inlineStr">
+        <is>
+          <t>Existentes, sin trazar</t>
+        </is>
+      </c>
+      <c r="H10" s="26" t="inlineStr">
+        <is>
+          <t>Figura Done pero nunca se ejecuto por el Gateway con un token real: el perimetro aceptaba solo HS256 y MANI-QA emite ES256. TEC-10 ya dejo un solo validador con ES256 y VAL-01 graba el login real de extremo a extremo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>M-02.10</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>Recuperacion segura de contrasena</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>M-02</t>
+        </is>
+      </c>
+      <c r="D11" s="26" t="inlineStr">
+        <is>
+          <t>RF-04</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F11" s="28" t="inlineStr">
+        <is>
+          <t>CONS-04</t>
+        </is>
+      </c>
+      <c r="G11" s="26" t="inlineStr">
+        <is>
+          <t>Existente, sin trazar</t>
+        </is>
+      </c>
+      <c r="H11" s="26" t="inlineStr">
+        <is>
+          <t>RF-04 es de prioridad alta y no hay nada construido. CONS-04 lo construye desde cero contra Supabase Auth orquestado por Core, con el enlace de un solo uso y sin exponer si el correo existe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>M-02.13</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>Validacion perimetral del token y propagacion de claims</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>M-02</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="inlineStr">
+        <is>
+          <t>RF-03</t>
+        </is>
+      </c>
+      <c r="E12" s="26" t="inlineStr">
+        <is>
+          <t>Implementado con defecto abierto</t>
+        </is>
+      </c>
+      <c r="F12" s="28" t="inlineStr">
+        <is>
+          <t>VAL-18 · TEC-10</t>
+        </is>
+      </c>
+      <c r="G12" s="26" t="inlineStr">
+        <is>
+          <t>Existentes, sin trazar</t>
+        </is>
+      </c>
+      <c r="H12" s="26" t="inlineStr">
+        <is>
+          <t>Habia dos validadores con politicas distintas y el perimetro era mas estricto que el interior. TEC-10 unifica en un solo validador; VAL-18 ejecuta la regresion de seguridad: token ausente, mal formado, alterado, vencido, con kid desconocido y con alg none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>M-02.14</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>Autorizacion por rol y tenant en cada peticion</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>M-02</t>
+        </is>
+      </c>
+      <c r="D13" s="26" t="inlineStr">
+        <is>
+          <t>RF-03</t>
+        </is>
+      </c>
+      <c r="E13" s="26" t="inlineStr">
+        <is>
+          <t>Implementado</t>
+        </is>
+      </c>
+      <c r="F13" s="28" t="inlineStr">
+        <is>
+          <t>VAL-18 · TEC-07</t>
+        </is>
+      </c>
+      <c r="G13" s="26" t="inlineStr">
+        <is>
+          <t>Existentes, sin trazar</t>
+        </is>
+      </c>
+      <c r="H13" s="26" t="inlineStr">
+        <is>
+          <t>Implementado en Core, pero JwtAuthHelper de Dispatch caia a claims planos mientras Core prohibe ese respaldo: dos politicas de token en el mismo sistema. TEC-07 las unifica y VAL-18 comprueba que un rol insuficiente recibe 403 en los tres servicios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>M-03.6</t>
+        </is>
+      </c>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>Perfil del aliado autenticado consumible por otros servicios</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>M-03</t>
+        </is>
+      </c>
+      <c r="D14" s="26" t="inlineStr">
+        <is>
+          <t>RF-30 / RF-05</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t>Implementado, nunca validado como contrato</t>
+        </is>
+      </c>
+      <c r="F14" s="29" t="inlineStr">
+        <is>
+          <t>VAL-19</t>
+        </is>
+      </c>
+      <c r="G14" s="26" t="inlineStr">
+        <is>
+          <t>Nueva · validacion</t>
+        </is>
+      </c>
+      <c r="H14" s="26" t="inlineStr">
+        <is>
+          <t>Existe en codigo y no figuraba ni en el cuerpo del PR que lo introdujo. VAL-19 lo valida como contrato: responde los campos que Dispatch y Rules declaran consumir, no expone documentos KYC, y con el token de otro tenant responde 403 o 404, nunca 200 con datos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>M-04.4</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>Catalogo jerarquico de zonas geograficas</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>M-04</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>REST-01 / RNF-09</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="F15" s="28" t="inlineStr">
+        <is>
+          <t>CONS-12</t>
+        </is>
+      </c>
+      <c r="G15" s="26" t="inlineStr">
+        <is>
+          <t>Existente, sin trazar</t>
+        </is>
+      </c>
+      <c r="H15" s="26" t="inlineStr">
+        <is>
+          <t>REST-01 y RNF-09 exigen cobertura por zonas de un catalogo jerarquico y nunca por radio. Falta el nivel de barrio, que es el mas fino del MVP, y eso lo construye CONS-12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>M-04.5</t>
+        </is>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>Consulta del catalogo por tenant</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>M-04</t>
+        </is>
+      </c>
+      <c r="D16" s="26" t="inlineStr">
+        <is>
+          <t>RF-10</t>
+        </is>
+      </c>
+      <c r="E16" s="26" t="inlineStr">
+        <is>
+          <t>Implementado, sin validar</t>
+        </is>
+      </c>
+      <c r="F16" s="29" t="inlineStr">
+        <is>
+          <t>VAL-20</t>
+        </is>
+      </c>
+      <c r="G16" s="26" t="inlineStr">
+        <is>
+          <t>Nueva · validacion</t>
+        </is>
+      </c>
+      <c r="H16" s="26" t="inlineStr">
+        <is>
+          <t>El catalogo es pre-auth en nginx, asi que hay que comprobar dos cosas distintas: que con token cada tenant ve solo sus categorias activas y no puede forzar el tenant, y que sin token no filtra datos de ningun tenant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>M-05.3</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>Contexto de la solicitud (zona, categoria, estado)</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>M-05</t>
+        </is>
+      </c>
+      <c r="D17" s="26" t="inlineStr">
+        <is>
+          <t>RF-12</t>
+        </is>
+      </c>
+      <c r="E17" s="26" t="inlineStr">
+        <is>
+          <t>Implementado, sin validar</t>
+        </is>
+      </c>
+      <c r="F17" s="29" t="inlineStr">
+        <is>
+          <t>VAL-21</t>
+        </is>
+      </c>
+      <c r="G17" s="26" t="inlineStr">
+        <is>
+          <t>Nueva · validacion</t>
+        </is>
+      </c>
+      <c r="H17" s="26" t="inlineStr">
+        <is>
+          <t>VAL-21 comprueba que Dispatch obtiene el contexto por HTTP a Core y no por SQL sobre tablas de Core (T1), que si Core no responde devuelve 503 sin logica local (T2), y que el contexto del tenant A nunca se entrega con el token del tenant B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="26" t="inlineStr">
+        <is>
+          <t>M-05.6</t>
+        </is>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>Broadcast de ofertas a los aliados elegibles</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>M-05</t>
+        </is>
+      </c>
+      <c r="D18" s="26" t="inlineStr">
+        <is>
+          <t>RF-14</t>
+        </is>
+      </c>
+      <c r="E18" s="26" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="F18" s="28" t="inlineStr">
+        <is>
+          <t>VAL-15 · TEC-04</t>
+        </is>
+      </c>
+      <c r="G18" s="26" t="inlineStr">
+        <is>
+          <t>Existentes, sin trazar</t>
+        </is>
+      </c>
+      <c r="H18" s="26" t="inlineStr">
+        <is>
+          <t>El broadcast pide PageSize=50 sin recorrer paginas y descarta totalCount, asi que con mas de 50 elegibles no oferta a todos. TEC-04 lo pagina y rehace la guarda de idempotencia; VAL-15 graba el broadcast completo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>M-05.8</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>Rechazar oferta</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>M-05</t>
+        </is>
+      </c>
+      <c r="D19" s="26" t="inlineStr">
+        <is>
+          <t>RF-14</t>
+        </is>
+      </c>
+      <c r="E19" s="26" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="F19" s="28" t="inlineStr">
+        <is>
+          <t>VAL-14 · TEC-03</t>
+        </is>
+      </c>
+      <c r="G19" s="26" t="inlineStr">
+        <is>
+          <t>Existentes, sin trazar</t>
+        </is>
+      </c>
+      <c r="H19" s="26" t="inlineStr">
+        <is>
+          <t>La politica solicitud_rechazo_aliado lee la tabla aliado y Dispatch no tiene SELECT sobre ella, asi que el INSERT falla con permission denied. TEC-03 corrige la politica y VAL-14 graba el rechazo y comprueba que la solicitud sigue disponible para los demas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>M-05.9</t>
+        </is>
+      </c>
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t>Idempotencia de la creacion y del despacho</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>M-05</t>
+        </is>
+      </c>
+      <c r="D20" s="26" t="inlineStr">
+        <is>
+          <t>RNF-03</t>
+        </is>
+      </c>
+      <c r="E20" s="26" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="F20" s="29" t="inlineStr">
+        <is>
+          <t>VAL-22 · TEC-04</t>
+        </is>
+      </c>
+      <c r="G20" s="26" t="inlineStr">
+        <is>
+          <t>Nueva validacion + tarea existente</t>
+        </is>
+      </c>
+      <c r="H20" s="26" t="inlineStr">
+        <is>
+          <t>RNF-03 exige que las operaciones criticas resistan reintentos sin duplicar. Hoy la guarda existingOffers.Count&gt;0 congela el reintento tras un corte parcial. TEC-04 la rehace y VAL-22 comprueba los tres casos: misma claveIdempotencia, reintento de la orquestacion y corte parcial del broadcast.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>M-08.3</t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="inlineStr">
+        <is>
+          <t>Cierre condicionado a la calificacion bidireccional</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>M-08</t>
+        </is>
+      </c>
+      <c r="D21" s="26" t="inlineStr">
+        <is>
+          <t>RF-19</t>
+        </is>
+      </c>
+      <c r="E21" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="F21" s="28" t="inlineStr">
+        <is>
+          <t>CONS-30</t>
+        </is>
+      </c>
+      <c r="G21" s="26" t="inlineStr">
+        <is>
+          <t>Existente, sin trazar</t>
+        </is>
+      </c>
+      <c r="H21" s="26" t="inlineStr">
+        <is>
+          <t>RF-19 exige que el servicio no pueda cerrarse hasta que ambas partes califiquen. CONS-30 lo construye desde cero, con la calificacion de las dos partes como condicion de cierre y no como paso opcional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>M-09.1</t>
+        </is>
+      </c>
+      <c r="B22" s="26" t="inlineStr">
+        <is>
+          <t>Frontera de notificacion del backend</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>M-09</t>
+        </is>
+      </c>
+      <c r="D22" s="26" t="inlineStr">
+        <is>
+          <t>RF-20</t>
+        </is>
+      </c>
+      <c r="E22" s="26" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="F22" s="28" t="inlineStr">
+        <is>
+          <t>CONS-35 · TEC-01</t>
+        </is>
+      </c>
+      <c r="G22" s="26" t="inlineStr">
+        <is>
+          <t>Existentes, sin trazar</t>
+        </is>
+      </c>
+      <c r="H22" s="26" t="inlineStr">
+        <is>
+          <t>Dispatch no debe insertar en tablas de notificacion: notifica a traves de Core (T1). El pendiente P-4 del SAD §7.4 sobre quien es dueno de la frontera sigue abierto y lo cierra TEC-01; CONS-35 construye el mock del proveedor push para que el front exista.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="96" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>Sprint 5 · Historias de gestion: Scrum Master y Product Owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="76" customHeight="1">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>Dos historias que no son de desarrollo y que el sprint necesita igual. SM-01 es la facilitacion del sprint, que hoy no esta en ningun bloque aunque la Scrum Master la ejecuta. PO-01 es la validacion del producto al final: es la que cierra el sprint, porque el DoD exige que cada funcionalidad este demostrada por video y aceptada, y alguien tiene que dar esa aceptacion. Autoridad: el PO decide los criterios de aceptacion y QA decide el DoD (GOBIERNO_DEL_EQUIPO.md §2.3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>Historia</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>Criterios de aceptacion</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="inlineStr">
+        <is>
+          <t>Prioridad</t>
+        </is>
+      </c>
+      <c r="G4" s="25" t="inlineStr">
+        <is>
+          <t>Dependencias</t>
+        </is>
+      </c>
+      <c r="H4" s="25" t="inlineStr">
+        <is>
+          <t>Momento</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>SM-01</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>Facilitar el sprint y sostener la trazabilidad del tablero</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>Sara Albarracin (Scrum Master)</t>
+        </is>
+      </c>
+      <c r="D5" s="26" t="inlineStr">
+        <is>
+          <t>Ceremonias de la sesion 5 celebradas y registradas: planning con el compromiso del sprint, dailies, review con la demostracion por video y retro con acuerdos. Cada item VAL, CONS y TEC existe en Jira con su clave, su estimacion y su responsable. Los impedimentos quedan registrados con fecha de apertura, responsable y fecha de cierre. Los indicadores del sprint se publican al cierre. Ningun item se declara terminado sin la subtarea de QA cerrada.</t>
+        </is>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="26" t="inlineStr">
+        <is>
+          <t>Highest</t>
+        </is>
+      </c>
+      <c r="G5" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" s="26" t="inlineStr">
+        <is>
+          <t>Todo el sprint</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="30" t="inlineStr">
+        <is>
+          <t>PO-01</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>Validar el producto terminado y aceptar el incremento</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
+        <is>
+          <t>Camila Beltran (Product Owner)</t>
+        </is>
+      </c>
+      <c r="D6" s="26" t="inlineStr">
+        <is>
+          <t>Recorrido completo del producto por el front, en QA y a traves del Gateway, con token real ES256, sobre el build desplegado. Se recorre el ciclo entero: registro, inicio de sesion por tipo, solicitud, elegibilidad, aceptacion sin doble asignacion, cotizacion, ejecucion, calificacion y cierre. Por cada funcionalidad del libro de modulos el PO declara aceptada o rechazada contra su criterio de §6 del backlog, no contra el estado del tablero. Un rechazo abre bug con el minuto exacto del video. El acta de aceptacion lista que se acepta, que se rechaza y que queda fuera del incremento con su causa (GOBIERNO_DEL_EQUIPO.md §10, incremento no entregado). Sin esta aceptacion el sprint no se cierra.</t>
+        </is>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" s="26" t="inlineStr">
+        <is>
+          <t>Highest</t>
+        </is>
+      </c>
+      <c r="G6" s="26" t="inlineStr">
+        <is>
+          <t>Todas las VAL y las CONS del sprint</t>
+        </is>
+      </c>
+      <c r="H6" s="26" t="inlineStr">
+        <is>
+          <t>Ultimos dias del sprint</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E95"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="54" customWidth="1" min="4" max="4"/>
+    <col width="104" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>Una subtarea de QA por historia: revisar y cerrar en Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="78" customHeight="1">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>Acuerdo del 24-oct-2026: ninguna historia pasa a Done por si misma. Cada una lleva una subtarea de Santiago (QA) que revisa la evidencia contra los criterios de la historia y es quien la mueve a Done. QA decide el DoD (GOBIERNO_DEL_EQUIPO.md §2.3), asi que la subtarea es el punto de control: si la evidencia no cumple, la historia vuelve y no se cierra. Esto cierra el hueco del Sprint 4, donde 14 subtareas de QA existian pero tres historias (SCRUM-1063, 1066 y 1068) no tenian ninguna, pendiente PE4 de §6.5 del backlog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>Subtarea</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>Historia</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>Bloque</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>Titulo de la historia</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t>Que revisa y cierra QA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-01</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>VAL-01</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>Validacion</t>
+        </is>
+      </c>
+      <c r="D5" s="26" t="inlineStr">
+        <is>
+          <t>Validar inicio de sesion con token real ES256 de extremo a extremo</t>
+        </is>
+      </c>
+      <c r="E5" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-02</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>VAL-02</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
+        <is>
+          <t>Validacion</t>
+        </is>
+      </c>
+      <c r="D6" s="26" t="inlineStr">
+        <is>
+          <t>Validar registro de aliado persona natural por el camino Gateway-Core</t>
+        </is>
+      </c>
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-03</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>VAL-03</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="inlineStr">
+        <is>
+          <t>Validacion</t>
+        </is>
+      </c>
+      <c r="D7" s="26" t="inlineStr">
+        <is>
+          <t>Validar registro de aliado empresa</t>
+        </is>
+      </c>
+      <c r="E7" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-04</t>
+        </is>
+      </c>
+      <c r="B8" s="26" t="inlineStr">
+        <is>
+          <t>VAL-04</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>Validacion</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="inlineStr">
+        <is>
+          <t>Validar registro de cliente persona natural</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-05</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>VAL-05</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>Validacion</t>
+        </is>
+      </c>
+      <c r="D9" s="26" t="inlineStr">
+        <is>
+          <t>Validar edicion del perfil propio</t>
+        </is>
+      </c>
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-06</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>VAL-06</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>Validacion</t>
+        </is>
+      </c>
+      <c r="D10" s="26" t="inlineStr">
+        <is>
+          <t>Validar aprobacion y rechazo de aliado en la bandeja de verificacion</t>
+        </is>
+      </c>
+      <c r="E10" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-07</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>VAL-07</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>Validacion</t>
+        </is>
+      </c>
+      <c r="D11" s="26" t="inlineStr">
+        <is>
+          <t>Validar declaracion de cobertura por zonas del aliado</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-08</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>VAL-08</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>Validacion</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="inlineStr">
+        <is>
+          <t>Validar que el aliado declara las categorias que atiende</t>
+        </is>
+      </c>
+      <c r="E12" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-09</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>VAL-09</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>Validacion</t>
+        </is>
+      </c>
+      <c r="D13" s="26" t="inlineStr">
+        <is>
+          <t>Validar gestion de categorias del tenant</t>
+        </is>
+      </c>
+      <c r="E13" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-10</t>
+        </is>
+      </c>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>VAL-10</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>Validacion</t>
+        </is>
+      </c>
+      <c r="D14" s="26" t="inlineStr">
+        <is>
+          <t>Validar creacion de la solicitud en Core desde el front</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-11</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>VAL-11</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>Validacion</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>Validar elegibilidad de aliados por categoria, zona, disponibilidad y rechazo previo</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-12</t>
+        </is>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>VAL-12</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>Validacion</t>
+        </is>
+      </c>
+      <c r="D16" s="26" t="inlineStr">
+        <is>
+          <t>Validar filtro por tipo de aliado</t>
+        </is>
+      </c>
+      <c r="E16" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-13</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>VAL-13</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>Validacion</t>
+        </is>
+      </c>
+      <c r="D17" s="26" t="inlineStr">
+        <is>
+          <t>Validar aceptacion sin doble asignacion con dos aliados simultaneos</t>
+        </is>
+      </c>
+      <c r="E17" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-14</t>
+        </is>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>VAL-14</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>Validacion</t>
+        </is>
+      </c>
+      <c r="D18" s="26" t="inlineStr">
+        <is>
+          <t>Validar rechazo de oferta</t>
+        </is>
+      </c>
+      <c r="E18" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-15</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>VAL-15</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>Validacion</t>
+        </is>
+      </c>
+      <c r="D19" s="26" t="inlineStr">
+        <is>
+          <t>Validar broadcast de ofertas y notificacion por la frontera de Core</t>
+        </is>
+      </c>
+      <c r="E19" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-16</t>
+        </is>
+      </c>
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t>VAL-16</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>Validacion</t>
+        </is>
+      </c>
+      <c r="D20" s="26" t="inlineStr">
+        <is>
+          <t>Validar aislamiento multi-tenant endpoint por endpoint</t>
+        </is>
+      </c>
+      <c r="E20" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-17</t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="inlineStr">
+        <is>
+          <t>VAL-17</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>Validacion</t>
+        </is>
+      </c>
+      <c r="D21" s="26" t="inlineStr">
+        <is>
+          <t>Validar logout y expiracion de sesion</t>
+        </is>
+      </c>
+      <c r="E21" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-18</t>
+        </is>
+      </c>
+      <c r="B22" s="26" t="inlineStr">
+        <is>
+          <t>VAL-18</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>Validacion</t>
+        </is>
+      </c>
+      <c r="D22" s="26" t="inlineStr">
+        <is>
+          <t>Ejecutar la regresion de seguridad de identidad (17 casos negativos y 1 positivo)</t>
+        </is>
+      </c>
+      <c r="E22" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-19</t>
+        </is>
+      </c>
+      <c r="B23" s="26" t="inlineStr">
+        <is>
+          <t>VAL-19</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>Validacion</t>
+        </is>
+      </c>
+      <c r="D23" s="26" t="inlineStr">
+        <is>
+          <t>Validar el contrato del perfil del aliado que consumen Dispatch y Rules</t>
+        </is>
+      </c>
+      <c r="E23" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-20</t>
+        </is>
+      </c>
+      <c r="B24" s="26" t="inlineStr">
+        <is>
+          <t>VAL-20</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>Validacion</t>
+        </is>
+      </c>
+      <c r="D24" s="26" t="inlineStr">
+        <is>
+          <t>Validar que el catalogo responde solo las categorias y zonas del tenant del claim</t>
+        </is>
+      </c>
+      <c r="E24" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-21</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="inlineStr">
+        <is>
+          <t>VAL-21</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>Validacion</t>
+        </is>
+      </c>
+      <c r="D25" s="26" t="inlineStr">
+        <is>
+          <t>Validar el contexto de solicitud que Dispatch pide a Core</t>
+        </is>
+      </c>
+      <c r="E25" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-22</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="inlineStr">
+        <is>
+          <t>VAL-22</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>Validacion</t>
+        </is>
+      </c>
+      <c r="D26" s="26" t="inlineStr">
+        <is>
+          <t>Validar idempotencia de la creacion de solicitud y del despacho bajo reintento</t>
+        </is>
+      </c>
+      <c r="E26" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-01</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="inlineStr">
+        <is>
+          <t>CONS-01</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D27" s="26" t="inlineStr">
+        <is>
+          <t>Inicio de sesion separado por tipo de usuario</t>
+        </is>
+      </c>
+      <c r="E27" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-02</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="inlineStr">
+        <is>
+          <t>CONS-02</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D28" s="26" t="inlineStr">
+        <is>
+          <t>Logout</t>
+        </is>
+      </c>
+      <c r="E28" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-03</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="inlineStr">
+        <is>
+          <t>CONS-03</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D29" s="26" t="inlineStr">
+        <is>
+          <t>Autenticacion consumida desde la API y retiro de Supabase directo en el cliente</t>
+        </is>
+      </c>
+      <c r="E29" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-04</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="inlineStr">
+        <is>
+          <t>CONS-04</t>
+        </is>
+      </c>
+      <c r="C30" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D30" s="26" t="inlineStr">
+        <is>
+          <t>Recuperacion segura de contrasena</t>
+        </is>
+      </c>
+      <c r="E30" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-05</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="inlineStr">
+        <is>
+          <t>CONS-05</t>
+        </is>
+      </c>
+      <c r="C31" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D31" s="26" t="inlineStr">
+        <is>
+          <t>Registro de cliente empresa</t>
+        </is>
+      </c>
+      <c r="E31" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-06</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="inlineStr">
+        <is>
+          <t>CONS-06</t>
+        </is>
+      </c>
+      <c r="C32" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D32" s="26" t="inlineStr">
+        <is>
+          <t>Registro de empleado directo</t>
+        </is>
+      </c>
+      <c r="E32" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-07</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="inlineStr">
+        <is>
+          <t>CONS-07</t>
+        </is>
+      </c>
+      <c r="C33" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D33" s="26" t="inlineStr">
+        <is>
+          <t>Menu superior por rol con sesion visible</t>
+        </is>
+      </c>
+      <c r="E33" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-08</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="inlineStr">
+        <is>
+          <t>CONS-08</t>
+        </is>
+      </c>
+      <c r="C34" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D34" s="26" t="inlineStr">
+        <is>
+          <t>Pantalla de inicio por tipo de usuario</t>
+        </is>
+      </c>
+      <c r="E34" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-09</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="inlineStr">
+        <is>
+          <t>CONS-09</t>
+        </is>
+      </c>
+      <c r="C35" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D35" s="26" t="inlineStr">
+        <is>
+          <t>Enrutamiento por rol con guardas de sesion</t>
+        </is>
+      </c>
+      <c r="E35" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-10</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="inlineStr">
+        <is>
+          <t>CONS-10</t>
+        </is>
+      </c>
+      <c r="C36" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D36" s="26" t="inlineStr">
+        <is>
+          <t>Dividir el front en modulos independientes por dominio</t>
+        </is>
+      </c>
+      <c r="E36" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-11</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="inlineStr">
+        <is>
+          <t>CONS-11</t>
+        </is>
+      </c>
+      <c r="C37" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D37" s="26" t="inlineStr">
+        <is>
+          <t>Dividir el Core por dominios internos</t>
+        </is>
+      </c>
+      <c r="E37" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-12</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="inlineStr">
+        <is>
+          <t>CONS-12</t>
+        </is>
+      </c>
+      <c r="C38" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D38" s="26" t="inlineStr">
+        <is>
+          <t>Barrios como nivel mas fino del catalogo de zonas</t>
+        </is>
+      </c>
+      <c r="E38" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-13</t>
+        </is>
+      </c>
+      <c r="B39" s="26" t="inlineStr">
+        <is>
+          <t>CONS-13</t>
+        </is>
+      </c>
+      <c r="C39" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D39" s="26" t="inlineStr">
+        <is>
+          <t>Visualizacion en mapa de zonas, barrios y sitio de servicio</t>
+        </is>
+      </c>
+      <c r="E39" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-14</t>
+        </is>
+      </c>
+      <c r="B40" s="26" t="inlineStr">
+        <is>
+          <t>CONS-14</t>
+        </is>
+      </c>
+      <c r="C40" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D40" s="26" t="inlineStr">
+        <is>
+          <t>Activar y desactivar categoria sin afectar servicios en curso</t>
+        </is>
+      </c>
+      <c r="E40" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-15</t>
+        </is>
+      </c>
+      <c r="B41" s="26" t="inlineStr">
+        <is>
+          <t>CONS-15</t>
+        </is>
+      </c>
+      <c r="C41" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D41" s="26" t="inlineStr">
+        <is>
+          <t>Aliado gestiona su disponibilidad y sus ausencias</t>
+        </is>
+      </c>
+      <c r="E41" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-16</t>
+        </is>
+      </c>
+      <c r="B42" s="26" t="inlineStr">
+        <is>
+          <t>CONS-16</t>
+        </is>
+      </c>
+      <c r="C42" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D42" s="26" t="inlineStr">
+        <is>
+          <t>Cliente empresa administra multiples sitios de servicio</t>
+        </is>
+      </c>
+      <c r="E42" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-17</t>
+        </is>
+      </c>
+      <c r="B43" s="26" t="inlineStr">
+        <is>
+          <t>CONS-17</t>
+        </is>
+      </c>
+      <c r="C43" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D43" s="26" t="inlineStr">
+        <is>
+          <t>Reglas contextuales del sitio visibles al aliado antes de programar</t>
+        </is>
+      </c>
+      <c r="E43" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-18</t>
+        </is>
+      </c>
+      <c r="B44" s="26" t="inlineStr">
+        <is>
+          <t>CONS-18</t>
+        </is>
+      </c>
+      <c r="C44" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D44" s="26" t="inlineStr">
+        <is>
+          <t>Orden del listado de aliados en el Rules Service</t>
+        </is>
+      </c>
+      <c r="E44" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-19</t>
+        </is>
+      </c>
+      <c r="B45" s="26" t="inlineStr">
+        <is>
+          <t>CONS-19</t>
+        </is>
+      </c>
+      <c r="C45" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D45" s="26" t="inlineStr">
+        <is>
+          <t>Priorizar solicitud por comision ofrecida</t>
+        </is>
+      </c>
+      <c r="E45" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-20</t>
+        </is>
+      </c>
+      <c r="B46" s="26" t="inlineStr">
+        <is>
+          <t>CONS-20</t>
+        </is>
+      </c>
+      <c r="C46" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D46" s="26" t="inlineStr">
+        <is>
+          <t>Cancelar solicitud antes de la ejecucion</t>
+        </is>
+      </c>
+      <c r="E46" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-21</t>
+        </is>
+      </c>
+      <c r="B47" s="26" t="inlineStr">
+        <is>
+          <t>CONS-21</t>
+        </is>
+      </c>
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D47" s="26" t="inlineStr">
+        <is>
+          <t>Cotizacion con mano de obra y materiales separados</t>
+        </is>
+      </c>
+      <c r="E47" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-22</t>
+        </is>
+      </c>
+      <c r="B48" s="26" t="inlineStr">
+        <is>
+          <t>CONS-22</t>
+        </is>
+      </c>
+      <c r="C48" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D48" s="26" t="inlineStr">
+        <is>
+          <t>Alerta de cotizacion fuera del rango del tarifario</t>
+        </is>
+      </c>
+      <c r="E48" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-23</t>
+        </is>
+      </c>
+      <c r="B49" s="26" t="inlineStr">
+        <is>
+          <t>CONS-23</t>
+        </is>
+      </c>
+      <c r="C49" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D49" s="26" t="inlineStr">
+        <is>
+          <t>Cliente acepta, rechaza o solicita ajuste de la cotizacion</t>
+        </is>
+      </c>
+      <c r="E49" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-24</t>
+        </is>
+      </c>
+      <c r="B50" s="26" t="inlineStr">
+        <is>
+          <t>CONS-24</t>
+        </is>
+      </c>
+      <c r="C50" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D50" s="26" t="inlineStr">
+        <is>
+          <t>Marcar inicio y fin de la ejecucion</t>
+        </is>
+      </c>
+      <c r="E50" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-25</t>
+        </is>
+      </c>
+      <c r="B51" s="26" t="inlineStr">
+        <is>
+          <t>CONS-25</t>
+        </is>
+      </c>
+      <c r="C51" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D51" s="26" t="inlineStr">
+        <is>
+          <t>Registrar eventos y observaciones durante la ejecucion</t>
+        </is>
+      </c>
+      <c r="E51" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-26</t>
+        </is>
+      </c>
+      <c r="B52" s="26" t="inlineStr">
+        <is>
+          <t>CONS-26</t>
+        </is>
+      </c>
+      <c r="C52" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D52" s="26" t="inlineStr">
+        <is>
+          <t>Registrar evidencias sin conexion y sincronizarlas</t>
+        </is>
+      </c>
+      <c r="E52" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-27</t>
+        </is>
+      </c>
+      <c r="B53" s="26" t="inlineStr">
+        <is>
+          <t>CONS-27</t>
+        </is>
+      </c>
+      <c r="C53" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D53" s="26" t="inlineStr">
+        <is>
+          <t>Cargar la tabla de tarifas por categoria</t>
+        </is>
+      </c>
+      <c r="E53" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-28</t>
+        </is>
+      </c>
+      <c r="B54" s="26" t="inlineStr">
+        <is>
+          <t>CONS-28</t>
+        </is>
+      </c>
+      <c r="C54" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D54" s="26" t="inlineStr">
+        <is>
+          <t>Ver la tarifa de referencia al cotizar</t>
+        </is>
+      </c>
+      <c r="E54" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-29</t>
+        </is>
+      </c>
+      <c r="B55" s="26" t="inlineStr">
+        <is>
+          <t>CONS-29</t>
+        </is>
+      </c>
+      <c r="C55" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D55" s="26" t="inlineStr">
+        <is>
+          <t>Reporte de cotizaciones fuera de rango por periodo</t>
+        </is>
+      </c>
+      <c r="E55" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-30</t>
+        </is>
+      </c>
+      <c r="B56" s="26" t="inlineStr">
+        <is>
+          <t>CONS-30</t>
+        </is>
+      </c>
+      <c r="C56" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D56" s="26" t="inlineStr">
+        <is>
+          <t>Calificacion bidireccional y cierre condicionado</t>
+        </is>
+      </c>
+      <c r="E56" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-31</t>
+        </is>
+      </c>
+      <c r="B57" s="26" t="inlineStr">
+        <is>
+          <t>CONS-31</t>
+        </is>
+      </c>
+      <c r="C57" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D57" s="26" t="inlineStr">
+        <is>
+          <t>Calificacion agregada visible en el listado de aliados</t>
+        </is>
+      </c>
+      <c r="E57" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-32</t>
+        </is>
+      </c>
+      <c r="B58" s="26" t="inlineStr">
+        <is>
+          <t>CONS-32</t>
+        </is>
+      </c>
+      <c r="C58" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D58" s="26" t="inlineStr">
+        <is>
+          <t>Penalizacion por cancelacion tardia</t>
+        </is>
+      </c>
+      <c r="E58" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-33</t>
+        </is>
+      </c>
+      <c r="B59" s="26" t="inlineStr">
+        <is>
+          <t>CONS-33</t>
+        </is>
+      </c>
+      <c r="C59" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D59" s="26" t="inlineStr">
+        <is>
+          <t>Historial de servicios del cliente y de trabajos del aliado</t>
+        </is>
+      </c>
+      <c r="E59" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-34</t>
+        </is>
+      </c>
+      <c r="B60" s="26" t="inlineStr">
+        <is>
+          <t>CONS-34</t>
+        </is>
+      </c>
+      <c r="C60" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D60" s="26" t="inlineStr">
+        <is>
+          <t>Mensajeria cliente-aliado por servicio</t>
+        </is>
+      </c>
+      <c r="E60" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-35</t>
+        </is>
+      </c>
+      <c r="B61" s="26" t="inlineStr">
+        <is>
+          <t>CONS-35</t>
+        </is>
+      </c>
+      <c r="C61" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D61" s="26" t="inlineStr">
+        <is>
+          <t>Mock del proveedor de notificaciones push en el backend</t>
+        </is>
+      </c>
+      <c r="E61" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-36</t>
+        </is>
+      </c>
+      <c r="B62" s="26" t="inlineStr">
+        <is>
+          <t>CONS-36</t>
+        </is>
+      </c>
+      <c r="C62" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D62" s="26" t="inlineStr">
+        <is>
+          <t>Notificaciones de mensajes nuevos y del ciclo del servicio</t>
+        </is>
+      </c>
+      <c r="E62" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-37</t>
+        </is>
+      </c>
+      <c r="B63" s="26" t="inlineStr">
+        <is>
+          <t>CONS-37</t>
+        </is>
+      </c>
+      <c r="C63" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D63" s="26" t="inlineStr">
+        <is>
+          <t>Consultar la conversacion para atender una queja</t>
+        </is>
+      </c>
+      <c r="E63" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-38</t>
+        </is>
+      </c>
+      <c r="B64" s="26" t="inlineStr">
+        <is>
+          <t>CONS-38</t>
+        </is>
+      </c>
+      <c r="C64" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D64" s="26" t="inlineStr">
+        <is>
+          <t>Mock de la pasarela de pagos</t>
+        </is>
+      </c>
+      <c r="E64" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-39</t>
+        </is>
+      </c>
+      <c r="B65" s="26" t="inlineStr">
+        <is>
+          <t>CONS-39</t>
+        </is>
+      </c>
+      <c r="C65" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D65" s="26" t="inlineStr">
+        <is>
+          <t>Registro inmutable de transacciones</t>
+        </is>
+      </c>
+      <c r="E65" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-40</t>
+        </is>
+      </c>
+      <c r="B66" s="26" t="inlineStr">
+        <is>
+          <t>CONS-40</t>
+        </is>
+      </c>
+      <c r="C66" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D66" s="26" t="inlineStr">
+        <is>
+          <t>Liquidacion al aliado con comision configurable</t>
+        </is>
+      </c>
+      <c r="E66" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-41</t>
+        </is>
+      </c>
+      <c r="B67" s="26" t="inlineStr">
+        <is>
+          <t>CONS-41</t>
+        </is>
+      </c>
+      <c r="C67" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D67" s="26" t="inlineStr">
+        <is>
+          <t>Registro y gestion de quejas</t>
+        </is>
+      </c>
+      <c r="E67" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-42</t>
+        </is>
+      </c>
+      <c r="B68" s="26" t="inlineStr">
+        <is>
+          <t>CONS-42</t>
+        </is>
+      </c>
+      <c r="C68" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D68" s="26" t="inlineStr">
+        <is>
+          <t>Metricas operativas por tenant y endpoint /metrics</t>
+        </is>
+      </c>
+      <c r="E68" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-43</t>
+        </is>
+      </c>
+      <c r="B69" s="26" t="inlineStr">
+        <is>
+          <t>CONS-43</t>
+        </is>
+      </c>
+      <c r="C69" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D69" s="26" t="inlineStr">
+        <is>
+          <t>Administrar el estado de los tenants</t>
+        </is>
+      </c>
+      <c r="E69" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-44</t>
+        </is>
+      </c>
+      <c r="B70" s="26" t="inlineStr">
+        <is>
+          <t>CONS-44</t>
+        </is>
+      </c>
+      <c r="C70" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D70" s="26" t="inlineStr">
+        <is>
+          <t>Configuracion de reglas por tenant sin despliegue</t>
+        </is>
+      </c>
+      <c r="E70" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-45</t>
+        </is>
+      </c>
+      <c r="B71" s="26" t="inlineStr">
+        <is>
+          <t>CONS-45</t>
+        </is>
+      </c>
+      <c r="C71" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D71" s="26" t="inlineStr">
+        <is>
+          <t>Cifrado y manejo de secretos verificado de punta a punta</t>
+        </is>
+      </c>
+      <c r="E71" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-46</t>
+        </is>
+      </c>
+      <c r="B72" s="26" t="inlineStr">
+        <is>
+          <t>CONS-46</t>
+        </is>
+      </c>
+      <c r="C72" s="26" t="inlineStr">
+        <is>
+          <t>Construccion</t>
+        </is>
+      </c>
+      <c r="D72" s="26" t="inlineStr">
+        <is>
+          <t>Alta y administracion de tenants por el administrador de plataforma</t>
+        </is>
+      </c>
+      <c r="E72" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-01</t>
+        </is>
+      </c>
+      <c r="B73" s="26" t="inlineStr">
+        <is>
+          <t>TEC-01</t>
+        </is>
+      </c>
+      <c r="C73" s="26" t="inlineStr">
+        <is>
+          <t>Tarea tecnica</t>
+        </is>
+      </c>
+      <c r="D73" s="26" t="inlineStr">
+        <is>
+          <t>Cerrar la contradiccion documental sobre quien crea la solicitud</t>
+        </is>
+      </c>
+      <c r="E73" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-02</t>
+        </is>
+      </c>
+      <c r="B74" s="26" t="inlineStr">
+        <is>
+          <t>TEC-02</t>
+        </is>
+      </c>
+      <c r="C74" s="26" t="inlineStr">
+        <is>
+          <t>Tarea tecnica</t>
+        </is>
+      </c>
+      <c r="D74" s="26" t="inlineStr">
+        <is>
+          <t>Fijar el contexto de identidad en cada transaccion de Dispatch</t>
+        </is>
+      </c>
+      <c r="E74" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-03</t>
+        </is>
+      </c>
+      <c r="B75" s="26" t="inlineStr">
+        <is>
+          <t>TEC-03</t>
+        </is>
+      </c>
+      <c r="C75" s="26" t="inlineStr">
+        <is>
+          <t>Tarea tecnica</t>
+        </is>
+      </c>
+      <c r="D75" s="26" t="inlineStr">
+        <is>
+          <t>Corregir la politica de solicitud_rechazo</t>
+        </is>
+      </c>
+      <c r="E75" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-04</t>
+        </is>
+      </c>
+      <c r="B76" s="26" t="inlineStr">
+        <is>
+          <t>TEC-04</t>
+        </is>
+      </c>
+      <c r="C76" s="26" t="inlineStr">
+        <is>
+          <t>Tarea tecnica</t>
+        </is>
+      </c>
+      <c r="D76" s="26" t="inlineStr">
+        <is>
+          <t>Paginar el broadcast y hacer idempotente el reintento parcial</t>
+        </is>
+      </c>
+      <c r="E76" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-05</t>
+        </is>
+      </c>
+      <c r="B77" s="26" t="inlineStr">
+        <is>
+          <t>TEC-05</t>
+        </is>
+      </c>
+      <c r="C77" s="26" t="inlineStr">
+        <is>
+          <t>Tarea tecnica</t>
+        </is>
+      </c>
+      <c r="D77" s="26" t="inlineStr">
+        <is>
+          <t>Distinguir conflicto de asignacion de conflicto de estado</t>
+        </is>
+      </c>
+      <c r="E77" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-06</t>
+        </is>
+      </c>
+      <c r="B78" s="26" t="inlineStr">
+        <is>
+          <t>TEC-06</t>
+        </is>
+      </c>
+      <c r="C78" s="26" t="inlineStr">
+        <is>
+          <t>Tarea tecnica</t>
+        </is>
+      </c>
+      <c r="D78" s="26" t="inlineStr">
+        <is>
+          <t>Declarar CORE_SERVICE_URL en manifiestos versionados</t>
+        </is>
+      </c>
+      <c r="E78" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-07</t>
+        </is>
+      </c>
+      <c r="B79" s="26" t="inlineStr">
+        <is>
+          <t>TEC-07</t>
+        </is>
+      </c>
+      <c r="C79" s="26" t="inlineStr">
+        <is>
+          <t>Tarea tecnica</t>
+        </is>
+      </c>
+      <c r="D79" s="26" t="inlineStr">
+        <is>
+          <t>Unificar la politica de token de Dispatch con la de Core</t>
+        </is>
+      </c>
+      <c r="E79" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-08</t>
+        </is>
+      </c>
+      <c r="B80" s="26" t="inlineStr">
+        <is>
+          <t>TEC-08</t>
+        </is>
+      </c>
+      <c r="C80" s="26" t="inlineStr">
+        <is>
+          <t>Tarea tecnica</t>
+        </is>
+      </c>
+      <c r="D80" s="26" t="inlineStr">
+        <is>
+          <t>Documentar el salto de numeracion de migraciones y recuperar 0012</t>
+        </is>
+      </c>
+      <c r="E80" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-09</t>
+        </is>
+      </c>
+      <c r="B81" s="26" t="inlineStr">
+        <is>
+          <t>TEC-09</t>
+        </is>
+      </c>
+      <c r="C81" s="26" t="inlineStr">
+        <is>
+          <t>Tarea tecnica</t>
+        </is>
+      </c>
+      <c r="D81" s="26" t="inlineStr">
+        <is>
+          <t>Cerrar dev-token y la ruta publica de validate-token en el Gateway, y rotar secretos</t>
+        </is>
+      </c>
+      <c r="E81" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-10</t>
+        </is>
+      </c>
+      <c r="B82" s="26" t="inlineStr">
+        <is>
+          <t>TEC-10</t>
+        </is>
+      </c>
+      <c r="C82" s="26" t="inlineStr">
+        <is>
+          <t>Tarea tecnica</t>
+        </is>
+      </c>
+      <c r="D82" s="26" t="inlineStr">
+        <is>
+          <t>Un solo validador de token, con ES256, iss y aud</t>
+        </is>
+      </c>
+      <c r="E82" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-11</t>
+        </is>
+      </c>
+      <c r="B83" s="26" t="inlineStr">
+        <is>
+          <t>TEC-11</t>
+        </is>
+      </c>
+      <c r="C83" s="26" t="inlineStr">
+        <is>
+          <t>Tarea tecnica</t>
+        </is>
+      </c>
+      <c r="D83" s="26" t="inlineStr">
+        <is>
+          <t>Confirmar o montar TLS en el borde</t>
+        </is>
+      </c>
+      <c r="E83" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-12</t>
+        </is>
+      </c>
+      <c r="B84" s="26" t="inlineStr">
+        <is>
+          <t>TEC-12</t>
+        </is>
+      </c>
+      <c r="C84" s="26" t="inlineStr">
+        <is>
+          <t>Tarea tecnica</t>
+        </is>
+      </c>
+      <c r="D84" s="26" t="inlineStr">
+        <is>
+          <t>Ratificar ADR-0030 y ADR-0016 en Mesa</t>
+        </is>
+      </c>
+      <c r="E84" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-13</t>
+        </is>
+      </c>
+      <c r="B85" s="26" t="inlineStr">
+        <is>
+          <t>TEC-13</t>
+        </is>
+      </c>
+      <c r="C85" s="26" t="inlineStr">
+        <is>
+          <t>Tarea tecnica</t>
+        </is>
+      </c>
+      <c r="D85" s="26" t="inlineStr">
+        <is>
+          <t>Definir identidad de servicio entre Dispatch y Core</t>
+        </is>
+      </c>
+      <c r="E85" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-14</t>
+        </is>
+      </c>
+      <c r="B86" s="26" t="inlineStr">
+        <is>
+          <t>TEC-14</t>
+        </is>
+      </c>
+      <c r="C86" s="26" t="inlineStr">
+        <is>
+          <t>Tarea tecnica</t>
+        </is>
+      </c>
+      <c r="D86" s="26" t="inlineStr">
+        <is>
+          <t>Observabilidad minima de autenticacion</t>
+        </is>
+      </c>
+      <c r="E86" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-15</t>
+        </is>
+      </c>
+      <c r="B87" s="26" t="inlineStr">
+        <is>
+          <t>TEC-15</t>
+        </is>
+      </c>
+      <c r="C87" s="26" t="inlineStr">
+        <is>
+          <t>Tarea tecnica</t>
+        </is>
+      </c>
+      <c r="D87" s="26" t="inlineStr">
+        <is>
+          <t>Crear el repositorio del Rules Service</t>
+        </is>
+      </c>
+      <c r="E87" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-16</t>
+        </is>
+      </c>
+      <c r="B88" s="26" t="inlineStr">
+        <is>
+          <t>TEC-16</t>
+        </is>
+      </c>
+      <c r="C88" s="26" t="inlineStr">
+        <is>
+          <t>Tarea tecnica</t>
+        </is>
+      </c>
+      <c r="D88" s="26" t="inlineStr">
+        <is>
+          <t>Preparar el ambiente QA y los datos sembrados del sprint de validacion</t>
+        </is>
+      </c>
+      <c r="E88" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-17</t>
+        </is>
+      </c>
+      <c r="B89" s="26" t="inlineStr">
+        <is>
+          <t>TEC-17</t>
+        </is>
+      </c>
+      <c r="C89" s="26" t="inlineStr">
+        <is>
+          <t>Tarea tecnica</t>
+        </is>
+      </c>
+      <c r="D89" s="26" t="inlineStr">
+        <is>
+          <t>Guia de grabacion y repositorio de videos</t>
+        </is>
+      </c>
+      <c r="E89" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-18</t>
+        </is>
+      </c>
+      <c r="B90" s="26" t="inlineStr">
+        <is>
+          <t>TEC-18</t>
+        </is>
+      </c>
+      <c r="C90" s="26" t="inlineStr">
+        <is>
+          <t>Tarea tecnica</t>
+        </is>
+      </c>
+      <c r="D90" s="26" t="inlineStr">
+        <is>
+          <t>Migrar el front de solicitudes y asignacion al camino Gateway-Core</t>
+        </is>
+      </c>
+      <c r="E90" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-19</t>
+        </is>
+      </c>
+      <c r="B91" s="26" t="inlineStr">
+        <is>
+          <t>TEC-19</t>
+        </is>
+      </c>
+      <c r="C91" s="26" t="inlineStr">
+        <is>
+          <t>Tarea tecnica</t>
+        </is>
+      </c>
+      <c r="D91" s="26" t="inlineStr">
+        <is>
+          <t>Migracion de usuario para direccion y foto de perfil</t>
+        </is>
+      </c>
+      <c r="E91" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-20</t>
+        </is>
+      </c>
+      <c r="B92" s="26" t="inlineStr">
+        <is>
+          <t>TEC-20</t>
+        </is>
+      </c>
+      <c r="C92" s="26" t="inlineStr">
+        <is>
+          <t>Tarea tecnica</t>
+        </is>
+      </c>
+      <c r="D92" s="26" t="inlineStr">
+        <is>
+          <t>Persistir verificado_por en el adaptador real</t>
+        </is>
+      </c>
+      <c r="E92" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-21</t>
+        </is>
+      </c>
+      <c r="B93" s="26" t="inlineStr">
+        <is>
+          <t>TEC-21</t>
+        </is>
+      </c>
+      <c r="C93" s="26" t="inlineStr">
+        <is>
+          <t>Tarea tecnica</t>
+        </is>
+      </c>
+      <c r="D93" s="26" t="inlineStr">
+        <is>
+          <t>Retirar BYPASSRLS: Core y Dispatch conectan con un rol de servicio sin privilegio de salto</t>
+        </is>
+      </c>
+      <c r="E93" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="30" t="inlineStr">
+        <is>
+          <t>QA-SM-01</t>
+        </is>
+      </c>
+      <c r="B94" s="26" t="inlineStr">
+        <is>
+          <t>SM-01</t>
+        </is>
+      </c>
+      <c r="C94" s="26" t="inlineStr">
+        <is>
+          <t>Gestion</t>
+        </is>
+      </c>
+      <c r="D94" s="26" t="inlineStr">
+        <is>
+          <t>Sara Albarracin (Scrum Master)</t>
+        </is>
+      </c>
+      <c r="E94" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el registro existe y es verificable: para SM-01, que las ceremonias, los impedimentos y los indicadores estan publicados y que ningun item se declaro terminado sin su subtarea de QA cerrada; para PO-01, que el acta de aceptacion lista explicitamente lo aceptado, lo rechazado y lo que queda fuera del incremento con su causa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="30" t="inlineStr">
+        <is>
+          <t>QA-PO-01</t>
+        </is>
+      </c>
+      <c r="B95" s="26" t="inlineStr">
+        <is>
+          <t>PO-01</t>
+        </is>
+      </c>
+      <c r="C95" s="26" t="inlineStr">
+        <is>
+          <t>Gestion</t>
+        </is>
+      </c>
+      <c r="D95" s="26" t="inlineStr">
+        <is>
+          <t>Camila Beltran (Product Owner)</t>
+        </is>
+      </c>
+      <c r="E95" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el registro existe y es verificable: para SM-01, que las ceremonias, los impedimentos y los indicadores estan publicados y que ningun item se declaro terminado sin su subtarea de QA cerrada; para PO-01, que el acta de aceptacion lista explicitamente lo aceptado, lo rechazado y lo que queda fuera del incremento con su causa.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -24123,7 +27992,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CONS-46</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -24175,7 +28044,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VAL-16 · TEC-21</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -24224,12 +28093,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>RF-02 / RNF-02 / RNF-10</t>
+          <t>RF-02 / RNF-02 / RNF-10 / REST-05</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CONS-44 · TEC-15</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -24282,7 +28151,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VAL-16 · TEC-09</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -24334,7 +28203,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TEC-08</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -24482,7 +28351,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VAL-01 · TEC-10</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -24893,7 +28762,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>RF-05 / RF-08</t>
+          <t>RF-30 / RF-05 / RF-08</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -24950,7 +28819,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CONS-04</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -24997,7 +28866,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>RF-31</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -25106,7 +28975,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VAL-18 · TEC-10</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -25158,7 +29027,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VAL-18 · TEC-07</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -25458,7 +29327,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>RF-12 (soporte)</t>
+          <t>RF-29 / RF-12 (soporte)</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -25614,12 +29483,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>RF-05</t>
+          <t>RF-30 / RF-05</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VAL-19</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -25925,7 +29794,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CONS-12</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -25977,7 +29846,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VAL-20</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -26278,7 +30147,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>RF-12</t>
+          <t>RF-12 / RNF-07</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -26336,7 +30205,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VAL-21</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -26495,7 +30364,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VAL-15 · TEC-04</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -26543,7 +30412,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>RF-14 / RNF-05</t>
+          <t>RF-14 / RNF-05 / RNF-07</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -26600,7 +30469,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VAL-14 · TEC-03</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -26652,7 +30521,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VAL-22 · TEC-04</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -26700,7 +30569,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>RF-14</t>
+          <t>RF-32 / RF-14</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">

--- a/wiki/05-backlog/MANI_MODULOS_SERVICIOS_Y_BACKLOG_S5.xlsx
+++ b/wiki/05-backlog/MANI_MODULOS_SERVICIOS_Y_BACKLOG_S5.xlsx
@@ -40,7 +40,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20 Criterios US-02.1.1" sheetId="31" state="visible" r:id="rId31"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21 Cierre de cobertura" sheetId="32" state="visible" r:id="rId32"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22 Gestion del sprint" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23 Subtareas de QA" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24 Sprint 5 por modulo" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -94,7 +94,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -144,6 +144,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00BDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -231,7 +241,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -310,6 +320,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -866,6 +882,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -1118,6 +1135,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -1527,6 +1545,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -1988,6 +2007,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2398,6 +2418,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2651,6 +2672,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3165,6 +3187,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3625,6 +3648,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -12156,38 +12180,26 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Validacion (VAL)</t>
+          <t>Historias por funcionalidad (hoja 24)</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Demostrar por video lo que el backlog declara cerrado, mas la regresion de identidad</t>
+          <t>Una historia por funcionalidad, repartida por modulo</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>101</v>
+        <v>382</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Construccion (CONS)</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Lo que falta del producto comprometido, incluidos los dos mocks y los items nuevos de la PO</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>277</v>
-      </c>
+      <c r="A18" s="3" t="n"/>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
@@ -12233,10 +12245,10 @@
       </c>
       <c r="B21" s="3" t="inlineStr"/>
       <c r="C21" s="21" t="n">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D21" s="21" t="n">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="22"/>
@@ -12350,7 +12362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13170,7 +13182,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" s="22" t="inlineStr">
         <is>
-          <t>VAL-17</t>
+          <t>VAL-18</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -13180,116 +13192,121 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Validar logout y expiracion de sesion</t>
+          <t>Ejecutar la regresion de seguridad de identidad (17 casos negativos y 1 positivo)</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Cliente / Aliado / Admin</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Al salir, el token local se descarta, el estado se limpia y el regreso exige autenticarse de nuevo. Con token expirado, el front vuelve al login en lugar de quedarse en blanco.</t>
+          <t>Los 17 casos de la hoja '11 Casos de regresion' verdes por el Gateway, con asercion de codigo y de cuerpo, y el caso positivo con token obtenido de GoTrue, no firmado en CI.</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Highest</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>TEC-09 (H-01), TEC-10 (H-02), TEC-11 (TLS)</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>CORE, DISPATCH</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="40" customHeight="1"/>
+    <row r="23">
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Total: 18 historias · 87 story points</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="28" t="inlineStr">
+        <is>
+          <t>VAL-19</t>
+        </is>
+      </c>
+      <c r="B24" s="26" t="inlineStr">
+        <is>
+          <t>M-03</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>Validar el contrato del perfil del aliado que consumen Dispatch y Rules</t>
+        </is>
+      </c>
+      <c r="D24" s="26" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+      <c r="E24" s="26" t="inlineStr">
+        <is>
+          <t>Existe en codigo pero nunca se valido como contrato. Pedir el perfil del aliado por el Gateway con token real ES256 y comprobar: responde los campos que Dispatch y Rules declaran consumir, no expone documentos KYC ni datos de otro aliado, y con el token de un aliado del tenant B sobre un aliado del tenant A responde 403 o 404 y nunca 200 con datos. Video desde el front o, si no tiene pantalla, corrida Newman adjunta.</t>
+        </is>
+      </c>
+      <c r="F24" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G24" s="26" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>CONS-02 (logout construido)</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>CORE</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22" ht="40" customHeight="1">
-      <c r="A22" s="22" t="inlineStr">
-        <is>
-          <t>VAL-18</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>M-02</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Ejecutar la regresion de seguridad de identidad (17 casos negativos y 1 positivo)</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Los 17 casos de la hoja '11 Casos de regresion' verdes por el Gateway, con asercion de codigo y de cuerpo, y el caso positivo con token obtenido de GoTrue, no firmado en CI.</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>Highest</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>TEC-09 (H-01), TEC-10 (H-02), TEC-11 (TLS)</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>CORE, DISPATCH</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>Total: 18 historias · 87 story points</t>
+      <c r="H24" s="26" t="inlineStr">
+        <is>
+          <t>TEC-10 (token real ES256)</t>
+        </is>
+      </c>
+      <c r="I24" s="26" t="inlineStr">
+        <is>
+          <t>CORE, DISPATCH, RULES</t>
+        </is>
+      </c>
+      <c r="J24" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="28" t="inlineStr">
         <is>
-          <t>VAL-19</t>
+          <t>VAL-20</t>
         </is>
       </c>
       <c r="B25" s="26" t="inlineStr">
         <is>
-          <t>M-03</t>
+          <t>M-04</t>
         </is>
       </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>Validar el contrato del perfil del aliado que consumen Dispatch y Rules</t>
+          <t>Validar que el catalogo responde solo las categorias y zonas del tenant del claim</t>
         </is>
       </c>
       <c r="D25" s="26" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Cliente / Aliado</t>
         </is>
       </c>
       <c r="E25" s="26" t="inlineStr">
         <is>
-          <t>Existe en codigo pero nunca se valido como contrato. Pedir el perfil del aliado por el Gateway con token real ES256 y comprobar: responde los campos que Dispatch y Rules declaran consumir, no expone documentos KYC ni datos de otro aliado, y con el token de un aliado del tenant B sobre un aliado del tenant A responde 403 o 404 y nunca 200 con datos. Video desde el front o, si no tiene pantalla, corrida Newman adjunta.</t>
+          <t>Implementado y sin validar. Consultar el catalogo por el Gateway con usuarios de dos tenants y comprobar que cada uno ve solo sus categorias activas, que una categoria desactivada no aparece, y que el tenant no se puede forzar por cuerpo ni por cabecera (se toma del claim, T4). El catalogo es pre-auth en nginx: comprobar tambien que sin token no filtra datos de ningun tenant.</t>
         </is>
       </c>
       <c r="F25" s="26" t="n">
@@ -13302,12 +13319,12 @@
       </c>
       <c r="H25" s="26" t="inlineStr">
         <is>
-          <t>TEC-10 (token real ES256)</t>
+          <t>TEC-10, TEC-16</t>
         </is>
       </c>
       <c r="I25" s="26" t="inlineStr">
         <is>
-          <t>CORE, DISPATCH, RULES</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="J25" s="26" t="inlineStr">
@@ -13319,27 +13336,27 @@
     <row r="26">
       <c r="A26" s="28" t="inlineStr">
         <is>
-          <t>VAL-20</t>
+          <t>VAL-21</t>
         </is>
       </c>
       <c r="B26" s="26" t="inlineStr">
         <is>
-          <t>M-04</t>
+          <t>M-05</t>
         </is>
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>Validar que el catalogo responde solo las categorias y zonas del tenant del claim</t>
+          <t>Validar el contexto de solicitud que Dispatch pide a Core</t>
         </is>
       </c>
       <c r="D26" s="26" t="inlineStr">
         <is>
-          <t>Cliente / Aliado</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="E26" s="26" t="inlineStr">
         <is>
-          <t>Implementado y sin validar. Consultar el catalogo por el Gateway con usuarios de dos tenants y comprobar que cada uno ve solo sus categorias activas, que una categoria desactivada no aparece, y que el tenant no se puede forzar por cuerpo ni por cabecera (se toma del claim, T4). El catalogo es pre-auth en nginx: comprobar tambien que sin token no filtra datos de ningun tenant.</t>
+          <t>Implementado y sin validar. Comprobar que Dispatch obtiene zona, categoria y estado de la solicitud por HTTP a Core y no por SQL sobre tablas de Core (T1), que si Core no responde Dispatch devuelve 503 y no arma el contexto con logica local (T2), y que el contexto de una solicitud del tenant A nunca se entrega con el token del tenant B.</t>
         </is>
       </c>
       <c r="F26" s="26" t="n">
@@ -13352,12 +13369,12 @@
       </c>
       <c r="H26" s="26" t="inlineStr">
         <is>
-          <t>TEC-10, TEC-16</t>
+          <t>TEC-02, TEC-10</t>
         </is>
       </c>
       <c r="I26" s="26" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>CORE, DISPATCH</t>
         </is>
       </c>
       <c r="J26" s="26" t="inlineStr">
@@ -13369,7 +13386,7 @@
     <row r="27">
       <c r="A27" s="28" t="inlineStr">
         <is>
-          <t>VAL-21</t>
+          <t>VAL-22</t>
         </is>
       </c>
       <c r="B27" s="26" t="inlineStr">
@@ -13379,7 +13396,7 @@
       </c>
       <c r="C27" s="26" t="inlineStr">
         <is>
-          <t>Validar el contexto de solicitud que Dispatch pide a Core</t>
+          <t>Validar idempotencia de la creacion de solicitud y del despacho bajo reintento</t>
         </is>
       </c>
       <c r="D27" s="26" t="inlineStr">
@@ -13389,20 +13406,20 @@
       </c>
       <c r="E27" s="26" t="inlineStr">
         <is>
-          <t>Implementado y sin validar. Comprobar que Dispatch obtiene zona, categoria y estado de la solicitud por HTTP a Core y no por SQL sobre tablas de Core (T1), que si Core no responde Dispatch devuelve 503 y no arma el contexto con logica local (T2), y que el contexto de una solicitud del tenant A nunca se entrega con el token del tenant B.</t>
+          <t>RNF-03 exige que las operaciones criticas resistan reintentos sin duplicar. Comprobar: reintento con la misma claveIdempotencia no crea una segunda solicitud; reintento de la orquestacion no duplica el broadcast; y tras un corte parcial del broadcast el reintento completa las ofertas que faltan en vez de congelarse, que es el defecto D-4. Requiere TEC-04 desplegado.</t>
         </is>
       </c>
       <c r="F27" s="26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G27" s="26" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Highest</t>
         </is>
       </c>
       <c r="H27" s="26" t="inlineStr">
         <is>
-          <t>TEC-02, TEC-10</t>
+          <t>TEC-04 (paginar y rehacer la guarda de idempotencia)</t>
         </is>
       </c>
       <c r="I27" s="26" t="inlineStr">
@@ -13411,56 +13428,6 @@
         </is>
       </c>
       <c r="J27" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="28" t="inlineStr">
-        <is>
-          <t>VAL-22</t>
-        </is>
-      </c>
-      <c r="B28" s="26" t="inlineStr">
-        <is>
-          <t>M-05</t>
-        </is>
-      </c>
-      <c r="C28" s="26" t="inlineStr">
-        <is>
-          <t>Validar idempotencia de la creacion de solicitud y del despacho bajo reintento</t>
-        </is>
-      </c>
-      <c r="D28" s="26" t="inlineStr">
-        <is>
-          <t>Sistema</t>
-        </is>
-      </c>
-      <c r="E28" s="26" t="inlineStr">
-        <is>
-          <t>RNF-03 exige que las operaciones criticas resistan reintentos sin duplicar. Comprobar: reintento con la misma claveIdempotencia no crea una segunda solicitud; reintento de la orquestacion no duplica el broadcast; y tras un corte parcial del broadcast el reintento completa las ofertas que faltan en vez de congelarse, que es el defecto D-4. Requiere TEC-04 desplegado.</t>
-        </is>
-      </c>
-      <c r="F28" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="G28" s="26" t="inlineStr">
-        <is>
-          <t>Highest</t>
-        </is>
-      </c>
-      <c r="H28" s="26" t="inlineStr">
-        <is>
-          <t>TEC-04 (paginar y rehacer la guarda de idempotencia)</t>
-        </is>
-      </c>
-      <c r="I28" s="26" t="inlineStr">
-        <is>
-          <t>CORE, DISPATCH</t>
-        </is>
-      </c>
-      <c r="J28" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -13481,7 +13448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13565,7 +13532,7 @@
     <row r="5" ht="52" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>CONS-01</t>
+          <t>CONS-04</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -13575,17 +13542,17 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Inicio de sesion separado por tipo de usuario</t>
+          <t>Recuperacion segura de contrasena</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Todos los roles</t>
+          <t>Cliente / Aliado</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Selector o rutas distintas por tipo (cliente PN, cliente empresa, aliado PN, aliado empresa, empleado directo, admin tenant, admin plataforma). El backend rechaza el cruce entre el tipo elegido y el rol del token. Mensaje de error que no revela si el correo existe.</t>
+          <t>Solicitud de recuperacion, correo con enlace de un solo uso y vigencia limitada, y cambio efectivo. No revela si el correo existe.</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
@@ -13593,12 +13560,12 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Highest</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>VAL-01</t>
+          <t>CONS-03</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -13611,7 +13578,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>CONS-02</t>
+          <t>CONS-05</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -13621,30 +13588,30 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Logout</t>
+          <t>Registro de cliente empresa</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Todos los roles</t>
+          <t>Cliente empresa</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Accion de salir disponible desde el menu superior en todas las pantallas, limpieza de token y de estado, y retorno al login del tipo correspondiente.</t>
+          <t>Alta de cuenta empresa con NIT y representante, separada de la administracion de sitios.</t>
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Highest</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>CONS-07 (menu superior)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -13657,7 +13624,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>CONS-03</t>
+          <t>CONS-06</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -13667,30 +13634,30 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Autenticacion consumida desde la API y retiro de Supabase directo en el cliente</t>
+          <t>Registro de empleado directo</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Admin de tenant</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>El cliente Flutter no usa .rpc(), .from() ni .storage.from(); todo pasa por el Gateway. Las interfaces de domain/repositories no cambian (ADR-0027).</t>
+          <t>Tercer tipo de aliado, creado por el tenant, con los documentos que su configuracion exige.</t>
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Highest</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>US-02.1.1-M3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -13703,27 +13670,27 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>CONS-04</t>
+          <t>CONS-08</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>M-02</t>
+          <t>M-13</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Recuperacion segura de contrasena</t>
+          <t>Pantalla de inicio por tipo de usuario</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Cliente / Aliado</t>
+          <t>Todos los roles</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Solicitud de recuperacion, correo con enlace de un solo uso y vigencia limitada, y cambio efectivo. No revela si el correo existe.</t>
+          <t>Inicio distinto por rol con los accesos y el resumen que cada uno necesita.</t>
         </is>
       </c>
       <c r="F8" s="3" t="n">
@@ -13736,7 +13703,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>CONS-03</t>
+          <t>CONS-07</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -13749,40 +13716,40 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>CONS-05</t>
+          <t>CONS-09</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>M-02</t>
+          <t>M-13</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Registro de cliente empresa</t>
+          <t>Enrutamiento por rol con guardas de sesion</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Cliente empresa</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Alta de cuenta empresa con NIT y representante, separada de la administracion de sitios.</t>
+          <t>Rutas protegidas por rol, redireccion al login ante 401 y bloqueo de rutas que no corresponden al rol.</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CONS-07</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -13795,17 +13762,17 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>CONS-06</t>
+          <t>CONS-14</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>M-02</t>
+          <t>M-04</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Registro de empleado directo</t>
+          <t>Activar y desactivar categoria sin afectar servicios en curso</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -13815,20 +13782,20 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Tercer tipo de aliado, creado por el tenant, con los documentos que su configuracion exige.</t>
+          <t>Al desactivar, la categoria deja de ofrecerse pero los servicios en curso continuan y se pueden cerrar.</t>
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VAL-09</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -13841,27 +13808,27 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>CONS-07</t>
+          <t>CONS-15</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>M-13</t>
+          <t>M-03</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Menu superior por rol con sesion visible</t>
+          <t>Aliado gestiona su disponibilidad y sus ausencias</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Todos los roles</t>
+          <t>Aliado</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Menu persistente con las entradas que corresponden al rol, nombre del usuario y del tenant visibles, y acceso a logout. Usable en movil (RNF-08).</t>
+          <t>Pantalla sobre la tabla aliado_ausencia ya migrada (008), sin solapamientos, y efecto inmediato en la elegibilidad.</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
@@ -13869,12 +13836,12 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Highest</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VAL-11</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -13887,40 +13854,40 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>CONS-08</t>
+          <t>CONS-16</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>M-13</t>
+          <t>M-03</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Pantalla de inicio por tipo de usuario</t>
+          <t>Cliente empresa administra multiples sitios de servicio</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Todos los roles</t>
+          <t>Cliente empresa</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Inicio distinto por rol con los accesos y el resumen que cada uno necesita.</t>
+          <t>Alta, edicion y baja de sitios, cada uno con zona obligatoria.</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>CONS-07</t>
+          <t>CONS-05</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -13933,40 +13900,40 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>CONS-09</t>
+          <t>CONS-17</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>M-13</t>
+          <t>M-03</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Enrutamiento por rol con guardas de sesion</t>
+          <t>Reglas contextuales del sitio visibles al aliado antes de programar</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Cliente / Aliado</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Rutas protegidas por rol, redireccion al login ante 401 y bloqueo de rutas que no corresponden al rol.</t>
+          <t>Reglas y condiciones del sitio mostradas en la oferta, antes de aceptar.</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>CONS-07</t>
+          <t>CONS-16</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -13979,45 +13946,45 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>CONS-10</t>
+          <t>CONS-18</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>M-13</t>
+          <t>M-05</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Dividir el front en modulos independientes por dominio</t>
+          <t>Orden del listado de aliados en el Rules Service</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Equipo de desarrollo</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Un feature por dominio, sin que profiles agrupe cobertura y verificacion ni services agrupe categorias y solicitudes. Sin cambios de comportamiento y con las pruebas existentes verdes.</t>
+          <t>Rules Service en Java con la regla del tenant (cobertura, calificacion o comision) y cliente HTTP en Dispatch que consume el orden. Cierra D-5. Incluye el repositorio, el Dockerfile, la ruta en el Gateway y el health.</t>
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Highest</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>P-1, TEC-15</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>RULES, DISPATCH</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr"/>
@@ -14025,31 +13992,31 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>CONS-11</t>
+          <t>CONS-19</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>M-13</t>
+          <t>M-05</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Dividir el Core por dominios internos</t>
+          <t>Priorizar solicitud por comision ofrecida</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Equipo de desarrollo</t>
+          <t>Cliente / Admin de tenant</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Dominios internos de identidad, directorio, catalogo, cobertura, disponibilidad, despacho y comunicacion, sin crear un servicio por CRUD (SAD §7.3, ADR-0022).</t>
+          <t>Criterio de comision dentro de la regla de ranking del tenant.</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -14058,12 +14025,12 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CONS-18</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>RULES</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr"/>
@@ -14071,27 +14038,27 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>CONS-12</t>
+          <t>CONS-20</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>M-04</t>
+          <t>M-05</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Barrios como nivel mas fino del catalogo de zonas</t>
+          <t>Cancelar solicitud antes de la ejecucion</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Admin de tenant</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Alta de barrios bajo la zona padre, cobertura declarable por barrio y resolucion por ancestro en la elegibilidad. No se introduce radio ni distancia (REST-01).</t>
+          <t>Cancelacion con motivo, estado final consistente y notificacion al aliado asignado. Respeta la decision de P-4 sobre el dueno del estado.</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
@@ -14104,12 +14071,12 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>VAL-07</t>
+          <t>P-4</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>CORE, DISPATCH</t>
+          <t>DISPATCH, CORE</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr"/>
@@ -14117,40 +14084,40 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>CONS-13</t>
+          <t>CONS-21</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>M-04</t>
+          <t>M-06</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Visualizacion en mapa de zonas, barrios y sitio de servicio</t>
+          <t>Cotizacion con mano de obra y materiales separados</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Cliente / Aliado</t>
+          <t>Aliado</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Mapa de solo lectura que ubica la zona, el barrio y el sitio. La seleccion sigue siendo por catalogo jerarquico, porque US-02.1.4-R1 retiro la seleccion libre en mapa.</t>
+          <t>Cotizacion con los dos renglones, total calculado y version persistida.</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>CONS-12</t>
+          <t>VAL-13</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -14163,31 +14130,31 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>CONS-14</t>
+          <t>CONS-22</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>M-04</t>
+          <t>M-06</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Activar y desactivar categoria sin afectar servicios en curso</t>
+          <t>Alerta de cotizacion fuera del rango del tarifario</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Admin de tenant</t>
+          <t>Aliado</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Al desactivar, la categoria deja de ofrecerse pero los servicios en curso continuan y se pueden cerrar.</t>
+          <t>Aviso bidireccional cuando el valor queda por encima o por debajo del rango del tenant, sin bloquear el envio.</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
@@ -14196,12 +14163,12 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>VAL-09</t>
+          <t>CONS-18, CONS-27</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>RULES</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr"/>
@@ -14209,40 +14176,40 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>CONS-15</t>
+          <t>CONS-23</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>M-03</t>
+          <t>M-06</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Aliado gestiona su disponibilidad y sus ausencias</t>
+          <t>Cliente acepta, rechaza o solicita ajuste de la cotizacion</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Aliado</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Pantalla sobre la tabla aliado_ausencia ya migrada (008), sin solapamientos, y efecto inmediato en la elegibilidad.</t>
+          <t>Las tres transiciones con su efecto en el estado del servicio y su notificacion.</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>VAL-11</t>
+          <t>CONS-21</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -14255,40 +14222,40 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>CONS-16</t>
+          <t>CONS-24</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>M-03</t>
+          <t>M-07</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Cliente empresa administra multiples sitios de servicio</t>
+          <t>Marcar inicio y fin de la ejecucion</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Cliente empresa</t>
+          <t>Aliado</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Alta, edicion y baja de sitios, cada uno con zona obligatoria.</t>
+          <t>Marcas con sello de tiempo del servidor y estado del servicio consistente.</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>CONS-05</t>
+          <t>CONS-23</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -14301,40 +14268,40 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>CONS-17</t>
+          <t>CONS-25</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>M-03</t>
+          <t>M-07</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Reglas contextuales del sitio visibles al aliado antes de programar</t>
+          <t>Registrar eventos y observaciones durante la ejecucion</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Cliente / Aliado</t>
+          <t>Aliado</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Reglas y condiciones del sitio mostradas en la oferta, antes de aceptar.</t>
+          <t>Bitacora cronologica inmutable con autor y sello de tiempo. Recupera la migracion 0012_evento_servicio_evidencia.sql que quedo sin fusionar.</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>CONS-16</t>
+          <t>CONS-24, TEC-08</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -14347,45 +14314,45 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>CONS-18</t>
+          <t>CONS-26</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>M-05</t>
+          <t>M-07</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Orden del listado de aliados en el Rules Service</t>
+          <t>Registrar evidencias sin conexion y sincronizarlas</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Aliado</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Rules Service en Java con la regla del tenant (cobertura, calificacion o comision) y cliente HTTP en Dispatch que consume el orden. Cierra D-5. Incluye el repositorio, el Dockerfile, la ruta en el Gateway y el health.</t>
+          <t>Captura en modo avion, cola local y sincronizacion idempotente al recuperar red, sin duplicar evidencias.</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Highest</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>P-1, TEC-15</t>
+          <t>CONS-25</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>RULES, DISPATCH</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr"/>
@@ -14393,27 +14360,27 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>CONS-19</t>
+          <t>CONS-27</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>M-05</t>
+          <t>M-10</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Priorizar solicitud por comision ofrecida</t>
+          <t>Cargar la tabla de tarifas por categoria</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Cliente / Admin de tenant</t>
+          <t>Admin de tenant</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Criterio de comision dentro de la regla de ranking del tenant.</t>
+          <t>Minimo, tipico y maximo por categoria y tenant, con validacion de orden de los tres valores.</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
@@ -14421,7 +14388,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -14431,7 +14398,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>RULES</t>
+          <t>RULES, CORE</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr"/>
@@ -14439,45 +14406,45 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>CONS-20</t>
+          <t>CONS-28</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>M-05</t>
+          <t>M-10</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Cancelar solicitud antes de la ejecucion</t>
+          <t>Ver la tarifa de referencia al cotizar</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Aliado</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Cancelacion con motivo, estado final consistente y notificacion al aliado asignado. Respeta la decision de P-4 sobre el dueno del estado.</t>
+          <t>Rango visible en la pantalla de cotizacion, resuelto por categoria y tenant.</t>
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>P-4</t>
+          <t>CONS-27</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>DISPATCH, CORE</t>
+          <t>RULES</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr"/>
@@ -14485,40 +14452,40 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>CONS-21</t>
+          <t>CONS-29</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>M-06</t>
+          <t>M-10</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Cotizacion con mano de obra y materiales separados</t>
+          <t>Reporte de cotizaciones fuera de rango por periodo</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Aliado</t>
+          <t>Admin de tenant</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Cotizacion con los dos renglones, total calculado y version persistida.</t>
+          <t>Consulta por periodo con exportacion, calculada sobre datos reales del tenant.</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>VAL-13</t>
+          <t>CONS-22</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -14531,31 +14498,31 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>CONS-22</t>
+          <t>CONS-30</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>M-06</t>
+          <t>M-08</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Alerta de cotizacion fuera del rango del tarifario</t>
+          <t>Calificacion bidireccional y cierre condicionado</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Aliado</t>
+          <t>Cliente / Aliado</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Aviso bidireccional cuando el valor queda por encima o por debajo del rango del tenant, sin bloquear el envio.</t>
+          <t>Ambas partes califican y el servicio no cierra hasta que las dos lo hayan hecho.</t>
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
@@ -14564,12 +14531,12 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>CONS-18, CONS-27</t>
+          <t>CONS-24</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>RULES</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr"/>
@@ -14577,17 +14544,17 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>CONS-23</t>
+          <t>CONS-31</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>M-06</t>
+          <t>M-08</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Cliente acepta, rechaza o solicita ajuste de la cotizacion</t>
+          <t>Calificacion agregada visible en el listado de aliados</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -14597,25 +14564,25 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Las tres transiciones con su efecto en el estado del servicio y su notificacion.</t>
+          <t>Promedio y conteo por aliado, usados tambien como criterio de orden.</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>CONS-21</t>
+          <t>CONS-30, CONS-18</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>CORE, RULES</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr"/>
@@ -14623,27 +14590,27 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>CONS-24</t>
+          <t>CONS-32</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>M-07</t>
+          <t>M-08</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Marcar inicio y fin de la ejecucion</t>
+          <t>Penalizacion por cancelacion tardia</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Aliado</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Marcas con sello de tiempo del servidor y estado del servicio consistente.</t>
+          <t>Regla configurable por tenant, aplicada segun el momento de la cancelacion.</t>
         </is>
       </c>
       <c r="F28" s="3" t="n">
@@ -14656,12 +14623,12 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>CONS-23</t>
+          <t>CONS-20, CONS-18</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>RULES</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr"/>
@@ -14669,40 +14636,40 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>CONS-25</t>
+          <t>CONS-33</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>M-07</t>
+          <t>M-08</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Registrar eventos y observaciones durante la ejecucion</t>
+          <t>Historial de servicios del cliente y de trabajos del aliado</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Aliado</t>
+          <t>Cliente / Aliado</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Bitacora cronologica inmutable con autor y sello de tiempo. Recupera la migracion 0012_evento_servicio_evidencia.sql que quedo sin fusionar.</t>
+          <t>Listados paginados por usuario y tenant con filtro por estado.</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>CONS-24, TEC-08</t>
+          <t>CONS-30</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -14715,27 +14682,27 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>CONS-26</t>
+          <t>CONS-34</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>M-07</t>
+          <t>M-09</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Registrar evidencias sin conexion y sincronizarlas</t>
+          <t>Mensajeria cliente-aliado por servicio</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Aliado</t>
+          <t>Cliente / Aliado</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Captura en modo avion, cola local y sincronizacion idempotente al recuperar red, sin duplicar evidencias.</t>
+          <t>Hilo por servicio, entrega casi en tiempo real cuando ambos estan conectados y persistencia del historial.</t>
         </is>
       </c>
       <c r="F30" s="3" t="n">
@@ -14748,7 +14715,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>CONS-25</t>
+          <t>VAL-13</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -14761,45 +14728,45 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>CONS-27</t>
+          <t>CONS-35</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>M-10</t>
+          <t>M-09</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Cargar la tabla de tarifas por categoria</t>
+          <t>Mock del proveedor de notificaciones push en el backend</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Admin de tenant</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Minimo, tipico y maximo por categoria y tenant, con validacion de orden de los tres valores.</t>
+          <t>Proveedor simulado detras de POST /notifications con bandeja consultable, para que el front exista sin FCM ni APNs reales. Conmutable por configuracion hacia el proveedor real (ADR-0014).</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Highest</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>CONS-18</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>RULES, CORE</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr"/>
@@ -14807,31 +14774,31 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>CONS-28</t>
+          <t>CONS-36</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>M-10</t>
+          <t>M-09</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Ver la tarifa de referencia al cotizar</t>
+          <t>Notificaciones de mensajes nuevos y del ciclo del servicio</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Aliado</t>
+          <t>Cliente / Aliado</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Rango visible en la pantalla de cotizacion, resuelto por categoria y tenant.</t>
+          <t>Notificacion cuando el destinatario no esta conectado, para mensajes y para los cuatro eventos del ciclo con el esquema v1 de ARQ-06.</t>
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
@@ -14840,12 +14807,12 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>CONS-27</t>
+          <t>CONS-34, CONS-35</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>RULES</t>
+          <t>CORE, DISPATCH</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr"/>
@@ -14853,17 +14820,17 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>CONS-29</t>
+          <t>CONS-37</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>M-10</t>
+          <t>M-09</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Reporte de cotizaciones fuera de rango por periodo</t>
+          <t>Consultar la conversacion para atender una queja</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -14873,7 +14840,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Consulta por periodo con exportacion, calculada sobre datos reales del tenant.</t>
+          <t>Acceso de solo lectura al hilo, acotado al tenant y registrado en auditoria.</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
@@ -14886,7 +14853,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>CONS-22</t>
+          <t>CONS-34</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -14899,27 +14866,27 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>CONS-30</t>
+          <t>CONS-38</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>M-08</t>
+          <t>M-11</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Calificacion bidireccional y cierre condicionado</t>
+          <t>Mock de la pasarela de pagos</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Cliente / Aliado</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Ambas partes califican y el servicio no cierra hasta que las dos lo hayan hecho.</t>
+          <t>Proveedor simulado con los tres desenlaces (aprobado, rechazado y pendiente), comprobante descargable de prueba y registro de la transaccion. Marcado como mock en la interfaz, sin datos reales de tarjeta y conmutable por configuracion.</t>
         </is>
       </c>
       <c r="F34" s="3" t="n">
@@ -14927,12 +14894,12 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Highest</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>CONS-24</t>
+          <t>CONS-23</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -14945,27 +14912,27 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>CONS-31</t>
+          <t>CONS-39</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>M-08</t>
+          <t>M-11</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Calificacion agregada visible en el listado de aliados</t>
+          <t>Registro inmutable de transacciones</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Promedio y conteo por aliado, usados tambien como criterio de orden.</t>
+          <t>Audit log de transacciones sin actualizacion ni borrado, con correlacion al servicio.</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
@@ -14978,12 +14945,12 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>CONS-30, CONS-18</t>
+          <t>CONS-38</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>CORE, RULES</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr"/>
@@ -14991,45 +14958,45 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>CONS-32</t>
+          <t>CONS-40</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>M-08</t>
+          <t>M-11</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Penalizacion por cancelacion tardia</t>
+          <t>Liquidacion al aliado con comision configurable</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Admin de tenant</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Regla configurable por tenant, aplicada segun el momento de la cancelacion.</t>
+          <t>Calculo con la comision del tenant y detalle consultable por el aliado.</t>
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>CONS-20, CONS-18</t>
+          <t>CONS-38, CONS-18</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>RULES</t>
+          <t>CORE, RULES</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr"/>
@@ -15037,31 +15004,31 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>CONS-33</t>
+          <t>CONS-41</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>M-08</t>
+          <t>M-12</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Historial de servicios del cliente y de trabajos del aliado</t>
+          <t>Registro y gestion de quejas</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Cliente / Aliado</t>
+          <t>Cliente / Admin de tenant</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Listados paginados por usuario y tenant con filtro por estado.</t>
+          <t>Alta de la queja asociada al servicio y workflow de estados del tenant.</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -15083,31 +15050,31 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>CONS-34</t>
+          <t>CONS-42</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>M-09</t>
+          <t>M-12</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Mensajeria cliente-aliado por servicio</t>
+          <t>Metricas operativas por tenant y endpoint /metrics</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Cliente / Aliado</t>
+          <t>Admin de tenant / plataforma</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Hilo por servicio, entrega casi en tiempo real cuando ambos estan conectados y persistencia del historial.</t>
+          <t>Metricas de operacion por tenant y exposicion tecnica de /metrics con alertas minimas, que hoy no existen (SCRUM-1266 H-05).</t>
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
@@ -15116,7 +15083,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>VAL-13</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
@@ -15129,35 +15096,35 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>CONS-35</t>
+          <t>CONS-43</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>M-09</t>
+          <t>M-12</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Mock del proveedor de notificaciones push en el backend</t>
+          <t>Administrar el estado de los tenants</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Admin de plataforma</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Proveedor simulado detras de POST /notifications con bandeja consultable, para que el front exista sin FCM ni APNs reales. Conmutable por configuracion hacia el proveedor real (ADR-0014).</t>
+          <t>Activar, suspender y reactivar un tenant, con efecto inmediato en el acceso de sus usuarios.</t>
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>Highest</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
@@ -15175,27 +15142,27 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>CONS-36</t>
+          <t>CONS-44</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>M-09</t>
+          <t>M-01</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones de mensajes nuevos y del ciclo del servicio</t>
+          <t>Configuracion de reglas por tenant sin despliegue</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Cliente / Aliado</t>
+          <t>Admin de tenant</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Notificacion cuando el destinatario no esta conectado, para mensajes y para los cuatro eventos del ciclo con el esquema v1 de ARQ-06.</t>
+          <t>Documentos exigidos por tipo de aliado, orden del listado, categorias y tarifas configurables desde la consola, sin desplegar codigo (RNF-02, RNF-10).</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
@@ -15203,492 +15170,85 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>CONS-34, CONS-35</t>
+          <t>CONS-18</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>CORE, DISPATCH</t>
+          <t>RULES, CORE</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr"/>
     </row>
-    <row r="41" ht="40" customHeight="1">
-      <c r="A41" s="13" t="inlineStr">
-        <is>
-          <t>CONS-37</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>M-09</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>Consultar la conversacion para atender una queja</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>Admin de tenant</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>Acceso de solo lectura al hilo, acotado al tenant y registrado en auditoria.</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>CONS-34</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
+    <row r="41" ht="40" customHeight="1"/>
+    <row r="42" ht="52" customHeight="1">
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>Total: 45 historias · 269 story points</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="40" customHeight="1">
+      <c r="A43" s="28" t="inlineStr">
+        <is>
+          <t>CONS-46</t>
+        </is>
+      </c>
+      <c r="B43" s="26" t="inlineStr">
+        <is>
+          <t>M-01</t>
+        </is>
+      </c>
+      <c r="C43" s="26" t="inlineStr">
+        <is>
+          <t>Alta y administracion de tenants por el administrador de plataforma</t>
+        </is>
+      </c>
+      <c r="D43" s="26" t="inlineStr">
+        <is>
+          <t>Admin de plataforma</t>
+        </is>
+      </c>
+      <c r="E43" s="26" t="inlineStr">
+        <is>
+          <t>RF-01 es critico y hoy solo existe GET /api/v1/core/tenants: no hay forma de crear un tenant por la aplicacion. End to end desde cero: pantalla de administracion de plataforma, alta del tenant con su slug y sus datos, edicion, y consulta del listado. El alta crea el tenant aislado: sus tablas nacen con tenant_id y su politica por tenant en la misma migracion (T3). Solo el administrador de plataforma puede crear tenants; un admin de tenant que lo intente recibe 403. Queda registrado quien lo creo, cuando y con que correlationId (T10). No incluye el estado del tenant, que es CONS-43.</t>
+        </is>
+      </c>
+      <c r="F43" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="G43" s="26" t="inlineStr">
+        <is>
+          <t>Highest</t>
+        </is>
+      </c>
+      <c r="H43" s="26" t="inlineStr">
+        <is>
+          <t>CONS-07 (shell), TEC-10</t>
+        </is>
+      </c>
+      <c r="I43" s="26" t="inlineStr">
         <is>
           <t>CORE</t>
         </is>
       </c>
-      <c r="J41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42" ht="52" customHeight="1">
-      <c r="A42" s="13" t="inlineStr">
-        <is>
-          <t>CONS-38</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>M-11</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>Mock de la pasarela de pagos</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>Proveedor simulado con los tres desenlaces (aprobado, rechazado y pendiente), comprobante descargable de prueba y registro de la transaccion. Marcado como mock en la interfaz, sin datos reales de tarjeta y conmutable por configuracion.</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t>Highest</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>CONS-23</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>CORE</t>
-        </is>
-      </c>
-      <c r="J42" s="3" t="inlineStr"/>
-    </row>
-    <row r="43" ht="40" customHeight="1">
-      <c r="A43" s="13" t="inlineStr">
-        <is>
-          <t>CONS-39</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>M-11</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>Registro inmutable de transacciones</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>Sistema</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>Audit log de transacciones sin actualizacion ni borrado, con correlacion al servicio.</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>CONS-38</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>CORE</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr"/>
-    </row>
-    <row r="44" ht="40" customHeight="1">
-      <c r="A44" s="13" t="inlineStr">
-        <is>
-          <t>CONS-40</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>M-11</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>Liquidacion al aliado con comision configurable</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>Admin de tenant</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>Calculo con la comision del tenant y detalle consultable por el aliado.</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>CONS-38, CONS-18</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>CORE, RULES</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr"/>
-    </row>
-    <row r="45" ht="40" customHeight="1">
-      <c r="A45" s="13" t="inlineStr">
-        <is>
-          <t>CONS-41</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>M-12</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>Registro y gestion de quejas</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>Cliente / Admin de tenant</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>Alta de la queja asociada al servicio y workflow de estados del tenant.</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>CONS-30</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>CORE</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="inlineStr"/>
-    </row>
-    <row r="46" ht="40" customHeight="1">
-      <c r="A46" s="13" t="inlineStr">
-        <is>
-          <t>CONS-42</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>M-12</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>Metricas operativas por tenant y endpoint /metrics</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>Admin de tenant / plataforma</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>Metricas de operacion por tenant y exposicion tecnica de /metrics con alertas minimas, que hoy no existen (SCRUM-1266 H-05).</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
+      <c r="J43" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t>CORE</t>
-        </is>
-      </c>
-      <c r="J46" s="3" t="inlineStr"/>
-    </row>
-    <row r="47" ht="40" customHeight="1">
-      <c r="A47" s="13" t="inlineStr">
-        <is>
-          <t>CONS-43</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>M-12</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>Administrar el estado de los tenants</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>Admin de plataforma</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>Activar, suspender y reactivar un tenant, con efecto inmediato en el acceso de sus usuarios.</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>CORE</t>
-        </is>
-      </c>
-      <c r="J47" s="3" t="inlineStr"/>
-    </row>
-    <row r="48" ht="40" customHeight="1">
-      <c r="A48" s="13" t="inlineStr">
-        <is>
-          <t>CONS-44</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>M-01</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>Configuracion de reglas por tenant sin despliegue</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>Admin de tenant</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>Documentos exigidos por tipo de aliado, orden del listado, categorias y tarifas configurables desde la consola, sin desplegar codigo (RNF-02, RNF-10).</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G48" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>CONS-18</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t>RULES, CORE</t>
-        </is>
-      </c>
-      <c r="J48" s="3" t="inlineStr"/>
-    </row>
-    <row r="49" ht="40" customHeight="1">
-      <c r="A49" s="13" t="inlineStr">
-        <is>
-          <t>CONS-45</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>M-02</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>Cifrado y manejo de secretos verificado de punta a punta</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>Sistema</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>TLS en el borde con redireccion 80 a 443, cifrado en reposo del KYC, prohibicion de registrar credenciales en logs y secretos fuera del control de versiones.</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>Highest</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>TEC-11, TEC-09</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>CORE</t>
-        </is>
-      </c>
-      <c r="J49" s="3" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="C51" s="12" t="inlineStr">
-        <is>
-          <t>Total: 45 historias · 269 story points</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="28" t="inlineStr">
-        <is>
-          <t>CONS-46</t>
-        </is>
-      </c>
-      <c r="B52" s="26" t="inlineStr">
-        <is>
-          <t>M-01</t>
-        </is>
-      </c>
-      <c r="C52" s="26" t="inlineStr">
-        <is>
-          <t>Alta y administracion de tenants por el administrador de plataforma</t>
-        </is>
-      </c>
-      <c r="D52" s="26" t="inlineStr">
-        <is>
-          <t>Admin de plataforma</t>
-        </is>
-      </c>
-      <c r="E52" s="26" t="inlineStr">
-        <is>
-          <t>RF-01 es critico y hoy solo existe GET /api/v1/core/tenants: no hay forma de crear un tenant por la aplicacion. End to end desde cero: pantalla de administracion de plataforma, alta del tenant con su slug y sus datos, edicion, y consulta del listado. El alta crea el tenant aislado: sus tablas nacen con tenant_id y su politica por tenant en la misma migracion (T3). Solo el administrador de plataforma puede crear tenants; un admin de tenant que lo intente recibe 403. Queda registrado quien lo creo, cuando y con que correlationId (T10). No incluye el estado del tenant, que es CONS-43.</t>
-        </is>
-      </c>
-      <c r="F52" s="26" t="n">
-        <v>8</v>
-      </c>
-      <c r="G52" s="26" t="inlineStr">
-        <is>
-          <t>Highest</t>
-        </is>
-      </c>
-      <c r="H52" s="26" t="inlineStr">
-        <is>
-          <t>CONS-07 (shell), TEC-10</t>
-        </is>
-      </c>
-      <c r="I52" s="26" t="inlineStr">
-        <is>
-          <t>CORE</t>
-        </is>
-      </c>
-      <c r="J52" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="44" ht="40" customHeight="1"/>
+    <row r="45" ht="40" customHeight="1"/>
+    <row r="46" ht="40" customHeight="1"/>
+    <row r="47" ht="40" customHeight="1"/>
+    <row r="48" ht="40" customHeight="1"/>
+    <row r="49" ht="40" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
@@ -24882,2518 +24442,5359 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E95"/>
+  <dimension ref="A1:L92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="54" customWidth="1" min="4" max="4"/>
-    <col width="104" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="46" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="inlineStr">
         <is>
-          <t>Una subtarea de QA por historia: revisar y cerrar en Done</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="78" customHeight="1">
+          <t>Sprint 5 · Una historia por funcionalidad, un modulo por persona</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="100" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>Acuerdo del 24-oct-2026: ninguna historia pasa a Done por si misma. Cada una lleva una subtarea de Santiago (QA) que revisa la evidencia contra los criterios de la historia y es quien la mueve a Done. QA decide el DoD (GOBIERNO_DEL_EQUIPO.md §2.3), asi que la subtarea es el punto de control: si la evidencia no cumple, la historia vuelve y no se cierra. Esto cierra el hueco del Sprint 4, donde 14 subtareas de QA existian pero tres historias (SCRUM-1063, 1066 y 1068) no tenian ninguna, pendiente PE4 de §6.5 del backlog.</t>
+          <t>Una historia por cada funcionalidad del libro. Reparto por modulo completo y no por tarea, para que entre desarrolladores no haya tareas que se bloqueen: cada quien es dueno de sus modulos de punta a punta y las dependencias que quedan son de ambiente, concentradas en el bloque TEC. Quienes no programamos (Camila, Daniel, Santiago y Sara) llevamos un modulo cada uno, de validacion y verificacion; Daniel se ofrecio a llevar dos, M-01 y M-02. Trece historias de esos cinco modulos exigen codigo, asi que las ejecuta un desarrollador y el dueno del modulo las valida y acepta: son las unicas filas donde las dos columnas de persona no coinciden. Notificaciones (M-09) y pagos (M-11) entran como front contra mock, sin integracion real con el proveedor, porque el front tiene que existir completo. La visualizacion en mapa entra si o si. Cada historia lleva su subtarea de QA: Santiago revisa y es quien cierra en Done.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
-          <t>Subtarea</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="B4" s="25" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Func.</t>
         </is>
       </c>
       <c r="C4" s="25" t="inlineStr">
         <is>
-          <t>Bloque</t>
+          <t>Modulo</t>
         </is>
       </c>
       <c r="D4" s="25" t="inlineStr">
         <is>
-          <t>Titulo de la historia</t>
+          <t>Funcionalidad</t>
         </is>
       </c>
       <c r="E4" s="25" t="inlineStr">
         <is>
-          <t>Que revisa y cierra QA</t>
+          <t>RF / RNF</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="inlineStr">
+        <is>
+          <t>Tipo de trabajo</t>
+        </is>
+      </c>
+      <c r="G4" s="25" t="inlineStr">
+        <is>
+          <t>Estado hoy</t>
+        </is>
+      </c>
+      <c r="H4" s="25" t="inlineStr">
+        <is>
+          <t>Quien la ejecuta</t>
+        </is>
+      </c>
+      <c r="I4" s="25" t="inlineStr">
+        <is>
+          <t>Dueno del modulo (valida y acepta)</t>
+        </is>
+      </c>
+      <c r="J4" s="25" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K4" s="25" t="inlineStr">
+        <is>
+          <t>En el Sprint 5</t>
+        </is>
+      </c>
+      <c r="L4" s="25" t="inlineStr">
+        <is>
+          <t>Subtarea de QA</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="inlineStr">
-        <is>
-          <t>QA-VAL-01</t>
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>HU-M01-01</t>
         </is>
       </c>
       <c r="B5" s="26" t="inlineStr">
         <is>
-          <t>VAL-01</t>
+          <t>M-01.1</t>
         </is>
       </c>
       <c r="C5" s="26" t="inlineStr">
         <is>
-          <t>Validacion</t>
+          <t>M-01</t>
         </is>
       </c>
       <c r="D5" s="26" t="inlineStr">
         <is>
-          <t>Validar inicio de sesion con token real ES256 de extremo a extremo</t>
+          <t>Registrar y administrar empresas (tenants)</t>
         </is>
       </c>
       <c r="E5" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+          <t>RF-01</t>
+        </is>
+      </c>
+      <c r="F5" s="26" t="inlineStr">
+        <is>
+          <t>Correccion + validacion</t>
+        </is>
+      </c>
+      <c r="G5" s="26" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H5" s="26" t="inlineStr">
+        <is>
+          <t>Daniel Avila</t>
+        </is>
+      </c>
+      <c r="I5" s="26" t="inlineStr">
+        <is>
+          <t>Daniel Avila</t>
+        </is>
+      </c>
+      <c r="J5" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L5" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M01-01</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="28" t="inlineStr">
-        <is>
-          <t>QA-VAL-02</t>
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>HU-M01-02</t>
         </is>
       </c>
       <c r="B6" s="26" t="inlineStr">
         <is>
-          <t>VAL-02</t>
+          <t>M-01.2</t>
         </is>
       </c>
       <c r="C6" s="26" t="inlineStr">
         <is>
-          <t>Validacion</t>
+          <t>M-01</t>
         </is>
       </c>
       <c r="D6" s="26" t="inlineStr">
         <is>
-          <t>Validar registro de aliado persona natural por el camino Gateway-Core</t>
+          <t>Aislamiento estricto de datos y archivos por tenant</t>
         </is>
       </c>
       <c r="E6" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+          <t>RNF-01 / REST-04</t>
+        </is>
+      </c>
+      <c r="F6" s="26" t="inlineStr">
+        <is>
+          <t>Correccion + validacion</t>
+        </is>
+      </c>
+      <c r="G6" s="26" t="inlineStr">
+        <is>
+          <t>Parcial con defecto abierto</t>
+        </is>
+      </c>
+      <c r="H6" s="26" t="inlineStr">
+        <is>
+          <t>Daniel Avila</t>
+        </is>
+      </c>
+      <c r="I6" s="26" t="inlineStr">
+        <is>
+          <t>Daniel Avila</t>
+        </is>
+      </c>
+      <c r="J6" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L6" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M01-02</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="28" t="inlineStr">
-        <is>
-          <t>QA-VAL-03</t>
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>HU-M01-03</t>
         </is>
       </c>
       <c r="B7" s="26" t="inlineStr">
         <is>
-          <t>VAL-03</t>
+          <t>M-01.3</t>
         </is>
       </c>
       <c r="C7" s="26" t="inlineStr">
         <is>
-          <t>Validacion</t>
+          <t>M-01</t>
         </is>
       </c>
       <c r="D7" s="26" t="inlineStr">
         <is>
-          <t>Validar registro de aliado empresa</t>
+          <t>Configurar reglas operativas propias por tenant</t>
         </is>
       </c>
       <c r="E7" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+          <t>RF-02 / RNF-02 / RNF-10 / REST-05</t>
+        </is>
+      </c>
+      <c r="F7" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G7" s="26" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H7" s="33" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="I7" s="26" t="inlineStr">
+        <is>
+          <t>Daniel Avila</t>
+        </is>
+      </c>
+      <c r="J7" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K7" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L7" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M01-03</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="28" t="inlineStr">
-        <is>
-          <t>QA-VAL-04</t>
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>HU-M01-04</t>
         </is>
       </c>
       <c r="B8" s="26" t="inlineStr">
         <is>
-          <t>VAL-04</t>
+          <t>M-01.4</t>
         </is>
       </c>
       <c r="C8" s="26" t="inlineStr">
         <is>
-          <t>Validacion</t>
+          <t>M-01</t>
         </is>
       </c>
       <c r="D8" s="26" t="inlineStr">
         <is>
-          <t>Validar registro de cliente persona natural</t>
+          <t>Identificacion de tenant no falsificable (claim obligatorio)</t>
         </is>
       </c>
       <c r="E8" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+          <t>RNF-01 / ADR-0018</t>
+        </is>
+      </c>
+      <c r="F8" s="26" t="inlineStr">
+        <is>
+          <t>Correccion + validacion</t>
+        </is>
+      </c>
+      <c r="G8" s="26" t="inlineStr">
+        <is>
+          <t>Implementado con defecto abierto</t>
+        </is>
+      </c>
+      <c r="H8" s="26" t="inlineStr">
+        <is>
+          <t>Daniel Avila</t>
+        </is>
+      </c>
+      <c r="I8" s="26" t="inlineStr">
+        <is>
+          <t>Daniel Avila</t>
+        </is>
+      </c>
+      <c r="J8" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L8" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M01-04</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="28" t="inlineStr">
         <is>
-          <t>QA-VAL-05</t>
+          <t>HU-M01-05</t>
         </is>
       </c>
       <c r="B9" s="26" t="inlineStr">
         <is>
-          <t>VAL-05</t>
+          <t>M-01.5</t>
         </is>
       </c>
       <c r="C9" s="26" t="inlineStr">
         <is>
-          <t>Validacion</t>
+          <t>M-01</t>
         </is>
       </c>
       <c r="D9" s="26" t="inlineStr">
         <is>
-          <t>Validar edicion del perfil propio</t>
+          <t>Propiedad del esquema y de las migraciones en un solo servicio</t>
         </is>
       </c>
       <c r="E9" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+          <t>ADR-0030 §1</t>
+        </is>
+      </c>
+      <c r="F9" s="26" t="inlineStr">
+        <is>
+          <t>Validacion de lo implementado</t>
+        </is>
+      </c>
+      <c r="G9" s="26" t="inlineStr">
+        <is>
+          <t>Conforme</t>
+        </is>
+      </c>
+      <c r="H9" s="26" t="inlineStr">
+        <is>
+          <t>Daniel Avila</t>
+        </is>
+      </c>
+      <c r="I9" s="26" t="inlineStr">
+        <is>
+          <t>Daniel Avila</t>
+        </is>
+      </c>
+      <c r="J9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L9" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M01-05</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="28" t="inlineStr">
         <is>
-          <t>QA-VAL-06</t>
+          <t>HU-M02-01</t>
         </is>
       </c>
       <c r="B10" s="26" t="inlineStr">
         <is>
-          <t>VAL-06</t>
+          <t>M-02.1</t>
         </is>
       </c>
       <c r="C10" s="26" t="inlineStr">
         <is>
-          <t>Validacion</t>
+          <t>M-02</t>
         </is>
       </c>
       <c r="D10" s="26" t="inlineStr">
         <is>
-          <t>Validar aprobacion y rechazo de aliado en la bandeja de verificacion</t>
+          <t>Inicio de sesion</t>
         </is>
       </c>
       <c r="E10" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+          <t>RF-03</t>
+        </is>
+      </c>
+      <c r="F10" s="26" t="inlineStr">
+        <is>
+          <t>Validacion de lo implementado</t>
+        </is>
+      </c>
+      <c r="G10" s="26" t="inlineStr">
+        <is>
+          <t>Implementado (solo HS256)</t>
+        </is>
+      </c>
+      <c r="H10" s="26" t="inlineStr">
+        <is>
+          <t>Daniel Avila</t>
+        </is>
+      </c>
+      <c r="I10" s="26" t="inlineStr">
+        <is>
+          <t>Daniel Avila</t>
+        </is>
+      </c>
+      <c r="J10" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L10" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M02-01</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="inlineStr">
-        <is>
-          <t>QA-VAL-07</t>
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>HU-M02-02</t>
         </is>
       </c>
       <c r="B11" s="26" t="inlineStr">
         <is>
-          <t>VAL-07</t>
+          <t>M-02.2</t>
         </is>
       </c>
       <c r="C11" s="26" t="inlineStr">
         <is>
-          <t>Validacion</t>
+          <t>M-02</t>
         </is>
       </c>
       <c r="D11" s="26" t="inlineStr">
         <is>
-          <t>Validar declaracion de cobertura por zonas del aliado</t>
+          <t>Inicio de sesion separado por tipo de usuario</t>
         </is>
       </c>
       <c r="E11" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+          <t>RF-03</t>
+        </is>
+      </c>
+      <c r="F11" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G11" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H11" s="33" t="inlineStr">
+        <is>
+          <t>Nicolas Leon</t>
+        </is>
+      </c>
+      <c r="I11" s="26" t="inlineStr">
+        <is>
+          <t>Daniel Avila</t>
+        </is>
+      </c>
+      <c r="J11" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L11" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M02-02</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="28" t="inlineStr">
-        <is>
-          <t>QA-VAL-08</t>
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>HU-M02-03</t>
         </is>
       </c>
       <c r="B12" s="26" t="inlineStr">
         <is>
-          <t>VAL-08</t>
+          <t>M-02.3</t>
         </is>
       </c>
       <c r="C12" s="26" t="inlineStr">
         <is>
-          <t>Validacion</t>
+          <t>M-02</t>
         </is>
       </c>
       <c r="D12" s="26" t="inlineStr">
         <is>
-          <t>Validar que el aliado declara las categorias que atiende</t>
+          <t>Logout</t>
         </is>
       </c>
       <c r="E12" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+          <t>RF-03</t>
+        </is>
+      </c>
+      <c r="F12" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G12" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H12" s="33" t="inlineStr">
+        <is>
+          <t>Nicolas Leon</t>
+        </is>
+      </c>
+      <c r="I12" s="26" t="inlineStr">
+        <is>
+          <t>Daniel Avila</t>
+        </is>
+      </c>
+      <c r="J12" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L12" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M02-03</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="28" t="inlineStr">
         <is>
-          <t>QA-VAL-09</t>
+          <t>HU-M02-04</t>
         </is>
       </c>
       <c r="B13" s="26" t="inlineStr">
         <is>
-          <t>VAL-09</t>
+          <t>M-02.4</t>
         </is>
       </c>
       <c r="C13" s="26" t="inlineStr">
         <is>
-          <t>Validacion</t>
+          <t>M-02</t>
         </is>
       </c>
       <c r="D13" s="26" t="inlineStr">
         <is>
-          <t>Validar gestion de categorias del tenant</t>
+          <t>Registro de aliado persona natural con documentos KYC</t>
         </is>
       </c>
       <c r="E13" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+          <t>RF-05</t>
+        </is>
+      </c>
+      <c r="F13" s="26" t="inlineStr">
+        <is>
+          <t>Validacion de lo implementado</t>
+        </is>
+      </c>
+      <c r="G13" s="26" t="inlineStr">
+        <is>
+          <t>Done sin validar en arquitectura vigente</t>
+        </is>
+      </c>
+      <c r="H13" s="26" t="inlineStr">
+        <is>
+          <t>Daniel Avila</t>
+        </is>
+      </c>
+      <c r="I13" s="26" t="inlineStr">
+        <is>
+          <t>Daniel Avila</t>
+        </is>
+      </c>
+      <c r="J13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L13" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M02-04</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="28" t="inlineStr">
         <is>
-          <t>QA-VAL-10</t>
+          <t>HU-M02-05</t>
         </is>
       </c>
       <c r="B14" s="26" t="inlineStr">
         <is>
-          <t>VAL-10</t>
+          <t>M-02.5</t>
         </is>
       </c>
       <c r="C14" s="26" t="inlineStr">
         <is>
-          <t>Validacion</t>
+          <t>M-02</t>
         </is>
       </c>
       <c r="D14" s="26" t="inlineStr">
         <is>
-          <t>Validar creacion de la solicitud en Core desde el front</t>
+          <t>Registro de aliado empresa</t>
         </is>
       </c>
       <c r="E14" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+          <t>RF-05</t>
+        </is>
+      </c>
+      <c r="F14" s="26" t="inlineStr">
+        <is>
+          <t>Validacion de lo implementado</t>
+        </is>
+      </c>
+      <c r="G14" s="26" t="inlineStr">
+        <is>
+          <t>Done sin validar en arquitectura vigente</t>
+        </is>
+      </c>
+      <c r="H14" s="26" t="inlineStr">
+        <is>
+          <t>Daniel Avila</t>
+        </is>
+      </c>
+      <c r="I14" s="26" t="inlineStr">
+        <is>
+          <t>Daniel Avila</t>
+        </is>
+      </c>
+      <c r="J14" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L14" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M02-05</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="28" t="inlineStr">
         <is>
-          <t>QA-VAL-11</t>
+          <t>HU-M02-06</t>
         </is>
       </c>
       <c r="B15" s="26" t="inlineStr">
         <is>
-          <t>VAL-11</t>
+          <t>M-02.6</t>
         </is>
       </c>
       <c r="C15" s="26" t="inlineStr">
         <is>
-          <t>Validacion</t>
+          <t>M-02</t>
         </is>
       </c>
       <c r="D15" s="26" t="inlineStr">
         <is>
-          <t>Validar elegibilidad de aliados por categoria, zona, disponibilidad y rechazo previo</t>
+          <t>Registro de cliente persona natural</t>
         </is>
       </c>
       <c r="E15" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+          <t>RF-08</t>
+        </is>
+      </c>
+      <c r="F15" s="26" t="inlineStr">
+        <is>
+          <t>Validacion de lo implementado</t>
+        </is>
+      </c>
+      <c r="G15" s="26" t="inlineStr">
+        <is>
+          <t>Done sin validar en arquitectura vigente</t>
+        </is>
+      </c>
+      <c r="H15" s="26" t="inlineStr">
+        <is>
+          <t>Daniel Avila</t>
+        </is>
+      </c>
+      <c r="I15" s="26" t="inlineStr">
+        <is>
+          <t>Daniel Avila</t>
+        </is>
+      </c>
+      <c r="J15" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L15" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M02-06</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="28" t="inlineStr">
-        <is>
-          <t>QA-VAL-12</t>
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>HU-M02-07</t>
         </is>
       </c>
       <c r="B16" s="26" t="inlineStr">
         <is>
-          <t>VAL-12</t>
+          <t>M-02.7</t>
         </is>
       </c>
       <c r="C16" s="26" t="inlineStr">
         <is>
-          <t>Validacion</t>
+          <t>M-02</t>
         </is>
       </c>
       <c r="D16" s="26" t="inlineStr">
         <is>
-          <t>Validar filtro por tipo de aliado</t>
+          <t>Registro de cliente empresa</t>
         </is>
       </c>
       <c r="E16" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+          <t>RF-08</t>
+        </is>
+      </c>
+      <c r="F16" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G16" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H16" s="33" t="inlineStr">
+        <is>
+          <t>Nicolas Leon</t>
+        </is>
+      </c>
+      <c r="I16" s="26" t="inlineStr">
+        <is>
+          <t>Daniel Avila</t>
+        </is>
+      </c>
+      <c r="J16" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K16" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L16" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M02-07</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="28" t="inlineStr">
-        <is>
-          <t>QA-VAL-13</t>
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>HU-M02-08</t>
         </is>
       </c>
       <c r="B17" s="26" t="inlineStr">
         <is>
-          <t>VAL-13</t>
+          <t>M-02.8</t>
         </is>
       </c>
       <c r="C17" s="26" t="inlineStr">
         <is>
-          <t>Validacion</t>
+          <t>M-02</t>
         </is>
       </c>
       <c r="D17" s="26" t="inlineStr">
         <is>
-          <t>Validar aceptacion sin doble asignacion con dos aliados simultaneos</t>
+          <t>Registro de empleado directo</t>
         </is>
       </c>
       <c r="E17" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+          <t>RF-05</t>
+        </is>
+      </c>
+      <c r="F17" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G17" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H17" s="33" t="inlineStr">
+        <is>
+          <t>Nicolas Leon</t>
+        </is>
+      </c>
+      <c r="I17" s="26" t="inlineStr">
+        <is>
+          <t>Daniel Avila</t>
+        </is>
+      </c>
+      <c r="J17" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K17" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L17" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M02-08</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="28" t="inlineStr">
-        <is>
-          <t>QA-VAL-14</t>
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>HU-M02-09</t>
         </is>
       </c>
       <c r="B18" s="26" t="inlineStr">
         <is>
-          <t>VAL-14</t>
+          <t>M-02.9</t>
         </is>
       </c>
       <c r="C18" s="26" t="inlineStr">
         <is>
-          <t>Validacion</t>
+          <t>M-02</t>
         </is>
       </c>
       <c r="D18" s="26" t="inlineStr">
         <is>
-          <t>Validar rechazo de oferta</t>
+          <t>Edicion del perfil propio</t>
         </is>
       </c>
       <c r="E18" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+          <t>RF-30 / RF-05 / RF-08</t>
+        </is>
+      </c>
+      <c r="F18" s="26" t="inlineStr">
+        <is>
+          <t>Terminar + validacion</t>
+        </is>
+      </c>
+      <c r="G18" s="26" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="H18" s="26" t="inlineStr">
+        <is>
+          <t>Daniel Avila</t>
+        </is>
+      </c>
+      <c r="I18" s="26" t="inlineStr">
+        <is>
+          <t>Daniel Avila</t>
+        </is>
+      </c>
+      <c r="J18" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K18" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L18" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M02-09</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="28" t="inlineStr">
-        <is>
-          <t>QA-VAL-15</t>
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>HU-M02-10</t>
         </is>
       </c>
       <c r="B19" s="26" t="inlineStr">
         <is>
-          <t>VAL-15</t>
+          <t>M-02.10</t>
         </is>
       </c>
       <c r="C19" s="26" t="inlineStr">
         <is>
-          <t>Validacion</t>
+          <t>M-02</t>
         </is>
       </c>
       <c r="D19" s="26" t="inlineStr">
         <is>
-          <t>Validar broadcast de ofertas y notificacion por la frontera de Core</t>
+          <t>Recuperacion segura de contrasena</t>
         </is>
       </c>
       <c r="E19" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+          <t>RF-04</t>
+        </is>
+      </c>
+      <c r="F19" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G19" s="26" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H19" s="33" t="inlineStr">
+        <is>
+          <t>Nicolas Leon</t>
+        </is>
+      </c>
+      <c r="I19" s="26" t="inlineStr">
+        <is>
+          <t>Daniel Avila</t>
+        </is>
+      </c>
+      <c r="J19" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L19" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M02-10</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="28" t="inlineStr">
-        <is>
-          <t>QA-VAL-16</t>
+      <c r="A20" s="29" t="inlineStr">
+        <is>
+          <t>HU-M02-11</t>
         </is>
       </c>
       <c r="B20" s="26" t="inlineStr">
         <is>
-          <t>VAL-16</t>
+          <t>M-02.11</t>
         </is>
       </c>
       <c r="C20" s="26" t="inlineStr">
         <is>
-          <t>Validacion</t>
+          <t>M-02</t>
         </is>
       </c>
       <c r="D20" s="26" t="inlineStr">
         <is>
-          <t>Validar aislamiento multi-tenant endpoint por endpoint</t>
+          <t>Aceptacion de Terminos y Condiciones</t>
         </is>
       </c>
       <c r="E20" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+          <t>RF-31</t>
+        </is>
+      </c>
+      <c r="F20" s="26" t="inlineStr">
+        <is>
+          <t>Correccion + validacion</t>
+        </is>
+      </c>
+      <c r="G20" s="26" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H20" s="26" t="inlineStr">
+        <is>
+          <t>Daniel Avila</t>
+        </is>
+      </c>
+      <c r="I20" s="26" t="inlineStr">
+        <is>
+          <t>Daniel Avila</t>
+        </is>
+      </c>
+      <c r="J20" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K20" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L20" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M02-11</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="28" t="inlineStr">
-        <is>
-          <t>QA-VAL-17</t>
+      <c r="A21" s="29" t="inlineStr">
+        <is>
+          <t>HU-M02-12</t>
         </is>
       </c>
       <c r="B21" s="26" t="inlineStr">
         <is>
-          <t>VAL-17</t>
+          <t>M-02.12</t>
         </is>
       </c>
       <c r="C21" s="26" t="inlineStr">
         <is>
-          <t>Validacion</t>
+          <t>M-02</t>
         </is>
       </c>
       <c r="D21" s="26" t="inlineStr">
         <is>
-          <t>Validar logout y expiracion de sesion</t>
+          <t>Autenticacion consumida desde la API y no desde Supabase directo en el cliente</t>
         </is>
       </c>
       <c r="E21" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+          <t>RF-03 / ADR-0027</t>
+        </is>
+      </c>
+      <c r="F21" s="26" t="inlineStr">
+        <is>
+          <t>Correccion + validacion</t>
+        </is>
+      </c>
+      <c r="G21" s="26" t="inlineStr">
+        <is>
+          <t>Parcial (migracion en curso)</t>
+        </is>
+      </c>
+      <c r="H21" s="26" t="inlineStr">
+        <is>
+          <t>Daniel Avila</t>
+        </is>
+      </c>
+      <c r="I21" s="26" t="inlineStr">
+        <is>
+          <t>Daniel Avila</t>
+        </is>
+      </c>
+      <c r="J21" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K21" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L21" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M02-12</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="28" t="inlineStr">
-        <is>
-          <t>QA-VAL-18</t>
+      <c r="A22" s="29" t="inlineStr">
+        <is>
+          <t>HU-M02-13</t>
         </is>
       </c>
       <c r="B22" s="26" t="inlineStr">
         <is>
-          <t>VAL-18</t>
+          <t>M-02.13</t>
         </is>
       </c>
       <c r="C22" s="26" t="inlineStr">
         <is>
-          <t>Validacion</t>
+          <t>M-02</t>
         </is>
       </c>
       <c r="D22" s="26" t="inlineStr">
         <is>
-          <t>Ejecutar la regresion de seguridad de identidad (17 casos negativos y 1 positivo)</t>
+          <t>Validacion perimetral del token y propagacion de claims</t>
         </is>
       </c>
       <c r="E22" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+          <t>RF-03</t>
+        </is>
+      </c>
+      <c r="F22" s="26" t="inlineStr">
+        <is>
+          <t>Correccion + validacion</t>
+        </is>
+      </c>
+      <c r="G22" s="26" t="inlineStr">
+        <is>
+          <t>Implementado con defecto abierto</t>
+        </is>
+      </c>
+      <c r="H22" s="26" t="inlineStr">
+        <is>
+          <t>Daniel Avila</t>
+        </is>
+      </c>
+      <c r="I22" s="26" t="inlineStr">
+        <is>
+          <t>Daniel Avila</t>
+        </is>
+      </c>
+      <c r="J22" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K22" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L22" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M02-13</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="28" t="inlineStr">
         <is>
-          <t>QA-VAL-19</t>
+          <t>HU-M02-14</t>
         </is>
       </c>
       <c r="B23" s="26" t="inlineStr">
         <is>
-          <t>VAL-19</t>
+          <t>M-02.14</t>
         </is>
       </c>
       <c r="C23" s="26" t="inlineStr">
         <is>
-          <t>Validacion</t>
+          <t>M-02</t>
         </is>
       </c>
       <c r="D23" s="26" t="inlineStr">
         <is>
-          <t>Validar el contrato del perfil del aliado que consumen Dispatch y Rules</t>
+          <t>Autorizacion por rol y tenant en cada peticion</t>
         </is>
       </c>
       <c r="E23" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+          <t>RF-03</t>
+        </is>
+      </c>
+      <c r="F23" s="26" t="inlineStr">
+        <is>
+          <t>Validacion de lo implementado</t>
+        </is>
+      </c>
+      <c r="G23" s="26" t="inlineStr">
+        <is>
+          <t>Implementado</t>
+        </is>
+      </c>
+      <c r="H23" s="26" t="inlineStr">
+        <is>
+          <t>Daniel Avila</t>
+        </is>
+      </c>
+      <c r="I23" s="26" t="inlineStr">
+        <is>
+          <t>Daniel Avila</t>
+        </is>
+      </c>
+      <c r="J23" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L23" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M02-14</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="28" t="inlineStr">
-        <is>
-          <t>QA-VAL-20</t>
+      <c r="A24" s="29" t="inlineStr">
+        <is>
+          <t>HU-M02-15</t>
         </is>
       </c>
       <c r="B24" s="26" t="inlineStr">
         <is>
-          <t>VAL-20</t>
+          <t>M-02.15</t>
         </is>
       </c>
       <c r="C24" s="26" t="inlineStr">
         <is>
-          <t>Validacion</t>
+          <t>M-02</t>
         </is>
       </c>
       <c r="D24" s="26" t="inlineStr">
         <is>
-          <t>Validar que el catalogo responde solo las categorias y zonas del tenant del claim</t>
+          <t>Cifrado de credenciales y de datos sensibles</t>
         </is>
       </c>
       <c r="E24" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+          <t>RNF-01 / REST-02</t>
+        </is>
+      </c>
+      <c r="F24" s="26" t="inlineStr">
+        <is>
+          <t>Correccion + validacion</t>
+        </is>
+      </c>
+      <c r="G24" s="26" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H24" s="26" t="inlineStr">
+        <is>
+          <t>Daniel Avila</t>
+        </is>
+      </c>
+      <c r="I24" s="26" t="inlineStr">
+        <is>
+          <t>Daniel Avila</t>
+        </is>
+      </c>
+      <c r="J24" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K24" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L24" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M02-15</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="28" t="inlineStr">
         <is>
-          <t>QA-VAL-21</t>
+          <t>HU-M03-01</t>
         </is>
       </c>
       <c r="B25" s="26" t="inlineStr">
         <is>
-          <t>VAL-21</t>
+          <t>M-03.1</t>
         </is>
       </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>Validacion</t>
+          <t>M-03</t>
         </is>
       </c>
       <c r="D25" s="26" t="inlineStr">
         <is>
-          <t>Validar el contexto de solicitud que Dispatch pide a Core</t>
+          <t>Bandeja de verificacion: aprobar o rechazar aliado</t>
         </is>
       </c>
       <c r="E25" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+          <t>RF-06</t>
+        </is>
+      </c>
+      <c r="F25" s="26" t="inlineStr">
+        <is>
+          <t>Validacion de lo implementado</t>
+        </is>
+      </c>
+      <c r="G25" s="26" t="inlineStr">
+        <is>
+          <t>Done sin validar en arquitectura vigente</t>
+        </is>
+      </c>
+      <c r="H25" s="26" t="inlineStr">
+        <is>
+          <t>Camila Beltran (PO)</t>
+        </is>
+      </c>
+      <c r="I25" s="26" t="inlineStr">
+        <is>
+          <t>Camila Beltran (PO)</t>
+        </is>
+      </c>
+      <c r="J25" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L25" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M03-01</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="28" t="inlineStr">
-        <is>
-          <t>QA-VAL-22</t>
+      <c r="A26" s="29" t="inlineStr">
+        <is>
+          <t>HU-M03-02</t>
         </is>
       </c>
       <c r="B26" s="26" t="inlineStr">
         <is>
-          <t>VAL-22</t>
+          <t>M-03.2</t>
         </is>
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>Validacion</t>
+          <t>M-03</t>
         </is>
       </c>
       <c r="D26" s="26" t="inlineStr">
         <is>
-          <t>Validar idempotencia de la creacion de solicitud y del despacho bajo reintento</t>
+          <t>Declarar zonas de cobertura del aliado</t>
         </is>
       </c>
       <c r="E26" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
+          <t>RF-07</t>
+        </is>
+      </c>
+      <c r="F26" s="26" t="inlineStr">
+        <is>
+          <t>Terminar + validacion</t>
+        </is>
+      </c>
+      <c r="G26" s="26" t="inlineStr">
+        <is>
+          <t>Reespecificada</t>
+        </is>
+      </c>
+      <c r="H26" s="26" t="inlineStr">
+        <is>
+          <t>Camila Beltran (PO)</t>
+        </is>
+      </c>
+      <c r="I26" s="26" t="inlineStr">
+        <is>
+          <t>Camila Beltran (PO)</t>
+        </is>
+      </c>
+      <c r="J26" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K26" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L26" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M03-02</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="31" t="inlineStr">
-        <is>
-          <t>QA-CONS-01</t>
+      <c r="A27" s="29" t="inlineStr">
+        <is>
+          <t>HU-M03-03</t>
         </is>
       </c>
       <c r="B27" s="26" t="inlineStr">
         <is>
-          <t>CONS-01</t>
+          <t>M-03.3</t>
         </is>
       </c>
       <c r="C27" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-03</t>
         </is>
       </c>
       <c r="D27" s="26" t="inlineStr">
         <is>
-          <t>Inicio de sesion separado por tipo de usuario</t>
+          <t>Disponibilidad y ausencias del aliado</t>
         </is>
       </c>
       <c r="E27" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-29 / RF-12 (soporte)</t>
+        </is>
+      </c>
+      <c r="F27" s="26" t="inlineStr">
+        <is>
+          <t>Correccion + validacion</t>
+        </is>
+      </c>
+      <c r="G27" s="26" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H27" s="26" t="inlineStr">
+        <is>
+          <t>Camila Beltran (PO)</t>
+        </is>
+      </c>
+      <c r="I27" s="26" t="inlineStr">
+        <is>
+          <t>Camila Beltran (PO)</t>
+        </is>
+      </c>
+      <c r="J27" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K27" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L27" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M03-03</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="31" t="inlineStr">
         <is>
-          <t>QA-CONS-02</t>
+          <t>HU-M03-04</t>
         </is>
       </c>
       <c r="B28" s="26" t="inlineStr">
         <is>
-          <t>CONS-02</t>
+          <t>M-03.4</t>
         </is>
       </c>
       <c r="C28" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-03</t>
         </is>
       </c>
       <c r="D28" s="26" t="inlineStr">
         <is>
-          <t>Logout</t>
+          <t>Cliente empresa administra multiples sitios de servicio</t>
         </is>
       </c>
       <c r="E28" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-08</t>
+        </is>
+      </c>
+      <c r="F28" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G28" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H28" s="33" t="inlineStr">
+        <is>
+          <t>Jose Nicolas Alvarez</t>
+        </is>
+      </c>
+      <c r="I28" s="26" t="inlineStr">
+        <is>
+          <t>Camila Beltran (PO)</t>
+        </is>
+      </c>
+      <c r="J28" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K28" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L28" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M03-04</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="31" t="inlineStr">
         <is>
-          <t>QA-CONS-03</t>
+          <t>HU-M03-05</t>
         </is>
       </c>
       <c r="B29" s="26" t="inlineStr">
         <is>
-          <t>CONS-03</t>
+          <t>M-03.5</t>
         </is>
       </c>
       <c r="C29" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-03</t>
         </is>
       </c>
       <c r="D29" s="26" t="inlineStr">
         <is>
-          <t>Autenticacion consumida desde la API y retiro de Supabase directo en el cliente</t>
+          <t>Reglas contextuales del sitio visibles al aliado antes de programar</t>
         </is>
       </c>
       <c r="E29" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-09</t>
+        </is>
+      </c>
+      <c r="F29" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G29" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H29" s="33" t="inlineStr">
+        <is>
+          <t>Jose Nicolas Alvarez</t>
+        </is>
+      </c>
+      <c r="I29" s="26" t="inlineStr">
+        <is>
+          <t>Camila Beltran (PO)</t>
+        </is>
+      </c>
+      <c r="J29" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K29" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L29" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M03-05</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="31" t="inlineStr">
-        <is>
-          <t>QA-CONS-04</t>
+      <c r="A30" s="28" t="inlineStr">
+        <is>
+          <t>HU-M03-06</t>
         </is>
       </c>
       <c r="B30" s="26" t="inlineStr">
         <is>
-          <t>CONS-04</t>
+          <t>M-03.6</t>
         </is>
       </c>
       <c r="C30" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-03</t>
         </is>
       </c>
       <c r="D30" s="26" t="inlineStr">
         <is>
-          <t>Recuperacion segura de contrasena</t>
+          <t>Perfil del aliado autenticado consumible por otros servicios</t>
         </is>
       </c>
       <c r="E30" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-30 / RF-05</t>
+        </is>
+      </c>
+      <c r="F30" s="26" t="inlineStr">
+        <is>
+          <t>Validacion de lo implementado</t>
+        </is>
+      </c>
+      <c r="G30" s="26" t="inlineStr">
+        <is>
+          <t>Implementado</t>
+        </is>
+      </c>
+      <c r="H30" s="26" t="inlineStr">
+        <is>
+          <t>Camila Beltran (PO)</t>
+        </is>
+      </c>
+      <c r="I30" s="26" t="inlineStr">
+        <is>
+          <t>Camila Beltran (PO)</t>
+        </is>
+      </c>
+      <c r="J30" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K30" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L30" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M03-06</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="31" t="inlineStr">
-        <is>
-          <t>QA-CONS-05</t>
+      <c r="A31" s="28" t="inlineStr">
+        <is>
+          <t>HU-M04-01</t>
         </is>
       </c>
       <c r="B31" s="26" t="inlineStr">
         <is>
-          <t>CONS-05</t>
+          <t>M-04.1</t>
         </is>
       </c>
       <c r="C31" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-04</t>
         </is>
       </c>
       <c r="D31" s="26" t="inlineStr">
         <is>
-          <t>Registro de cliente empresa</t>
+          <t>Crear categoria de servicio con flujo operativo</t>
         </is>
       </c>
       <c r="E31" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-10</t>
+        </is>
+      </c>
+      <c r="F31" s="26" t="inlineStr">
+        <is>
+          <t>Validacion de lo implementado</t>
+        </is>
+      </c>
+      <c r="G31" s="26" t="inlineStr">
+        <is>
+          <t>Done sin validar en arquitectura vigente</t>
+        </is>
+      </c>
+      <c r="H31" s="26" t="inlineStr">
+        <is>
+          <t>Sara Albarracin (SM)</t>
+        </is>
+      </c>
+      <c r="I31" s="26" t="inlineStr">
+        <is>
+          <t>Sara Albarracin (SM)</t>
+        </is>
+      </c>
+      <c r="J31" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K31" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L31" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M04-01</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="31" t="inlineStr">
         <is>
-          <t>QA-CONS-06</t>
+          <t>HU-M04-02</t>
         </is>
       </c>
       <c r="B32" s="26" t="inlineStr">
         <is>
-          <t>CONS-06</t>
+          <t>M-04.2</t>
         </is>
       </c>
       <c r="C32" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-04</t>
         </is>
       </c>
       <c r="D32" s="26" t="inlineStr">
         <is>
-          <t>Registro de empleado directo</t>
+          <t>Activar y desactivar categoria sin afectar servicios en curso</t>
         </is>
       </c>
       <c r="E32" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-10</t>
+        </is>
+      </c>
+      <c r="F32" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G32" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H32" s="33" t="inlineStr">
+        <is>
+          <t>Jose Nicolas Alvarez</t>
+        </is>
+      </c>
+      <c r="I32" s="26" t="inlineStr">
+        <is>
+          <t>Sara Albarracin (SM)</t>
+        </is>
+      </c>
+      <c r="J32" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K32" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L32" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M04-02</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="31" t="inlineStr">
-        <is>
-          <t>QA-CONS-07</t>
+      <c r="A33" s="29" t="inlineStr">
+        <is>
+          <t>HU-M04-03</t>
         </is>
       </c>
       <c r="B33" s="26" t="inlineStr">
         <is>
-          <t>CONS-07</t>
+          <t>M-04.3</t>
         </is>
       </c>
       <c r="C33" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-04</t>
         </is>
       </c>
       <c r="D33" s="26" t="inlineStr">
         <is>
-          <t>Menu superior por rol con sesion visible</t>
+          <t>Aliado declara las categorias que atiende</t>
         </is>
       </c>
       <c r="E33" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-11</t>
+        </is>
+      </c>
+      <c r="F33" s="26" t="inlineStr">
+        <is>
+          <t>Terminar + validacion</t>
+        </is>
+      </c>
+      <c r="G33" s="26" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="H33" s="26" t="inlineStr">
+        <is>
+          <t>Sara Albarracin (SM)</t>
+        </is>
+      </c>
+      <c r="I33" s="26" t="inlineStr">
+        <is>
+          <t>Sara Albarracin (SM)</t>
+        </is>
+      </c>
+      <c r="J33" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K33" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L33" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M04-03</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="31" t="inlineStr">
-        <is>
-          <t>QA-CONS-08</t>
+      <c r="A34" s="29" t="inlineStr">
+        <is>
+          <t>HU-M04-04</t>
         </is>
       </c>
       <c r="B34" s="26" t="inlineStr">
         <is>
-          <t>CONS-08</t>
+          <t>M-04.4</t>
         </is>
       </c>
       <c r="C34" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-04</t>
         </is>
       </c>
       <c r="D34" s="26" t="inlineStr">
         <is>
-          <t>Pantalla de inicio por tipo de usuario</t>
+          <t>Catalogo jerarquico de zonas geograficas</t>
         </is>
       </c>
       <c r="E34" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>REST-01 / RNF-09</t>
+        </is>
+      </c>
+      <c r="F34" s="26" t="inlineStr">
+        <is>
+          <t>Correccion + validacion</t>
+        </is>
+      </c>
+      <c r="G34" s="26" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H34" s="26" t="inlineStr">
+        <is>
+          <t>Sara Albarracin (SM)</t>
+        </is>
+      </c>
+      <c r="I34" s="26" t="inlineStr">
+        <is>
+          <t>Sara Albarracin (SM)</t>
+        </is>
+      </c>
+      <c r="J34" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K34" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L34" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M04-04</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="31" t="inlineStr">
-        <is>
-          <t>QA-CONS-09</t>
+      <c r="A35" s="28" t="inlineStr">
+        <is>
+          <t>HU-M04-05</t>
         </is>
       </c>
       <c r="B35" s="26" t="inlineStr">
         <is>
-          <t>CONS-09</t>
+          <t>M-04.5</t>
         </is>
       </c>
       <c r="C35" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-04</t>
         </is>
       </c>
       <c r="D35" s="26" t="inlineStr">
         <is>
-          <t>Enrutamiento por rol con guardas de sesion</t>
+          <t>Consulta del catalogo por tenant</t>
         </is>
       </c>
       <c r="E35" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-10</t>
+        </is>
+      </c>
+      <c r="F35" s="26" t="inlineStr">
+        <is>
+          <t>Validacion de lo implementado</t>
+        </is>
+      </c>
+      <c r="G35" s="26" t="inlineStr">
+        <is>
+          <t>Implementado</t>
+        </is>
+      </c>
+      <c r="H35" s="26" t="inlineStr">
+        <is>
+          <t>Sara Albarracin (SM)</t>
+        </is>
+      </c>
+      <c r="I35" s="26" t="inlineStr">
+        <is>
+          <t>Sara Albarracin (SM)</t>
+        </is>
+      </c>
+      <c r="J35" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K35" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L35" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M04-05</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="31" t="inlineStr">
         <is>
-          <t>QA-CONS-10</t>
+          <t>HU-M04-06</t>
         </is>
       </c>
       <c r="B36" s="26" t="inlineStr">
         <is>
-          <t>CONS-10</t>
+          <t>M-04.6</t>
         </is>
       </c>
       <c r="C36" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-04</t>
         </is>
       </c>
       <c r="D36" s="26" t="inlineStr">
         <is>
-          <t>Dividir el front en modulos independientes por dominio</t>
+          <t>Barrios como nivel mas fino de la jerarquia y cobertura por barrio</t>
         </is>
       </c>
       <c r="E36" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-07 / RNF-09</t>
+        </is>
+      </c>
+      <c r="F36" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G36" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H36" s="33" t="inlineStr">
+        <is>
+          <t>Jose Nicolas Alvarez</t>
+        </is>
+      </c>
+      <c r="I36" s="26" t="inlineStr">
+        <is>
+          <t>Sara Albarracin (SM)</t>
+        </is>
+      </c>
+      <c r="J36" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K36" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L36" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M04-06</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="31" t="inlineStr">
         <is>
-          <t>QA-CONS-11</t>
+          <t>HU-M04-07</t>
         </is>
       </c>
       <c r="B37" s="26" t="inlineStr">
         <is>
-          <t>CONS-11</t>
+          <t>M-04.7</t>
         </is>
       </c>
       <c r="C37" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-04</t>
         </is>
       </c>
       <c r="D37" s="26" t="inlineStr">
         <is>
-          <t>Dividir el Core por dominios internos</t>
+          <t>Visualizacion en mapa de zonas, barrios y del sitio de servicio</t>
         </is>
       </c>
       <c r="E37" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RNF-08</t>
+        </is>
+      </c>
+      <c r="F37" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G37" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H37" s="33" t="inlineStr">
+        <is>
+          <t>Jose Nicolas Alvarez</t>
+        </is>
+      </c>
+      <c r="I37" s="26" t="inlineStr">
+        <is>
+          <t>Sara Albarracin (SM)</t>
+        </is>
+      </c>
+      <c r="J37" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K37" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L37" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M04-07</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="31" t="inlineStr">
-        <is>
-          <t>QA-CONS-12</t>
+      <c r="A38" s="28" t="inlineStr">
+        <is>
+          <t>HU-M05-01</t>
         </is>
       </c>
       <c r="B38" s="26" t="inlineStr">
         <is>
-          <t>CONS-12</t>
+          <t>M-05.1</t>
         </is>
       </c>
       <c r="C38" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-05</t>
         </is>
       </c>
       <c r="D38" s="26" t="inlineStr">
         <is>
-          <t>Barrios como nivel mas fino del catalogo de zonas</t>
+          <t>Crear y persistir la solicitud de servicio</t>
         </is>
       </c>
       <c r="E38" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-12</t>
+        </is>
+      </c>
+      <c r="F38" s="26" t="inlineStr">
+        <is>
+          <t>Validacion de lo implementado</t>
+        </is>
+      </c>
+      <c r="G38" s="26" t="inlineStr">
+        <is>
+          <t>Implementado en servicio, sin validar por el front</t>
+        </is>
+      </c>
+      <c r="H38" s="26" t="inlineStr">
+        <is>
+          <t>Santiago Hernandez (QA)</t>
+        </is>
+      </c>
+      <c r="I38" s="26" t="inlineStr">
+        <is>
+          <t>Santiago Hernandez (QA)</t>
+        </is>
+      </c>
+      <c r="J38" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K38" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L38" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M05-01</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="31" t="inlineStr">
-        <is>
-          <t>QA-CONS-13</t>
+      <c r="A39" s="28" t="inlineStr">
+        <is>
+          <t>HU-M05-02</t>
         </is>
       </c>
       <c r="B39" s="26" t="inlineStr">
         <is>
-          <t>CONS-13</t>
+          <t>M-05.2</t>
         </is>
       </c>
       <c r="C39" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-05</t>
         </is>
       </c>
       <c r="D39" s="26" t="inlineStr">
         <is>
-          <t>Visualizacion en mapa de zonas, barrios y sitio de servicio</t>
+          <t>Elegibilidad: aliados validos por categoria, zona, disponibilidad y rechazo previo</t>
         </is>
       </c>
       <c r="E39" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-12 / RNF-07</t>
+        </is>
+      </c>
+      <c r="F39" s="26" t="inlineStr">
+        <is>
+          <t>Validacion de lo implementado</t>
+        </is>
+      </c>
+      <c r="G39" s="26" t="inlineStr">
+        <is>
+          <t>Implementado en servicio, sin validar por el front</t>
+        </is>
+      </c>
+      <c r="H39" s="26" t="inlineStr">
+        <is>
+          <t>Santiago Hernandez (QA)</t>
+        </is>
+      </c>
+      <c r="I39" s="26" t="inlineStr">
+        <is>
+          <t>Santiago Hernandez (QA)</t>
+        </is>
+      </c>
+      <c r="J39" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K39" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L39" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M05-02</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="31" t="inlineStr">
-        <is>
-          <t>QA-CONS-14</t>
+      <c r="A40" s="28" t="inlineStr">
+        <is>
+          <t>HU-M05-03</t>
         </is>
       </c>
       <c r="B40" s="26" t="inlineStr">
         <is>
-          <t>CONS-14</t>
+          <t>M-05.3</t>
         </is>
       </c>
       <c r="C40" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-05</t>
         </is>
       </c>
       <c r="D40" s="26" t="inlineStr">
         <is>
-          <t>Activar y desactivar categoria sin afectar servicios en curso</t>
+          <t>Contexto de la solicitud (zona, categoria, estado)</t>
         </is>
       </c>
       <c r="E40" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-12</t>
+        </is>
+      </c>
+      <c r="F40" s="26" t="inlineStr">
+        <is>
+          <t>Validacion de lo implementado</t>
+        </is>
+      </c>
+      <c r="G40" s="26" t="inlineStr">
+        <is>
+          <t>Implementado</t>
+        </is>
+      </c>
+      <c r="H40" s="26" t="inlineStr">
+        <is>
+          <t>Santiago Hernandez (QA)</t>
+        </is>
+      </c>
+      <c r="I40" s="26" t="inlineStr">
+        <is>
+          <t>Santiago Hernandez (QA)</t>
+        </is>
+      </c>
+      <c r="J40" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K40" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L40" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M05-03</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="31" t="inlineStr">
-        <is>
-          <t>QA-CONS-15</t>
+      <c r="A41" s="28" t="inlineStr">
+        <is>
+          <t>HU-M05-04</t>
         </is>
       </c>
       <c r="B41" s="26" t="inlineStr">
         <is>
-          <t>CONS-15</t>
+          <t>M-05.4</t>
         </is>
       </c>
       <c r="C41" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-05</t>
         </is>
       </c>
       <c r="D41" s="26" t="inlineStr">
         <is>
-          <t>Aliado gestiona su disponibilidad y sus ausencias</t>
+          <t>Filtrar aliados por tipo de aliado</t>
         </is>
       </c>
       <c r="E41" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-12</t>
+        </is>
+      </c>
+      <c r="F41" s="26" t="inlineStr">
+        <is>
+          <t>Validacion de lo implementado</t>
+        </is>
+      </c>
+      <c r="G41" s="26" t="inlineStr">
+        <is>
+          <t>Implementado en servicio, sin validar por el front</t>
+        </is>
+      </c>
+      <c r="H41" s="26" t="inlineStr">
+        <is>
+          <t>Santiago Hernandez (QA)</t>
+        </is>
+      </c>
+      <c r="I41" s="26" t="inlineStr">
+        <is>
+          <t>Santiago Hernandez (QA)</t>
+        </is>
+      </c>
+      <c r="J41" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K41" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L41" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M05-04</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="31" t="inlineStr">
         <is>
-          <t>QA-CONS-16</t>
+          <t>HU-M05-05</t>
         </is>
       </c>
       <c r="B42" s="26" t="inlineStr">
         <is>
-          <t>CONS-16</t>
+          <t>M-05.5</t>
         </is>
       </c>
       <c r="C42" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-05</t>
         </is>
       </c>
       <c r="D42" s="26" t="inlineStr">
         <is>
-          <t>Cliente empresa administra multiples sitios de servicio</t>
+          <t>Ordenar el listado de aliados segun la regla del tenant</t>
         </is>
       </c>
       <c r="E42" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-13</t>
+        </is>
+      </c>
+      <c r="F42" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G42" s="26" t="inlineStr">
+        <is>
+          <t>No implementado</t>
+        </is>
+      </c>
+      <c r="H42" s="33" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="I42" s="26" t="inlineStr">
+        <is>
+          <t>Santiago Hernandez (QA)</t>
+        </is>
+      </c>
+      <c r="J42" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K42" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L42" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M05-05</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="31" t="inlineStr">
-        <is>
-          <t>QA-CONS-17</t>
+      <c r="A43" s="29" t="inlineStr">
+        <is>
+          <t>HU-M05-06</t>
         </is>
       </c>
       <c r="B43" s="26" t="inlineStr">
         <is>
-          <t>CONS-17</t>
+          <t>M-05.6</t>
         </is>
       </c>
       <c r="C43" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-05</t>
         </is>
       </c>
       <c r="D43" s="26" t="inlineStr">
         <is>
-          <t>Reglas contextuales del sitio visibles al aliado antes de programar</t>
+          <t>Broadcast de ofertas a los aliados elegibles</t>
         </is>
       </c>
       <c r="E43" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-14</t>
+        </is>
+      </c>
+      <c r="F43" s="26" t="inlineStr">
+        <is>
+          <t>Correccion + validacion</t>
+        </is>
+      </c>
+      <c r="G43" s="26" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H43" s="26" t="inlineStr">
+        <is>
+          <t>Santiago Hernandez (QA)</t>
+        </is>
+      </c>
+      <c r="I43" s="26" t="inlineStr">
+        <is>
+          <t>Santiago Hernandez (QA)</t>
+        </is>
+      </c>
+      <c r="J43" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K43" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L43" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M05-06</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="31" t="inlineStr">
-        <is>
-          <t>QA-CONS-18</t>
+      <c r="A44" s="29" t="inlineStr">
+        <is>
+          <t>HU-M05-07</t>
         </is>
       </c>
       <c r="B44" s="26" t="inlineStr">
         <is>
-          <t>CONS-18</t>
+          <t>M-05.7</t>
         </is>
       </c>
       <c r="C44" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-05</t>
         </is>
       </c>
       <c r="D44" s="26" t="inlineStr">
         <is>
-          <t>Orden del listado de aliados en el Rules Service</t>
+          <t>Aceptar solicitud sin doble asignacion</t>
         </is>
       </c>
       <c r="E44" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-14 / RNF-05 / RNF-07</t>
+        </is>
+      </c>
+      <c r="F44" s="26" t="inlineStr">
+        <is>
+          <t>Correccion + validacion</t>
+        </is>
+      </c>
+      <c r="G44" s="26" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H44" s="26" t="inlineStr">
+        <is>
+          <t>Santiago Hernandez (QA)</t>
+        </is>
+      </c>
+      <c r="I44" s="26" t="inlineStr">
+        <is>
+          <t>Santiago Hernandez (QA)</t>
+        </is>
+      </c>
+      <c r="J44" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K44" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L44" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M05-07</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="31" t="inlineStr">
-        <is>
-          <t>QA-CONS-19</t>
+      <c r="A45" s="29" t="inlineStr">
+        <is>
+          <t>HU-M05-08</t>
         </is>
       </c>
       <c r="B45" s="26" t="inlineStr">
         <is>
-          <t>CONS-19</t>
+          <t>M-05.8</t>
         </is>
       </c>
       <c r="C45" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-05</t>
         </is>
       </c>
       <c r="D45" s="26" t="inlineStr">
         <is>
-          <t>Priorizar solicitud por comision ofrecida</t>
+          <t>Rechazar oferta</t>
         </is>
       </c>
       <c r="E45" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-14</t>
+        </is>
+      </c>
+      <c r="F45" s="26" t="inlineStr">
+        <is>
+          <t>Correccion + validacion</t>
+        </is>
+      </c>
+      <c r="G45" s="26" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H45" s="26" t="inlineStr">
+        <is>
+          <t>Santiago Hernandez (QA)</t>
+        </is>
+      </c>
+      <c r="I45" s="26" t="inlineStr">
+        <is>
+          <t>Santiago Hernandez (QA)</t>
+        </is>
+      </c>
+      <c r="J45" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K45" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L45" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M05-08</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="31" t="inlineStr">
-        <is>
-          <t>QA-CONS-20</t>
+      <c r="A46" s="29" t="inlineStr">
+        <is>
+          <t>HU-M05-09</t>
         </is>
       </c>
       <c r="B46" s="26" t="inlineStr">
         <is>
-          <t>CONS-20</t>
+          <t>M-05.9</t>
         </is>
       </c>
       <c r="C46" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-05</t>
         </is>
       </c>
       <c r="D46" s="26" t="inlineStr">
         <is>
-          <t>Cancelar solicitud antes de la ejecucion</t>
+          <t>Idempotencia de la creacion y del despacho</t>
         </is>
       </c>
       <c r="E46" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RNF-03</t>
+        </is>
+      </c>
+      <c r="F46" s="26" t="inlineStr">
+        <is>
+          <t>Correccion + validacion</t>
+        </is>
+      </c>
+      <c r="G46" s="26" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H46" s="26" t="inlineStr">
+        <is>
+          <t>Santiago Hernandez (QA)</t>
+        </is>
+      </c>
+      <c r="I46" s="26" t="inlineStr">
+        <is>
+          <t>Santiago Hernandez (QA)</t>
+        </is>
+      </c>
+      <c r="J46" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K46" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L46" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M05-09</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="31" t="inlineStr">
         <is>
-          <t>QA-CONS-21</t>
+          <t>HU-M05-10</t>
         </is>
       </c>
       <c r="B47" s="26" t="inlineStr">
         <is>
-          <t>CONS-21</t>
+          <t>M-05.10</t>
         </is>
       </c>
       <c r="C47" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-05</t>
         </is>
       </c>
       <c r="D47" s="26" t="inlineStr">
         <is>
-          <t>Cotizacion con mano de obra y materiales separados</t>
+          <t>Cancelar solicitud antes de la ejecucion</t>
         </is>
       </c>
       <c r="E47" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-32 / RF-14</t>
+        </is>
+      </c>
+      <c r="F47" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G47" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H47" s="33" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="I47" s="26" t="inlineStr">
+        <is>
+          <t>Santiago Hernandez (QA)</t>
+        </is>
+      </c>
+      <c r="J47" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K47" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L47" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M05-10</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="31" t="inlineStr">
         <is>
-          <t>QA-CONS-22</t>
+          <t>HU-M06-01</t>
         </is>
       </c>
       <c r="B48" s="26" t="inlineStr">
         <is>
-          <t>CONS-22</t>
+          <t>M-06.1</t>
         </is>
       </c>
       <c r="C48" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-06</t>
         </is>
       </c>
       <c r="D48" s="26" t="inlineStr">
         <is>
-          <t>Alerta de cotizacion fuera del rango del tarifario</t>
+          <t>Elaborar cotizacion separando mano de obra y materiales</t>
         </is>
       </c>
       <c r="E48" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-15</t>
+        </is>
+      </c>
+      <c r="F48" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G48" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H48" s="26" t="inlineStr">
+        <is>
+          <t>Jose Nicolas Alvarez</t>
+        </is>
+      </c>
+      <c r="I48" s="26" t="inlineStr">
+        <is>
+          <t>Jose Nicolas Alvarez</t>
+        </is>
+      </c>
+      <c r="J48" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K48" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L48" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M06-01</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="31" t="inlineStr">
         <is>
-          <t>QA-CONS-23</t>
+          <t>HU-M06-02</t>
         </is>
       </c>
       <c r="B49" s="26" t="inlineStr">
         <is>
-          <t>CONS-23</t>
+          <t>M-06.2</t>
         </is>
       </c>
       <c r="C49" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-06</t>
         </is>
       </c>
       <c r="D49" s="26" t="inlineStr">
         <is>
-          <t>Cliente acepta, rechaza o solicita ajuste de la cotizacion</t>
+          <t>Alerta de cotizacion fuera del rango del tarifario</t>
         </is>
       </c>
       <c r="E49" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-16</t>
+        </is>
+      </c>
+      <c r="F49" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G49" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H49" s="26" t="inlineStr">
+        <is>
+          <t>Jose Nicolas Alvarez</t>
+        </is>
+      </c>
+      <c r="I49" s="26" t="inlineStr">
+        <is>
+          <t>Jose Nicolas Alvarez</t>
+        </is>
+      </c>
+      <c r="J49" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K49" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L49" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M06-02</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="31" t="inlineStr">
         <is>
-          <t>QA-CONS-24</t>
+          <t>HU-M06-03</t>
         </is>
       </c>
       <c r="B50" s="26" t="inlineStr">
         <is>
-          <t>CONS-24</t>
+          <t>M-06.3</t>
         </is>
       </c>
       <c r="C50" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-06</t>
         </is>
       </c>
       <c r="D50" s="26" t="inlineStr">
         <is>
-          <t>Marcar inicio y fin de la ejecucion</t>
+          <t>Cliente acepta, rechaza o solicita ajuste de la cotizacion</t>
         </is>
       </c>
       <c r="E50" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-17</t>
+        </is>
+      </c>
+      <c r="F50" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G50" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H50" s="26" t="inlineStr">
+        <is>
+          <t>Jose Nicolas Alvarez</t>
+        </is>
+      </c>
+      <c r="I50" s="26" t="inlineStr">
+        <is>
+          <t>Jose Nicolas Alvarez</t>
+        </is>
+      </c>
+      <c r="J50" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K50" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L50" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M06-03</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="31" t="inlineStr">
         <is>
-          <t>QA-CONS-25</t>
+          <t>HU-M07-01</t>
         </is>
       </c>
       <c r="B51" s="26" t="inlineStr">
         <is>
-          <t>CONS-25</t>
+          <t>M-07.1</t>
         </is>
       </c>
       <c r="C51" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-07</t>
         </is>
       </c>
       <c r="D51" s="26" t="inlineStr">
         <is>
-          <t>Registrar eventos y observaciones durante la ejecucion</t>
+          <t>Marcar inicio y fin de la ejecucion</t>
         </is>
       </c>
       <c r="E51" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-18</t>
+        </is>
+      </c>
+      <c r="F51" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G51" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H51" s="26" t="inlineStr">
+        <is>
+          <t>Jose Nicolas Alvarez</t>
+        </is>
+      </c>
+      <c r="I51" s="26" t="inlineStr">
+        <is>
+          <t>Jose Nicolas Alvarez</t>
+        </is>
+      </c>
+      <c r="J51" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K51" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L51" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M07-01</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="31" t="inlineStr">
         <is>
-          <t>QA-CONS-26</t>
+          <t>HU-M07-02</t>
         </is>
       </c>
       <c r="B52" s="26" t="inlineStr">
         <is>
-          <t>CONS-26</t>
+          <t>M-07.2</t>
         </is>
       </c>
       <c r="C52" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-07</t>
         </is>
       </c>
       <c r="D52" s="26" t="inlineStr">
         <is>
-          <t>Registrar evidencias sin conexion y sincronizarlas</t>
+          <t>Registrar cronologicamente eventos y observaciones</t>
         </is>
       </c>
       <c r="E52" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-18 / RNF-04</t>
+        </is>
+      </c>
+      <c r="F52" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G52" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H52" s="26" t="inlineStr">
+        <is>
+          <t>Jose Nicolas Alvarez</t>
+        </is>
+      </c>
+      <c r="I52" s="26" t="inlineStr">
+        <is>
+          <t>Jose Nicolas Alvarez</t>
+        </is>
+      </c>
+      <c r="J52" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K52" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L52" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M07-02</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="31" t="inlineStr">
         <is>
-          <t>QA-CONS-27</t>
+          <t>HU-M07-03</t>
         </is>
       </c>
       <c r="B53" s="26" t="inlineStr">
         <is>
-          <t>CONS-27</t>
+          <t>M-07.3</t>
         </is>
       </c>
       <c r="C53" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-07</t>
         </is>
       </c>
       <c r="D53" s="26" t="inlineStr">
         <is>
-          <t>Cargar la tabla de tarifas por categoria</t>
+          <t>Cliente consulta el log del servicio</t>
         </is>
       </c>
       <c r="E53" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-18</t>
+        </is>
+      </c>
+      <c r="F53" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G53" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H53" s="26" t="inlineStr">
+        <is>
+          <t>Jose Nicolas Alvarez</t>
+        </is>
+      </c>
+      <c r="I53" s="26" t="inlineStr">
+        <is>
+          <t>Jose Nicolas Alvarez</t>
+        </is>
+      </c>
+      <c r="J53" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K53" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L53" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M07-03</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="31" t="inlineStr">
-        <is>
-          <t>QA-CONS-28</t>
+      <c r="A54" s="32" t="inlineStr">
+        <is>
+          <t>HU-M07-04</t>
         </is>
       </c>
       <c r="B54" s="26" t="inlineStr">
         <is>
-          <t>CONS-28</t>
+          <t>M-07.4</t>
         </is>
       </c>
       <c r="C54" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-07</t>
         </is>
       </c>
       <c r="D54" s="26" t="inlineStr">
         <is>
-          <t>Ver la tarifa de referencia al cotizar</t>
+          <t>Cliente rastrea la ubicacion del aliado en vivo</t>
         </is>
       </c>
       <c r="E54" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
-        </is>
-      </c>
+          <t>Fuera de alcance MVP</t>
+        </is>
+      </c>
+      <c r="F54" s="26" t="inlineStr">
+        <is>
+          <t>Fuera de alcance</t>
+        </is>
+      </c>
+      <c r="G54" s="26" t="inlineStr">
+        <is>
+          <t>To Do (fuera de MVP)</t>
+        </is>
+      </c>
+      <c r="H54" s="26" t="inlineStr">
+        <is>
+          <t>Jose Nicolas Alvarez</t>
+        </is>
+      </c>
+      <c r="I54" s="26" t="inlineStr">
+        <is>
+          <t>Jose Nicolas Alvarez</t>
+        </is>
+      </c>
+      <c r="J54" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="26" t="inlineStr">
+        <is>
+          <t>Fuera: rastreo en vivo esta fuera del MVP por SRS §1.2</t>
+        </is>
+      </c>
+      <c r="L54" s="26" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="31" t="inlineStr">
         <is>
-          <t>QA-CONS-29</t>
+          <t>HU-M07-05</t>
         </is>
       </c>
       <c r="B55" s="26" t="inlineStr">
         <is>
-          <t>CONS-29</t>
+          <t>M-07.5</t>
         </is>
       </c>
       <c r="C55" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-07</t>
         </is>
       </c>
       <c r="D55" s="26" t="inlineStr">
         <is>
-          <t>Reporte de cotizaciones fuera de rango por periodo</t>
+          <t>Aliado solicita adicion por imprevisto</t>
         </is>
       </c>
       <c r="E55" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-34 / RF-15 / RF-17</t>
+        </is>
+      </c>
+      <c r="F55" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G55" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H55" s="26" t="inlineStr">
+        <is>
+          <t>Jose Nicolas Alvarez</t>
+        </is>
+      </c>
+      <c r="I55" s="26" t="inlineStr">
+        <is>
+          <t>Jose Nicolas Alvarez</t>
+        </is>
+      </c>
+      <c r="J55" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K55" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L55" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M07-05</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="31" t="inlineStr">
         <is>
-          <t>QA-CONS-30</t>
+          <t>HU-M07-06</t>
         </is>
       </c>
       <c r="B56" s="26" t="inlineStr">
         <is>
-          <t>CONS-30</t>
+          <t>M-07.6</t>
         </is>
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-07</t>
         </is>
       </c>
       <c r="D56" s="26" t="inlineStr">
         <is>
-          <t>Calificacion bidireccional y cierre condicionado</t>
+          <t>Registrar evidencias sin conexion</t>
         </is>
       </c>
       <c r="E56" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-35 / RNF-03</t>
+        </is>
+      </c>
+      <c r="F56" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G56" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H56" s="26" t="inlineStr">
+        <is>
+          <t>Jose Nicolas Alvarez</t>
+        </is>
+      </c>
+      <c r="I56" s="26" t="inlineStr">
+        <is>
+          <t>Jose Nicolas Alvarez</t>
+        </is>
+      </c>
+      <c r="J56" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K56" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L56" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M07-06</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="31" t="inlineStr">
         <is>
-          <t>QA-CONS-31</t>
+          <t>HU-M08-01</t>
         </is>
       </c>
       <c r="B57" s="26" t="inlineStr">
         <is>
-          <t>CONS-31</t>
+          <t>M-08.1</t>
         </is>
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-08</t>
         </is>
       </c>
       <c r="D57" s="26" t="inlineStr">
         <is>
-          <t>Calificacion agregada visible en el listado de aliados</t>
+          <t>Cliente califica al aliado</t>
         </is>
       </c>
       <c r="E57" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-19</t>
+        </is>
+      </c>
+      <c r="F57" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G57" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H57" s="26" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="I57" s="26" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="J57" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K57" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L57" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M08-01</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="31" t="inlineStr">
         <is>
-          <t>QA-CONS-32</t>
+          <t>HU-M08-02</t>
         </is>
       </c>
       <c r="B58" s="26" t="inlineStr">
         <is>
-          <t>CONS-32</t>
+          <t>M-08.2</t>
         </is>
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-08</t>
         </is>
       </c>
       <c r="D58" s="26" t="inlineStr">
         <is>
-          <t>Penalizacion por cancelacion tardia</t>
+          <t>Aliado califica al cliente</t>
         </is>
       </c>
       <c r="E58" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-19</t>
+        </is>
+      </c>
+      <c r="F58" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G58" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H58" s="26" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="I58" s="26" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="J58" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K58" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L58" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M08-02</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="31" t="inlineStr">
         <is>
-          <t>QA-CONS-33</t>
+          <t>HU-M08-03</t>
         </is>
       </c>
       <c r="B59" s="26" t="inlineStr">
         <is>
-          <t>CONS-33</t>
+          <t>M-08.3</t>
         </is>
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-08</t>
         </is>
       </c>
       <c r="D59" s="26" t="inlineStr">
         <is>
-          <t>Historial de servicios del cliente y de trabajos del aliado</t>
+          <t>Cierre condicionado a la calificacion bidireccional</t>
         </is>
       </c>
       <c r="E59" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-19</t>
+        </is>
+      </c>
+      <c r="F59" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G59" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H59" s="26" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="I59" s="26" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="J59" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K59" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L59" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M08-03</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="31" t="inlineStr">
         <is>
-          <t>QA-CONS-34</t>
+          <t>HU-M08-04</t>
         </is>
       </c>
       <c r="B60" s="26" t="inlineStr">
         <is>
-          <t>CONS-34</t>
+          <t>M-08.4</t>
         </is>
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-08</t>
         </is>
       </c>
       <c r="D60" s="26" t="inlineStr">
         <is>
-          <t>Mensajeria cliente-aliado por servicio</t>
+          <t>Calificacion agregada visible en el listado</t>
         </is>
       </c>
       <c r="E60" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-13 / RF-19</t>
+        </is>
+      </c>
+      <c r="F60" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G60" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H60" s="26" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="I60" s="26" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="J60" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K60" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L60" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M08-04</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="31" t="inlineStr">
         <is>
-          <t>QA-CONS-35</t>
+          <t>HU-M08-05</t>
         </is>
       </c>
       <c r="B61" s="26" t="inlineStr">
         <is>
-          <t>CONS-35</t>
+          <t>M-08.5</t>
         </is>
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-08</t>
         </is>
       </c>
       <c r="D61" s="26" t="inlineStr">
         <is>
-          <t>Mock del proveedor de notificaciones push en el backend</t>
+          <t>Penalizacion por cancelacion tardia</t>
         </is>
       </c>
       <c r="E61" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-33 / RF-02 / RNF-10</t>
+        </is>
+      </c>
+      <c r="F61" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G61" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H61" s="26" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="I61" s="26" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="J61" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K61" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L61" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M08-05</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="31" t="inlineStr">
         <is>
-          <t>QA-CONS-36</t>
+          <t>HU-M08-06</t>
         </is>
       </c>
       <c r="B62" s="26" t="inlineStr">
         <is>
-          <t>CONS-36</t>
+          <t>M-08.6</t>
         </is>
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-08</t>
         </is>
       </c>
       <c r="D62" s="26" t="inlineStr">
         <is>
-          <t>Notificaciones de mensajes nuevos y del ciclo del servicio</t>
+          <t>Cliente consulta su historial de servicios</t>
         </is>
       </c>
       <c r="E62" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-36 / RF-18</t>
+        </is>
+      </c>
+      <c r="F62" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G62" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H62" s="26" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="I62" s="26" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="J62" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K62" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L62" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M08-06</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="31" t="inlineStr">
         <is>
-          <t>QA-CONS-37</t>
+          <t>HU-M08-07</t>
         </is>
       </c>
       <c r="B63" s="26" t="inlineStr">
         <is>
-          <t>CONS-37</t>
+          <t>M-08.7</t>
         </is>
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-08</t>
         </is>
       </c>
       <c r="D63" s="26" t="inlineStr">
         <is>
+          <t>Aliado consulta su historial de trabajos</t>
+        </is>
+      </c>
+      <c r="E63" s="26" t="inlineStr">
+        <is>
+          <t>RF-36 / RF-18</t>
+        </is>
+      </c>
+      <c r="F63" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G63" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H63" s="26" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="I63" s="26" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="J63" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K63" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L63" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M08-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="30" t="inlineStr">
+        <is>
+          <t>HU-M09-01</t>
+        </is>
+      </c>
+      <c r="B64" s="26" t="inlineStr">
+        <is>
+          <t>M-09.1</t>
+        </is>
+      </c>
+      <c r="C64" s="26" t="inlineStr">
+        <is>
+          <t>M-09</t>
+        </is>
+      </c>
+      <c r="D64" s="26" t="inlineStr">
+        <is>
+          <t>Frontera de notificacion del backend</t>
+        </is>
+      </c>
+      <c r="E64" s="26" t="inlineStr">
+        <is>
+          <t>RF-20</t>
+        </is>
+      </c>
+      <c r="F64" s="26" t="inlineStr">
+        <is>
+          <t>Front contra mock</t>
+        </is>
+      </c>
+      <c r="G64" s="26" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H64" s="26" t="inlineStr">
+        <is>
+          <t>Nicolas Leon</t>
+        </is>
+      </c>
+      <c r="I64" s="26" t="inlineStr">
+        <is>
+          <t>Nicolas Leon</t>
+        </is>
+      </c>
+      <c r="J64" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K64" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L64" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="30" t="inlineStr">
+        <is>
+          <t>HU-M09-02</t>
+        </is>
+      </c>
+      <c r="B65" s="26" t="inlineStr">
+        <is>
+          <t>M-09.2</t>
+        </is>
+      </c>
+      <c r="C65" s="26" t="inlineStr">
+        <is>
+          <t>M-09</t>
+        </is>
+      </c>
+      <c r="D65" s="26" t="inlineStr">
+        <is>
+          <t>Mensajeria cliente-aliado por servicio</t>
+        </is>
+      </c>
+      <c r="E65" s="26" t="inlineStr">
+        <is>
+          <t>RF-20</t>
+        </is>
+      </c>
+      <c r="F65" s="26" t="inlineStr">
+        <is>
+          <t>Front contra mock</t>
+        </is>
+      </c>
+      <c r="G65" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H65" s="26" t="inlineStr">
+        <is>
+          <t>Nicolas Leon</t>
+        </is>
+      </c>
+      <c r="I65" s="26" t="inlineStr">
+        <is>
+          <t>Nicolas Leon</t>
+        </is>
+      </c>
+      <c r="J65" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K65" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L65" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="30" t="inlineStr">
+        <is>
+          <t>HU-M09-03</t>
+        </is>
+      </c>
+      <c r="B66" s="26" t="inlineStr">
+        <is>
+          <t>M-09.3</t>
+        </is>
+      </c>
+      <c r="C66" s="26" t="inlineStr">
+        <is>
+          <t>M-09</t>
+        </is>
+      </c>
+      <c r="D66" s="26" t="inlineStr">
+        <is>
+          <t>Notificaciones de mensajes nuevos</t>
+        </is>
+      </c>
+      <c r="E66" s="26" t="inlineStr">
+        <is>
+          <t>RF-20</t>
+        </is>
+      </c>
+      <c r="F66" s="26" t="inlineStr">
+        <is>
+          <t>Front contra mock</t>
+        </is>
+      </c>
+      <c r="G66" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H66" s="26" t="inlineStr">
+        <is>
+          <t>Nicolas Leon</t>
+        </is>
+      </c>
+      <c r="I66" s="26" t="inlineStr">
+        <is>
+          <t>Nicolas Leon</t>
+        </is>
+      </c>
+      <c r="J66" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K66" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L66" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M09-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="30" t="inlineStr">
+        <is>
+          <t>HU-M09-04</t>
+        </is>
+      </c>
+      <c r="B67" s="26" t="inlineStr">
+        <is>
+          <t>M-09.4</t>
+        </is>
+      </c>
+      <c r="C67" s="26" t="inlineStr">
+        <is>
+          <t>M-09</t>
+        </is>
+      </c>
+      <c r="D67" s="26" t="inlineStr">
+        <is>
           <t>Consultar la conversacion para atender una queja</t>
         </is>
       </c>
-      <c r="E63" s="26" t="inlineStr">
-        <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="31" t="inlineStr">
-        <is>
-          <t>QA-CONS-38</t>
-        </is>
-      </c>
-      <c r="B64" s="26" t="inlineStr">
-        <is>
-          <t>CONS-38</t>
-        </is>
-      </c>
-      <c r="C64" s="26" t="inlineStr">
-        <is>
-          <t>Construccion</t>
-        </is>
-      </c>
-      <c r="D64" s="26" t="inlineStr">
-        <is>
-          <t>Mock de la pasarela de pagos</t>
-        </is>
-      </c>
-      <c r="E64" s="26" t="inlineStr">
-        <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="31" t="inlineStr">
-        <is>
-          <t>QA-CONS-39</t>
-        </is>
-      </c>
-      <c r="B65" s="26" t="inlineStr">
-        <is>
-          <t>CONS-39</t>
-        </is>
-      </c>
-      <c r="C65" s="26" t="inlineStr">
-        <is>
-          <t>Construccion</t>
-        </is>
-      </c>
-      <c r="D65" s="26" t="inlineStr">
-        <is>
-          <t>Registro inmutable de transacciones</t>
-        </is>
-      </c>
-      <c r="E65" s="26" t="inlineStr">
-        <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="31" t="inlineStr">
-        <is>
-          <t>QA-CONS-40</t>
-        </is>
-      </c>
-      <c r="B66" s="26" t="inlineStr">
-        <is>
-          <t>CONS-40</t>
-        </is>
-      </c>
-      <c r="C66" s="26" t="inlineStr">
-        <is>
-          <t>Construccion</t>
-        </is>
-      </c>
-      <c r="D66" s="26" t="inlineStr">
-        <is>
-          <t>Liquidacion al aliado con comision configurable</t>
-        </is>
-      </c>
-      <c r="E66" s="26" t="inlineStr">
-        <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="31" t="inlineStr">
-        <is>
-          <t>QA-CONS-41</t>
-        </is>
-      </c>
-      <c r="B67" s="26" t="inlineStr">
-        <is>
-          <t>CONS-41</t>
-        </is>
-      </c>
-      <c r="C67" s="26" t="inlineStr">
-        <is>
-          <t>Construccion</t>
-        </is>
-      </c>
-      <c r="D67" s="26" t="inlineStr">
-        <is>
-          <t>Registro y gestion de quejas</t>
-        </is>
-      </c>
       <c r="E67" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-21</t>
+        </is>
+      </c>
+      <c r="F67" s="26" t="inlineStr">
+        <is>
+          <t>Front contra mock</t>
+        </is>
+      </c>
+      <c r="G67" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H67" s="26" t="inlineStr">
+        <is>
+          <t>Nicolas Leon</t>
+        </is>
+      </c>
+      <c r="I67" s="26" t="inlineStr">
+        <is>
+          <t>Nicolas Leon</t>
+        </is>
+      </c>
+      <c r="J67" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K67" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L67" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M09-04</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="31" t="inlineStr">
-        <is>
-          <t>QA-CONS-42</t>
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>HU-M09-05</t>
         </is>
       </c>
       <c r="B68" s="26" t="inlineStr">
         <is>
-          <t>CONS-42</t>
+          <t>M-09.5</t>
         </is>
       </c>
       <c r="C68" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-09</t>
         </is>
       </c>
       <c r="D68" s="26" t="inlineStr">
         <is>
-          <t>Metricas operativas por tenant y endpoint /metrics</t>
+          <t>Notificaciones push de los eventos del ciclo del servicio</t>
         </is>
       </c>
       <c r="E68" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-20</t>
+        </is>
+      </c>
+      <c r="F68" s="26" t="inlineStr">
+        <is>
+          <t>Front contra mock</t>
+        </is>
+      </c>
+      <c r="G68" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H68" s="26" t="inlineStr">
+        <is>
+          <t>Nicolas Leon</t>
+        </is>
+      </c>
+      <c r="I68" s="26" t="inlineStr">
+        <is>
+          <t>Nicolas Leon</t>
+        </is>
+      </c>
+      <c r="J68" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K68" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L68" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M09-05</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>QA-CONS-43</t>
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>HU-M09-06</t>
         </is>
       </c>
       <c r="B69" s="26" t="inlineStr">
         <is>
-          <t>CONS-43</t>
+          <t>M-09.6</t>
         </is>
       </c>
       <c r="C69" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-09</t>
         </is>
       </c>
       <c r="D69" s="26" t="inlineStr">
         <is>
-          <t>Administrar el estado de los tenants</t>
+          <t>Mock del proveedor de notificaciones push en el backend</t>
         </is>
       </c>
       <c r="E69" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-20</t>
+        </is>
+      </c>
+      <c r="F69" s="26" t="inlineStr">
+        <is>
+          <t>Front contra mock</t>
+        </is>
+      </c>
+      <c r="G69" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H69" s="26" t="inlineStr">
+        <is>
+          <t>Nicolas Leon</t>
+        </is>
+      </c>
+      <c r="I69" s="26" t="inlineStr">
+        <is>
+          <t>Nicolas Leon</t>
+        </is>
+      </c>
+      <c r="J69" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K69" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L69" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M09-06</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>QA-CONS-44</t>
+          <t>HU-M10-01</t>
         </is>
       </c>
       <c r="B70" s="26" t="inlineStr">
         <is>
-          <t>CONS-44</t>
+          <t>M-10.1</t>
         </is>
       </c>
       <c r="C70" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-10</t>
         </is>
       </c>
       <c r="D70" s="26" t="inlineStr">
         <is>
-          <t>Configuracion de reglas por tenant sin despliegue</t>
+          <t>Cargar la tabla de tarifas por categoria</t>
         </is>
       </c>
       <c r="E70" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-22</t>
+        </is>
+      </c>
+      <c r="F70" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G70" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H70" s="26" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="I70" s="26" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="J70" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K70" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L70" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M10-01</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>QA-CONS-45</t>
+          <t>HU-M10-02</t>
         </is>
       </c>
       <c r="B71" s="26" t="inlineStr">
         <is>
-          <t>CONS-45</t>
+          <t>M-10.2</t>
         </is>
       </c>
       <c r="C71" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-10</t>
         </is>
       </c>
       <c r="D71" s="26" t="inlineStr">
         <is>
-          <t>Cifrado y manejo de secretos verificado de punta a punta</t>
+          <t>Ver la tarifa de referencia al cotizar</t>
         </is>
       </c>
       <c r="E71" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-22 / RF-16</t>
+        </is>
+      </c>
+      <c r="F71" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G71" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H71" s="26" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="I71" s="26" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="J71" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K71" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L71" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M10-02</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>QA-CONS-46</t>
+          <t>HU-M10-03</t>
         </is>
       </c>
       <c r="B72" s="26" t="inlineStr">
         <is>
-          <t>CONS-46</t>
+          <t>M-10.3</t>
         </is>
       </c>
       <c r="C72" s="26" t="inlineStr">
         <is>
-          <t>Construccion</t>
+          <t>M-10</t>
         </is>
       </c>
       <c r="D72" s="26" t="inlineStr">
         <is>
-          <t>Alta y administracion de tenants por el administrador de plataforma</t>
+          <t>Reporte de cotizaciones fuera de rango por periodo</t>
         </is>
       </c>
       <c r="E72" s="26" t="inlineStr">
         <is>
-          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
+          <t>RF-23</t>
+        </is>
+      </c>
+      <c r="F72" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G72" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H72" s="26" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="I72" s="26" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="J72" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K72" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L72" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M10-03</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="29" t="inlineStr">
-        <is>
-          <t>QA-TEC-01</t>
+      <c r="A73" s="30" t="inlineStr">
+        <is>
+          <t>HU-M11-01</t>
         </is>
       </c>
       <c r="B73" s="26" t="inlineStr">
         <is>
-          <t>TEC-01</t>
+          <t>M-11.1</t>
         </is>
       </c>
       <c r="C73" s="26" t="inlineStr">
         <is>
-          <t>Tarea tecnica</t>
+          <t>M-11</t>
         </is>
       </c>
       <c r="D73" s="26" t="inlineStr">
         <is>
-          <t>Cerrar la contradiccion documental sobre quien crea la solicitud</t>
+          <t>Mock de la pasarela de pagos (sandbox simulado)</t>
         </is>
       </c>
       <c r="E73" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+          <t>RF-24 / REST-03</t>
+        </is>
+      </c>
+      <c r="F73" s="26" t="inlineStr">
+        <is>
+          <t>Front contra mock</t>
+        </is>
+      </c>
+      <c r="G73" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H73" s="26" t="inlineStr">
+        <is>
+          <t>Nicolas Leon</t>
+        </is>
+      </c>
+      <c r="I73" s="26" t="inlineStr">
+        <is>
+          <t>Nicolas Leon</t>
+        </is>
+      </c>
+      <c r="J73" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K73" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L73" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M11-01</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="29" t="inlineStr">
-        <is>
-          <t>QA-TEC-02</t>
+      <c r="A74" s="30" t="inlineStr">
+        <is>
+          <t>HU-M11-02</t>
         </is>
       </c>
       <c r="B74" s="26" t="inlineStr">
         <is>
-          <t>TEC-02</t>
+          <t>M-11.2</t>
         </is>
       </c>
       <c r="C74" s="26" t="inlineStr">
         <is>
-          <t>Tarea tecnica</t>
+          <t>M-11</t>
         </is>
       </c>
       <c r="D74" s="26" t="inlineStr">
         <is>
-          <t>Fijar el contexto de identidad en cada transaccion de Dispatch</t>
+          <t>Pago en linea al aceptar la cotizacion</t>
         </is>
       </c>
       <c r="E74" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+          <t>RF-24 / RNF-06 / RNF-11 / REST-03</t>
+        </is>
+      </c>
+      <c r="F74" s="26" t="inlineStr">
+        <is>
+          <t>Front contra mock</t>
+        </is>
+      </c>
+      <c r="G74" s="26" t="inlineStr">
+        <is>
+          <t>To Do (2do incremento)</t>
+        </is>
+      </c>
+      <c r="H74" s="26" t="inlineStr">
+        <is>
+          <t>Nicolas Leon</t>
+        </is>
+      </c>
+      <c r="I74" s="26" t="inlineStr">
+        <is>
+          <t>Nicolas Leon</t>
+        </is>
+      </c>
+      <c r="J74" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K74" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L74" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M11-02</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="29" t="inlineStr">
-        <is>
-          <t>QA-TEC-03</t>
+      <c r="A75" s="30" t="inlineStr">
+        <is>
+          <t>HU-M11-03</t>
         </is>
       </c>
       <c r="B75" s="26" t="inlineStr">
         <is>
-          <t>TEC-03</t>
+          <t>M-11.3</t>
         </is>
       </c>
       <c r="C75" s="26" t="inlineStr">
         <is>
-          <t>Tarea tecnica</t>
+          <t>M-11</t>
         </is>
       </c>
       <c r="D75" s="26" t="inlineStr">
         <is>
-          <t>Corregir la politica de solicitud_rechazo</t>
+          <t>Registro inmutable de transacciones</t>
         </is>
       </c>
       <c r="E75" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+          <t>RF-24 / RNF-04</t>
+        </is>
+      </c>
+      <c r="F75" s="26" t="inlineStr">
+        <is>
+          <t>Front contra mock</t>
+        </is>
+      </c>
+      <c r="G75" s="26" t="inlineStr">
+        <is>
+          <t>To Do (2do incremento)</t>
+        </is>
+      </c>
+      <c r="H75" s="26" t="inlineStr">
+        <is>
+          <t>Nicolas Leon</t>
+        </is>
+      </c>
+      <c r="I75" s="26" t="inlineStr">
+        <is>
+          <t>Nicolas Leon</t>
+        </is>
+      </c>
+      <c r="J75" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K75" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L75" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M11-03</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="29" t="inlineStr">
-        <is>
-          <t>QA-TEC-04</t>
+      <c r="A76" s="30" t="inlineStr">
+        <is>
+          <t>HU-M11-04</t>
         </is>
       </c>
       <c r="B76" s="26" t="inlineStr">
         <is>
-          <t>TEC-04</t>
+          <t>M-11.4</t>
         </is>
       </c>
       <c r="C76" s="26" t="inlineStr">
         <is>
-          <t>Tarea tecnica</t>
+          <t>M-11</t>
         </is>
       </c>
       <c r="D76" s="26" t="inlineStr">
         <is>
-          <t>Paginar el broadcast y hacer idempotente el reintento parcial</t>
+          <t>Descargar soporte de pago</t>
         </is>
       </c>
       <c r="E76" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+          <t>RF-24</t>
+        </is>
+      </c>
+      <c r="F76" s="26" t="inlineStr">
+        <is>
+          <t>Front contra mock</t>
+        </is>
+      </c>
+      <c r="G76" s="26" t="inlineStr">
+        <is>
+          <t>To Do (2do incremento)</t>
+        </is>
+      </c>
+      <c r="H76" s="26" t="inlineStr">
+        <is>
+          <t>Nicolas Leon</t>
+        </is>
+      </c>
+      <c r="I76" s="26" t="inlineStr">
+        <is>
+          <t>Nicolas Leon</t>
+        </is>
+      </c>
+      <c r="J76" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K76" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L76" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M11-04</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="29" t="inlineStr">
-        <is>
-          <t>QA-TEC-05</t>
+      <c r="A77" s="30" t="inlineStr">
+        <is>
+          <t>HU-M11-05</t>
         </is>
       </c>
       <c r="B77" s="26" t="inlineStr">
         <is>
-          <t>TEC-05</t>
+          <t>M-11.5</t>
         </is>
       </c>
       <c r="C77" s="26" t="inlineStr">
         <is>
-          <t>Tarea tecnica</t>
+          <t>M-11</t>
         </is>
       </c>
       <c r="D77" s="26" t="inlineStr">
         <is>
-          <t>Distinguir conflicto de asignacion de conflicto de estado</t>
+          <t>Retencion de fondos en garantia (escrow)</t>
         </is>
       </c>
       <c r="E77" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+          <t>RF-24 / RNF-11</t>
+        </is>
+      </c>
+      <c r="F77" s="26" t="inlineStr">
+        <is>
+          <t>Front contra mock</t>
+        </is>
+      </c>
+      <c r="G77" s="26" t="inlineStr">
+        <is>
+          <t>To Do (2do incremento)</t>
+        </is>
+      </c>
+      <c r="H77" s="26" t="inlineStr">
+        <is>
+          <t>Nicolas Leon</t>
+        </is>
+      </c>
+      <c r="I77" s="26" t="inlineStr">
+        <is>
+          <t>Nicolas Leon</t>
+        </is>
+      </c>
+      <c r="J77" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K77" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L77" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M11-05</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="29" t="inlineStr">
-        <is>
-          <t>QA-TEC-06</t>
+      <c r="A78" s="30" t="inlineStr">
+        <is>
+          <t>HU-M11-06</t>
         </is>
       </c>
       <c r="B78" s="26" t="inlineStr">
         <is>
-          <t>TEC-06</t>
+          <t>M-11.6</t>
         </is>
       </c>
       <c r="C78" s="26" t="inlineStr">
         <is>
-          <t>Tarea tecnica</t>
+          <t>M-11</t>
         </is>
       </c>
       <c r="D78" s="26" t="inlineStr">
         <is>
-          <t>Declarar CORE_SERVICE_URL en manifiestos versionados</t>
+          <t>Liberacion automatica de fondos</t>
         </is>
       </c>
       <c r="E78" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+          <t>RF-24</t>
+        </is>
+      </c>
+      <c r="F78" s="26" t="inlineStr">
+        <is>
+          <t>Front contra mock</t>
+        </is>
+      </c>
+      <c r="G78" s="26" t="inlineStr">
+        <is>
+          <t>To Do (2do incremento)</t>
+        </is>
+      </c>
+      <c r="H78" s="26" t="inlineStr">
+        <is>
+          <t>Nicolas Leon</t>
+        </is>
+      </c>
+      <c r="I78" s="26" t="inlineStr">
+        <is>
+          <t>Nicolas Leon</t>
+        </is>
+      </c>
+      <c r="J78" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K78" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L78" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M11-06</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="29" t="inlineStr">
-        <is>
-          <t>QA-TEC-07</t>
+      <c r="A79" s="30" t="inlineStr">
+        <is>
+          <t>HU-M11-07</t>
         </is>
       </c>
       <c r="B79" s="26" t="inlineStr">
         <is>
-          <t>TEC-07</t>
+          <t>M-11.7</t>
         </is>
       </c>
       <c r="C79" s="26" t="inlineStr">
         <is>
-          <t>Tarea tecnica</t>
+          <t>M-11</t>
         </is>
       </c>
       <c r="D79" s="26" t="inlineStr">
         <is>
-          <t>Unificar la politica de token de Dispatch con la de Core</t>
+          <t>Liquidacion al aliado descontando comision configurable</t>
         </is>
       </c>
       <c r="E79" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+          <t>RF-25 / RNF-10 / REST-05</t>
+        </is>
+      </c>
+      <c r="F79" s="26" t="inlineStr">
+        <is>
+          <t>Front contra mock</t>
+        </is>
+      </c>
+      <c r="G79" s="26" t="inlineStr">
+        <is>
+          <t>To Do (2do incremento)</t>
+        </is>
+      </c>
+      <c r="H79" s="26" t="inlineStr">
+        <is>
+          <t>Nicolas Leon</t>
+        </is>
+      </c>
+      <c r="I79" s="26" t="inlineStr">
+        <is>
+          <t>Nicolas Leon</t>
+        </is>
+      </c>
+      <c r="J79" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K79" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L79" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M11-07</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="29" t="inlineStr">
-        <is>
-          <t>QA-TEC-08</t>
+      <c r="A80" s="30" t="inlineStr">
+        <is>
+          <t>HU-M11-08</t>
         </is>
       </c>
       <c r="B80" s="26" t="inlineStr">
         <is>
-          <t>TEC-08</t>
+          <t>M-11.8</t>
         </is>
       </c>
       <c r="C80" s="26" t="inlineStr">
         <is>
-          <t>Tarea tecnica</t>
+          <t>M-11</t>
         </is>
       </c>
       <c r="D80" s="26" t="inlineStr">
         <is>
-          <t>Documentar el salto de numeracion de migraciones y recuperar 0012</t>
+          <t>Aliado consulta el detalle de sus pagos</t>
         </is>
       </c>
       <c r="E80" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+          <t>RF-25</t>
+        </is>
+      </c>
+      <c r="F80" s="26" t="inlineStr">
+        <is>
+          <t>Front contra mock</t>
+        </is>
+      </c>
+      <c r="G80" s="26" t="inlineStr">
+        <is>
+          <t>To Do (2do incremento)</t>
+        </is>
+      </c>
+      <c r="H80" s="26" t="inlineStr">
+        <is>
+          <t>Nicolas Leon</t>
+        </is>
+      </c>
+      <c r="I80" s="26" t="inlineStr">
+        <is>
+          <t>Nicolas Leon</t>
+        </is>
+      </c>
+      <c r="J80" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K80" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L80" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M11-08</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="29" t="inlineStr">
-        <is>
-          <t>QA-TEC-09</t>
+      <c r="A81" s="31" t="inlineStr">
+        <is>
+          <t>HU-M12-01</t>
         </is>
       </c>
       <c r="B81" s="26" t="inlineStr">
         <is>
-          <t>TEC-09</t>
+          <t>M-12.1</t>
         </is>
       </c>
       <c r="C81" s="26" t="inlineStr">
         <is>
-          <t>Tarea tecnica</t>
+          <t>M-12</t>
         </is>
       </c>
       <c r="D81" s="26" t="inlineStr">
         <is>
-          <t>Cerrar dev-token y la ruta publica de validate-token en el Gateway, y rotar secretos</t>
+          <t>Cliente registra una queja</t>
         </is>
       </c>
       <c r="E81" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+          <t>RF-26</t>
+        </is>
+      </c>
+      <c r="F81" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G81" s="26" t="inlineStr">
+        <is>
+          <t>To Do (2do incremento)</t>
+        </is>
+      </c>
+      <c r="H81" s="26" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="I81" s="26" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="J81" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K81" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L81" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M12-01</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="29" t="inlineStr">
-        <is>
-          <t>QA-TEC-10</t>
+      <c r="A82" s="31" t="inlineStr">
+        <is>
+          <t>HU-M12-02</t>
         </is>
       </c>
       <c r="B82" s="26" t="inlineStr">
         <is>
-          <t>TEC-10</t>
+          <t>M-12.2</t>
         </is>
       </c>
       <c r="C82" s="26" t="inlineStr">
         <is>
-          <t>Tarea tecnica</t>
+          <t>M-12</t>
         </is>
       </c>
       <c r="D82" s="26" t="inlineStr">
         <is>
-          <t>Un solo validador de token, con ES256, iss y aud</t>
+          <t>Tenant gestiona el estado de las quejas</t>
         </is>
       </c>
       <c r="E82" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+          <t>RF-26</t>
+        </is>
+      </c>
+      <c r="F82" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G82" s="26" t="inlineStr">
+        <is>
+          <t>To Do (2do incremento)</t>
+        </is>
+      </c>
+      <c r="H82" s="26" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="I82" s="26" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="J82" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K82" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L82" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M12-02</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="29" t="inlineStr">
-        <is>
-          <t>QA-TEC-11</t>
+      <c r="A83" s="32" t="inlineStr">
+        <is>
+          <t>HU-M12-03</t>
         </is>
       </c>
       <c r="B83" s="26" t="inlineStr">
         <is>
-          <t>TEC-11</t>
+          <t>M-12.3</t>
         </is>
       </c>
       <c r="C83" s="26" t="inlineStr">
         <is>
-          <t>Tarea tecnica</t>
+          <t>M-12</t>
         </is>
       </c>
       <c r="D83" s="26" t="inlineStr">
         <is>
-          <t>Confirmar o montar TLS en el borde</t>
+          <t>Resolucion de disputa financiera</t>
         </is>
       </c>
       <c r="E83" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
-        </is>
-      </c>
+          <t>RF-26 / RF-24</t>
+        </is>
+      </c>
+      <c r="F83" s="26" t="inlineStr">
+        <is>
+          <t>Fuera de alcance</t>
+        </is>
+      </c>
+      <c r="G83" s="26" t="inlineStr">
+        <is>
+          <t>To Do (2do incremento)</t>
+        </is>
+      </c>
+      <c r="H83" s="26" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="I83" s="26" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="J83" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" s="26" t="inlineStr">
+        <is>
+          <t>Fuera: 2.o incremento</t>
+        </is>
+      </c>
+      <c r="L83" s="26" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="29" t="inlineStr">
-        <is>
-          <t>QA-TEC-12</t>
+      <c r="A84" s="32" t="inlineStr">
+        <is>
+          <t>HU-M12-04</t>
         </is>
       </c>
       <c r="B84" s="26" t="inlineStr">
         <is>
-          <t>TEC-12</t>
+          <t>M-12.4</t>
         </is>
       </c>
       <c r="C84" s="26" t="inlineStr">
         <is>
-          <t>Tarea tecnica</t>
+          <t>M-12</t>
         </is>
       </c>
       <c r="D84" s="26" t="inlineStr">
         <is>
-          <t>Ratificar ADR-0030 y ADR-0016 en Mesa</t>
+          <t>Publicar contenido en redes conectadas</t>
         </is>
       </c>
       <c r="E84" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
-        </is>
-      </c>
+          <t>RF-27</t>
+        </is>
+      </c>
+      <c r="F84" s="26" t="inlineStr">
+        <is>
+          <t>Fuera de alcance</t>
+        </is>
+      </c>
+      <c r="G84" s="26" t="inlineStr">
+        <is>
+          <t>To Do (2do incremento)</t>
+        </is>
+      </c>
+      <c r="H84" s="26" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="I84" s="26" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="J84" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="26" t="inlineStr">
+        <is>
+          <t>Fuera: 2.o incremento</t>
+        </is>
+      </c>
+      <c r="L84" s="26" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="29" t="inlineStr">
-        <is>
-          <t>QA-TEC-13</t>
+      <c r="A85" s="32" t="inlineStr">
+        <is>
+          <t>HU-M12-05</t>
         </is>
       </c>
       <c r="B85" s="26" t="inlineStr">
         <is>
-          <t>TEC-13</t>
+          <t>M-12.5</t>
         </is>
       </c>
       <c r="C85" s="26" t="inlineStr">
         <is>
-          <t>Tarea tecnica</t>
+          <t>M-12</t>
         </is>
       </c>
       <c r="D85" s="26" t="inlineStr">
         <is>
-          <t>Definir identidad de servicio entre Dispatch y Core</t>
+          <t>Registrar campanas y ver su desempeno</t>
         </is>
       </c>
       <c r="E85" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
-        </is>
-      </c>
+          <t>RF-27</t>
+        </is>
+      </c>
+      <c r="F85" s="26" t="inlineStr">
+        <is>
+          <t>Fuera de alcance</t>
+        </is>
+      </c>
+      <c r="G85" s="26" t="inlineStr">
+        <is>
+          <t>To Do (2do incremento)</t>
+        </is>
+      </c>
+      <c r="H85" s="26" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="I85" s="26" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="J85" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="26" t="inlineStr">
+        <is>
+          <t>Fuera: 2.o incremento</t>
+        </is>
+      </c>
+      <c r="L85" s="26" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="29" t="inlineStr">
-        <is>
-          <t>QA-TEC-14</t>
+      <c r="A86" s="31" t="inlineStr">
+        <is>
+          <t>HU-M12-06</t>
         </is>
       </c>
       <c r="B86" s="26" t="inlineStr">
         <is>
-          <t>TEC-14</t>
+          <t>M-12.6</t>
         </is>
       </c>
       <c r="C86" s="26" t="inlineStr">
         <is>
-          <t>Tarea tecnica</t>
+          <t>M-12</t>
         </is>
       </c>
       <c r="D86" s="26" t="inlineStr">
         <is>
-          <t>Observabilidad minima de autenticacion</t>
+          <t>Metricas operativas por tenant</t>
         </is>
       </c>
       <c r="E86" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+          <t>RF-28</t>
+        </is>
+      </c>
+      <c r="F86" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G86" s="26" t="inlineStr">
+        <is>
+          <t>To Do (2do incremento)</t>
+        </is>
+      </c>
+      <c r="H86" s="26" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="I86" s="26" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="J86" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K86" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L86" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M12-06</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="29" t="inlineStr">
-        <is>
-          <t>QA-TEC-15</t>
+      <c r="A87" s="31" t="inlineStr">
+        <is>
+          <t>HU-M12-07</t>
         </is>
       </c>
       <c r="B87" s="26" t="inlineStr">
         <is>
-          <t>TEC-15</t>
+          <t>M-12.7</t>
         </is>
       </c>
       <c r="C87" s="26" t="inlineStr">
         <is>
-          <t>Tarea tecnica</t>
+          <t>M-12</t>
         </is>
       </c>
       <c r="D87" s="26" t="inlineStr">
         <is>
-          <t>Crear el repositorio del Rules Service</t>
+          <t>Administrar el estado de los tenants</t>
         </is>
       </c>
       <c r="E87" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+          <t>RF-28 / RF-01</t>
+        </is>
+      </c>
+      <c r="F87" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G87" s="26" t="inlineStr">
+        <is>
+          <t>To Do (2do incremento)</t>
+        </is>
+      </c>
+      <c r="H87" s="26" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="I87" s="26" t="inlineStr">
+        <is>
+          <t>Juan Sebastian Alvarez</t>
+        </is>
+      </c>
+      <c r="J87" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K87" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L87" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M12-07</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="29" t="inlineStr">
-        <is>
-          <t>QA-TEC-16</t>
+      <c r="A88" s="31" t="inlineStr">
+        <is>
+          <t>HU-M13-01</t>
         </is>
       </c>
       <c r="B88" s="26" t="inlineStr">
         <is>
-          <t>TEC-16</t>
+          <t>M-13.1</t>
         </is>
       </c>
       <c r="C88" s="26" t="inlineStr">
         <is>
-          <t>Tarea tecnica</t>
+          <t>M-13</t>
         </is>
       </c>
       <c r="D88" s="26" t="inlineStr">
         <is>
-          <t>Preparar el ambiente QA y los datos sembrados del sprint de validacion</t>
+          <t>Menu superior por rol, con sesion visible y logout accesible</t>
         </is>
       </c>
       <c r="E88" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+          <t>RNF-08</t>
+        </is>
+      </c>
+      <c r="F88" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G88" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H88" s="26" t="inlineStr">
+        <is>
+          <t>Jose Nicolas Alvarez</t>
+        </is>
+      </c>
+      <c r="I88" s="26" t="inlineStr">
+        <is>
+          <t>Jose Nicolas Alvarez</t>
+        </is>
+      </c>
+      <c r="J88" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K88" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L88" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M13-01</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="29" t="inlineStr">
         <is>
-          <t>QA-TEC-17</t>
+          <t>HU-M13-02</t>
         </is>
       </c>
       <c r="B89" s="26" t="inlineStr">
         <is>
-          <t>TEC-17</t>
+          <t>M-13.2</t>
         </is>
       </c>
       <c r="C89" s="26" t="inlineStr">
         <is>
-          <t>Tarea tecnica</t>
+          <t>M-13</t>
         </is>
       </c>
       <c r="D89" s="26" t="inlineStr">
         <is>
-          <t>Guia de grabacion y repositorio de videos</t>
+          <t>Enrutamiento por rol con guardas de sesion y expiracion</t>
         </is>
       </c>
       <c r="E89" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+          <t>RF-03</t>
+        </is>
+      </c>
+      <c r="F89" s="26" t="inlineStr">
+        <is>
+          <t>Correccion + validacion</t>
+        </is>
+      </c>
+      <c r="G89" s="26" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="H89" s="26" t="inlineStr">
+        <is>
+          <t>Jose Nicolas Alvarez</t>
+        </is>
+      </c>
+      <c r="I89" s="26" t="inlineStr">
+        <is>
+          <t>Jose Nicolas Alvarez</t>
+        </is>
+      </c>
+      <c r="J89" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K89" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L89" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M13-02</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="29" t="inlineStr">
-        <is>
-          <t>QA-TEC-18</t>
+      <c r="A90" s="31" t="inlineStr">
+        <is>
+          <t>HU-M13-03</t>
         </is>
       </c>
       <c r="B90" s="26" t="inlineStr">
         <is>
-          <t>TEC-18</t>
+          <t>M-13.3</t>
         </is>
       </c>
       <c r="C90" s="26" t="inlineStr">
         <is>
-          <t>Tarea tecnica</t>
+          <t>M-13</t>
         </is>
       </c>
       <c r="D90" s="26" t="inlineStr">
         <is>
-          <t>Migrar el front de solicitudes y asignacion al camino Gateway-Core</t>
+          <t>Pantalla de inicio por tipo de usuario</t>
         </is>
       </c>
       <c r="E90" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+          <t>RNF-08</t>
+        </is>
+      </c>
+      <c r="F90" s="26" t="inlineStr">
+        <is>
+          <t>Construccion desde 0</t>
+        </is>
+      </c>
+      <c r="G90" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H90" s="26" t="inlineStr">
+        <is>
+          <t>Jose Nicolas Alvarez</t>
+        </is>
+      </c>
+      <c r="I90" s="26" t="inlineStr">
+        <is>
+          <t>Jose Nicolas Alvarez</t>
+        </is>
+      </c>
+      <c r="J90" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K90" s="26" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L90" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M13-03</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="29" t="inlineStr">
-        <is>
-          <t>QA-TEC-19</t>
+      <c r="A91" s="32" t="inlineStr">
+        <is>
+          <t>HU-M13-04</t>
         </is>
       </c>
       <c r="B91" s="26" t="inlineStr">
         <is>
-          <t>TEC-19</t>
+          <t>M-13.4</t>
         </is>
       </c>
       <c r="C91" s="26" t="inlineStr">
         <is>
-          <t>Tarea tecnica</t>
+          <t>M-13</t>
         </is>
       </c>
       <c r="D91" s="26" t="inlineStr">
         <is>
-          <t>Migracion de usuario para direccion y foto de perfil</t>
+          <t>Dividir el front en modulos independientes por dominio</t>
         </is>
       </c>
       <c r="E91" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
-        </is>
-      </c>
+          <t>PROY-05 / RNF-02</t>
+        </is>
+      </c>
+      <c r="F91" s="26" t="inlineStr">
+        <is>
+          <t>Fuera de alcance</t>
+        </is>
+      </c>
+      <c r="G91" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H91" s="26" t="inlineStr">
+        <is>
+          <t>Jose Nicolas Alvarez</t>
+        </is>
+      </c>
+      <c r="I91" s="26" t="inlineStr">
+        <is>
+          <t>Jose Nicolas Alvarez</t>
+        </is>
+      </c>
+      <c r="J91" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" s="26" t="inlineStr">
+        <is>
+          <t>Fuera: refactor del front, no cambia si el producto funciona</t>
+        </is>
+      </c>
+      <c r="L91" s="26" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="29" t="inlineStr">
-        <is>
-          <t>QA-TEC-20</t>
+      <c r="A92" s="32" t="inlineStr">
+        <is>
+          <t>HU-M13-05</t>
         </is>
       </c>
       <c r="B92" s="26" t="inlineStr">
         <is>
-          <t>TEC-20</t>
+          <t>M-13.5</t>
         </is>
       </c>
       <c r="C92" s="26" t="inlineStr">
         <is>
-          <t>Tarea tecnica</t>
+          <t>M-13</t>
         </is>
       </c>
       <c r="D92" s="26" t="inlineStr">
         <is>
-          <t>Persistir verificado_por en el adaptador real</t>
+          <t>Dividir el Core por dominios internos sin crear un servicio por CRUD</t>
         </is>
       </c>
       <c r="E92" s="26" t="inlineStr">
         <is>
-          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="29" t="inlineStr">
-        <is>
-          <t>QA-TEC-21</t>
-        </is>
-      </c>
-      <c r="B93" s="26" t="inlineStr">
-        <is>
-          <t>TEC-21</t>
-        </is>
-      </c>
-      <c r="C93" s="26" t="inlineStr">
-        <is>
-          <t>Tarea tecnica</t>
-        </is>
-      </c>
-      <c r="D93" s="26" t="inlineStr">
-        <is>
-          <t>Retirar BYPASSRLS: Core y Dispatch conectan con un rol de servicio sin privilegio de salto</t>
-        </is>
-      </c>
-      <c r="E93" s="26" t="inlineStr">
-        <is>
-          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="30" t="inlineStr">
-        <is>
-          <t>QA-SM-01</t>
-        </is>
-      </c>
-      <c r="B94" s="26" t="inlineStr">
-        <is>
-          <t>SM-01</t>
-        </is>
-      </c>
-      <c r="C94" s="26" t="inlineStr">
-        <is>
-          <t>Gestion</t>
-        </is>
-      </c>
-      <c r="D94" s="26" t="inlineStr">
-        <is>
-          <t>Sara Albarracin (Scrum Master)</t>
-        </is>
-      </c>
-      <c r="E94" s="26" t="inlineStr">
-        <is>
-          <t>Comprueba que el registro existe y es verificable: para SM-01, que las ceremonias, los impedimentos y los indicadores estan publicados y que ningun item se declaro terminado sin su subtarea de QA cerrada; para PO-01, que el acta de aceptacion lista explicitamente lo aceptado, lo rechazado y lo que queda fuera del incremento con su causa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="30" t="inlineStr">
-        <is>
-          <t>QA-PO-01</t>
-        </is>
-      </c>
-      <c r="B95" s="26" t="inlineStr">
-        <is>
-          <t>PO-01</t>
-        </is>
-      </c>
-      <c r="C95" s="26" t="inlineStr">
-        <is>
-          <t>Gestion</t>
-        </is>
-      </c>
-      <c r="D95" s="26" t="inlineStr">
-        <is>
-          <t>Camila Beltran (Product Owner)</t>
-        </is>
-      </c>
-      <c r="E95" s="26" t="inlineStr">
-        <is>
-          <t>Comprueba que el registro existe y es verificable: para SM-01, que las ceremonias, los impedimentos y los indicadores estan publicados y que ningun item se declaro terminado sin su subtarea de QA cerrada; para PO-01, que el acta de aceptacion lista explicitamente lo aceptado, lo rechazado y lo que queda fuera del incremento con su causa.</t>
-        </is>
-      </c>
+          <t>RNF-02 / ADR-0022</t>
+        </is>
+      </c>
+      <c r="F92" s="26" t="inlineStr">
+        <is>
+          <t>Fuera de alcance</t>
+        </is>
+      </c>
+      <c r="G92" s="26" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H92" s="26" t="inlineStr">
+        <is>
+          <t>Jose Nicolas Alvarez</t>
+        </is>
+      </c>
+      <c r="I92" s="26" t="inlineStr">
+        <is>
+          <t>Jose Nicolas Alvarez</t>
+        </is>
+      </c>
+      <c r="J92" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" s="26" t="inlineStr">
+        <is>
+          <t>Fuera: refactor del Core, no cambia si el producto funciona</t>
+        </is>
+      </c>
+      <c r="L92" s="26" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27922,6 +30323,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -28281,6 +30683,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -29158,6 +31561,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -29567,6 +31971,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -30029,6 +32434,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>

--- a/wiki/05-backlog/MANI_MODULOS_SERVICIOS_Y_BACKLOG_S5.xlsx
+++ b/wiki/05-backlog/MANI_MODULOS_SERVICIOS_Y_BACKLOG_S5.xlsx
@@ -882,7 +882,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -1357,7 +1356,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Fuera de alcance MVP</t>
+          <t>RF-37</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1372,7 +1371,7 @@
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>To Do (fuera de MVP)</t>
+          <t>To Do (entra al MVP el 24-oct-2026)</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1387,7 +1386,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>SRS §1.2 excluye geolocalizacion en tiempo real</t>
+          <t>SRS §4.4 RF-37; antes excluido por §1.2. Pendiente de confirmacion del PO</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1545,7 +1544,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2007,7 +2005,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2418,7 +2415,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2672,7 +2668,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3187,7 +3182,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3648,7 +3642,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -12189,10 +12182,10 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>382</v>
+        <v>398</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
@@ -12245,10 +12238,10 @@
       </c>
       <c r="B21" s="3" t="inlineStr"/>
       <c r="C21" s="21" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D21" s="21" t="n">
-        <v>485</v>
+        <v>501</v>
       </c>
     </row>
     <row r="22"/>
@@ -27476,7 +27469,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="32" t="inlineStr">
+      <c r="A54" s="31" t="inlineStr">
         <is>
           <t>HU-M07-04</t>
         </is>
@@ -27498,12 +27491,12 @@
       </c>
       <c r="E54" s="26" t="inlineStr">
         <is>
-          <t>Fuera de alcance MVP</t>
+          <t>RF-37</t>
         </is>
       </c>
       <c r="F54" s="26" t="inlineStr">
         <is>
-          <t>Fuera de alcance</t>
+          <t>Construccion desde 0</t>
         </is>
       </c>
       <c r="G54" s="26" t="inlineStr">
@@ -27522,14 +27515,18 @@
         </is>
       </c>
       <c r="J54" s="26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K54" s="26" t="inlineStr">
         <is>
-          <t>Fuera: rastreo en vivo esta fuera del MVP por SRS §1.2</t>
-        </is>
-      </c>
-      <c r="L54" s="26" t="inlineStr"/>
+          <t>Si — RF-37, creado el 24-oct-2026 al traerlo al sprint. Pendiente de confirmacion del PO: si lo revierte, la historia sale. La ubicacion es dato personal (Ley 1581 de 2012): permiso expreso del aliado, ventana limitada a la ejecucion y retencion configurable por tenant.</t>
+        </is>
+      </c>
+      <c r="L54" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M07-04</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="31" t="inlineStr">
@@ -29730,13 +29727,13 @@
       </c>
       <c r="K91" s="26" t="inlineStr">
         <is>
-          <t>Fuera: refactor del front, no cambia si el producto funciona</t>
+          <t>Fuera: dividir el front se queda fuera por decision del 24-oct-2026. El choque es menor que en Core porque cada modulo tiende a su propia pantalla. Se asume conflicto en lib/features.</t>
         </is>
       </c>
       <c r="L91" s="26" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="32" t="inlineStr">
+      <c r="A92" s="31" t="inlineStr">
         <is>
           <t>HU-M13-05</t>
         </is>
@@ -29763,7 +29760,7 @@
       </c>
       <c r="F92" s="26" t="inlineStr">
         <is>
-          <t>Fuera de alcance</t>
+          <t>Construccion desde 0</t>
         </is>
       </c>
       <c r="G92" s="26" t="inlineStr">
@@ -29782,14 +29779,18 @@
         </is>
       </c>
       <c r="J92" s="26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K92" s="26" t="inlineStr">
         <is>
-          <t>Fuera: refactor del Core, no cambia si el producto funciona</t>
-        </is>
-      </c>
-      <c r="L92" s="26" t="inlineStr"/>
+          <t>Si — PRERREQUISITO. Entra los primeros dias del sprint, junto a las TEC de ambiente, porque los 13 modulos convergen en Core y sin dividirlo siete personas editan el mismo servicio. Nadie construye sobre Core hasta que esta division este fusionada.</t>
+        </is>
+      </c>
+      <c r="L92" s="26" t="inlineStr">
+        <is>
+          <t>QA-HU-M13-05</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -30323,7 +30324,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -30683,7 +30683,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -31561,7 +31560,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -31971,7 +31969,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -32434,7 +32431,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>

--- a/wiki/05-backlog/MANI_MODULOS_SERVICIOS_Y_BACKLOG_S5.xlsx
+++ b/wiki/05-backlog/MANI_MODULOS_SERVICIOS_Y_BACKLOG_S5.xlsx
@@ -1134,7 +1134,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -12061,7 +12060,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="88" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -12076,7 +12074,6 @@
       <c r="C3" s="19" t="n"/>
       <c r="D3" s="20" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
@@ -12140,7 +12137,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
@@ -12244,7 +12240,6 @@
         <v>501</v>
       </c>
     </row>
-    <row r="22"/>
     <row r="23" ht="34" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
@@ -16232,6 +16227,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="B26" s="12" t="inlineStr">
         <is>
@@ -16260,27 +16256,27 @@
           <t>BUG-SEC-02, R-09, R-06</t>
         </is>
       </c>
-      <c r="E27" s="26" t="n">
+      <c r="E27" s="26" t="inlineStr">
+        <is>
+          <t>MANI-Node, MANI-.NET</t>
+        </is>
+      </c>
+      <c r="F27" s="26" t="inlineStr">
+        <is>
+          <t>Hoy Core usa service_role o postgres y Dispatch usa postgres, los tres con BYPASSRLS, asi que ninguna politica RLS se evalua y el aislamiento de RNF-01 descansa solo en el codigo. Cierra cuando: cada servicio conecta con un rol propio sin BYPASSRLS; las 15 politicas tenant_isolation_* dejan de estar TO public (R-06); y una prueba demuestra que, con el filtro de aplicacion desactivado a proposito, la politica sigue bloqueando el acceso cruzado. Sin esto, HU-M01-02 no demuestra aislamiento real sino aislamiento por codigo.</t>
+        </is>
+      </c>
+      <c r="G27" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="F27" s="26" t="inlineStr">
+      <c r="H27" s="26" t="inlineStr">
         <is>
           <t>Highest</t>
         </is>
       </c>
-      <c r="G27" s="26" t="inlineStr">
-        <is>
-          <t>Core y DevOps</t>
-        </is>
-      </c>
-      <c r="H27" s="26" t="inlineStr">
+      <c r="I27" s="26" t="inlineStr">
         <is>
           <t>TEC-13 (identidad de servicio)</t>
-        </is>
-      </c>
-      <c r="I27" s="26" t="inlineStr">
-        <is>
-          <t>Hoy Core usa service_role o postgres y Dispatch usa postgres, los tres con BYPASSRLS, asi que ninguna politica RLS se evalua y el aislamiento de RNF-01 descansa solo en el codigo. Cerrar: cada servicio conecta con un rol propio sin BYPASSRLS; las 15 politicas tenant_isolation_* dejan de estar TO public (R-06); y una prueba demuestra que, con el filtro de aplicacion desactivado a proposito, la politica sigue bloqueando el acceso cruzado. Sin esto, VAL-16 no demuestra aislamiento real sino aislamiento por codigo.</t>
         </is>
       </c>
     </row>

--- a/wiki/05-backlog/MANI_MODULOS_SERVICIOS_Y_BACKLOG_S5.xlsx
+++ b/wiki/05-backlog/MANI_MODULOS_SERVICIOS_Y_BACKLOG_S5.xlsx
@@ -1018,7 +1018,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Rules no existe (D-5)</t>
+          <t>Rules existe: MANI-Java esta en main desde el 21-oct con reglas de categoria reales (SCRUM-1070); /evaluate-rate y /rank-allies responden datos simulados. Falta el tarifario (CONS-27) y la validacion real contra el (CONS-22). D-5 es otro hueco: Dispatch no consulta a Rules para ordenar el listado.</t>
         </is>
       </c>
     </row>
@@ -12044,7 +12044,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="88" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -12059,7 +12058,6 @@
       <c r="C3" s="19" t="n"/>
       <c r="D3" s="20" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
@@ -12123,7 +12121,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
@@ -12239,7 +12236,6 @@
         <v>481</v>
       </c>
     </row>
-    <row r="22"/>
     <row r="23" ht="34" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
@@ -14275,7 +14271,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Alta, edicion y baja de sitios, cada uno con zona obligatoria.</t>
+          <t>Alta y edicion de sitios, cada uno con zona obligatoria. La baja queda pendiente de que la PO defina su semantica (estado o borrado logico), segun SCRUM-1387 (26-oct).</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
@@ -14321,7 +14317,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Reglas y condiciones del sitio mostradas en la oferta, antes de aceptar.</t>
+          <t>Reglas y condiciones del sitio visibles para el aliado asignado a una solicitud en ese sitio, antes de programar el servicio (criterio aprobado por la PO en SCRUM-1388 el 26-oct, tomado de SCRUM-853). Un aliado no asignado no las recibe.</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">

--- a/wiki/05-backlog/MANI_MODULOS_SERVICIOS_Y_BACKLOG_S5.xlsx
+++ b/wiki/05-backlog/MANI_MODULOS_SERVICIOS_Y_BACKLOG_S5.xlsx
@@ -40,7 +40,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20 Criterios US-02.1.1" sheetId="31" state="visible" r:id="rId31"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21 Cierre de cobertura" sheetId="32" state="visible" r:id="rId32"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22 Gestion del sprint" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24 Sprint 5 por modulo" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23 Subtareas de QA" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -94,7 +94,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -144,16 +144,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00BDD7EE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -241,7 +231,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -320,12 +310,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1034,7 +1018,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Rules no existe (D-5)</t>
+          <t>Rules existe: MANI-Java esta en main desde el 21-oct con reglas de categoria reales (SCRUM-1070); /evaluate-rate y /rank-allies responden datos simulados. Falta el tarifario (CONS-27) y la validacion real contra el (CONS-22). D-5 es otro hueco: Dispatch no consulta a Rules para ordenar el listado.</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1339,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>RF-37</t>
+          <t>Fuera de alcance MVP</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1370,7 +1354,7 @@
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>To Do (entra al MVP el 24-oct-2026)</t>
+          <t>To Do (fuera de MVP)</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1385,7 +1369,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>SRS §4.4 RF-37; antes excluido por §1.2. Pendiente de confirmacion del PO</t>
+          <t>SRS §1.2 excluye geolocalizacion en tiempo real</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -12169,26 +12153,38 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Historias por funcionalidad (hoja 24)</t>
+          <t>Validacion (VAL)</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Una historia por funcionalidad, repartida por modulo</t>
+          <t>Demostrar por video lo que el backlog declara cerrado, mas la regresion de identidad</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>398</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="3" t="n"/>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Construccion (CONS)</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Lo que falta del producto comprometido, incluidos los dos mocks y los items nuevos de la PO</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>277</v>
+      </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
@@ -12234,10 +12230,10 @@
       </c>
       <c r="B21" s="3" t="inlineStr"/>
       <c r="C21" s="21" t="n">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="D21" s="21" t="n">
-        <v>501</v>
+        <v>481</v>
       </c>
     </row>
     <row r="23" ht="34" customHeight="1">
@@ -12350,7 +12346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13170,131 +13166,126 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" s="22" t="inlineStr">
         <is>
+          <t>VAL-17</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>M-02</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Validar logout y expiracion de sesion</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Cliente / Aliado / Admin</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Al salir, el token local se descarta, el estado se limpia y el regreso exige autenticarse de nuevo. Con token expirado, el front vuelve al login en lugar de quedarse en blanco.</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>CONS-02 (logout construido)</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
           <t>VAL-18</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>M-02</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Ejecutar la regresion de seguridad de identidad (17 casos negativos y 1 positivo)</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Los 17 casos de la hoja '11 Casos de regresion' verdes por el Gateway, con asercion de codigo y de cuerpo, y el caso positivo con token obtenido de GoTrue, no firmado en CI.</t>
         </is>
       </c>
-      <c r="F21" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>Highest</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>TEC-09 (H-01), TEC-10 (H-02), TEC-11 (TLS)</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>CORE, DISPATCH</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22" ht="40" customHeight="1"/>
-    <row r="23">
-      <c r="C23" s="12" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>Total: 18 historias · 87 story points</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="28" t="inlineStr">
-        <is>
-          <t>VAL-19</t>
-        </is>
-      </c>
-      <c r="B24" s="26" t="inlineStr">
-        <is>
-          <t>M-03</t>
-        </is>
-      </c>
-      <c r="C24" s="26" t="inlineStr">
-        <is>
-          <t>Validar el contrato del perfil del aliado que consumen Dispatch y Rules</t>
-        </is>
-      </c>
-      <c r="D24" s="26" t="inlineStr">
-        <is>
-          <t>Sistema</t>
-        </is>
-      </c>
-      <c r="E24" s="26" t="inlineStr">
-        <is>
-          <t>Existe en codigo pero nunca se valido como contrato. Pedir el perfil del aliado por el Gateway con token real ES256 y comprobar: responde los campos que Dispatch y Rules declaran consumir, no expone documentos KYC ni datos de otro aliado, y con el token de un aliado del tenant B sobre un aliado del tenant A responde 403 o 404 y nunca 200 con datos. Video desde el front o, si no tiene pantalla, corrida Newman adjunta.</t>
-        </is>
-      </c>
-      <c r="F24" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="G24" s="26" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H24" s="26" t="inlineStr">
-        <is>
-          <t>TEC-10 (token real ES256)</t>
-        </is>
-      </c>
-      <c r="I24" s="26" t="inlineStr">
-        <is>
-          <t>CORE, DISPATCH, RULES</t>
-        </is>
-      </c>
-      <c r="J24" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="28" t="inlineStr">
         <is>
-          <t>VAL-20</t>
+          <t>VAL-19</t>
         </is>
       </c>
       <c r="B25" s="26" t="inlineStr">
         <is>
-          <t>M-04</t>
+          <t>M-03</t>
         </is>
       </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>Validar que el catalogo responde solo las categorias y zonas del tenant del claim</t>
+          <t>Validar el contrato del perfil del aliado que consumen Dispatch y Rules</t>
         </is>
       </c>
       <c r="D25" s="26" t="inlineStr">
         <is>
-          <t>Cliente / Aliado</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="E25" s="26" t="inlineStr">
         <is>
-          <t>Implementado y sin validar. Consultar el catalogo por el Gateway con usuarios de dos tenants y comprobar que cada uno ve solo sus categorias activas, que una categoria desactivada no aparece, y que el tenant no se puede forzar por cuerpo ni por cabecera (se toma del claim, T4). El catalogo es pre-auth en nginx: comprobar tambien que sin token no filtra datos de ningun tenant.</t>
+          <t>Existe en codigo pero nunca se valido como contrato. Pedir el perfil del aliado por el Gateway con token real ES256 y comprobar: responde los campos que Dispatch y Rules declaran consumir, no expone documentos KYC ni datos de otro aliado, y con el token de un aliado del tenant B sobre un aliado del tenant A responde 403 o 404 y nunca 200 con datos. Video desde el front o, si no tiene pantalla, corrida Newman adjunta.</t>
         </is>
       </c>
       <c r="F25" s="26" t="n">
@@ -13307,12 +13298,12 @@
       </c>
       <c r="H25" s="26" t="inlineStr">
         <is>
-          <t>TEC-10, TEC-16</t>
+          <t>TEC-10 (token real ES256)</t>
         </is>
       </c>
       <c r="I25" s="26" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>CORE, DISPATCH, RULES</t>
         </is>
       </c>
       <c r="J25" s="26" t="inlineStr">
@@ -13324,27 +13315,27 @@
     <row r="26">
       <c r="A26" s="28" t="inlineStr">
         <is>
-          <t>VAL-21</t>
+          <t>VAL-20</t>
         </is>
       </c>
       <c r="B26" s="26" t="inlineStr">
         <is>
-          <t>M-05</t>
+          <t>M-04</t>
         </is>
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>Validar el contexto de solicitud que Dispatch pide a Core</t>
+          <t>Validar que el catalogo responde solo las categorias y zonas del tenant del claim</t>
         </is>
       </c>
       <c r="D26" s="26" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Cliente / Aliado</t>
         </is>
       </c>
       <c r="E26" s="26" t="inlineStr">
         <is>
-          <t>Implementado y sin validar. Comprobar que Dispatch obtiene zona, categoria y estado de la solicitud por HTTP a Core y no por SQL sobre tablas de Core (T1), que si Core no responde Dispatch devuelve 503 y no arma el contexto con logica local (T2), y que el contexto de una solicitud del tenant A nunca se entrega con el token del tenant B.</t>
+          <t>Implementado y sin validar. Consultar el catalogo por el Gateway con usuarios de dos tenants y comprobar que cada uno ve solo sus categorias activas, que una categoria desactivada no aparece, y que el tenant no se puede forzar por cuerpo ni por cabecera (se toma del claim, T4). El catalogo es pre-auth en nginx: comprobar tambien que sin token no filtra datos de ningun tenant.</t>
         </is>
       </c>
       <c r="F26" s="26" t="n">
@@ -13357,12 +13348,12 @@
       </c>
       <c r="H26" s="26" t="inlineStr">
         <is>
-          <t>TEC-02, TEC-10</t>
+          <t>TEC-10, TEC-16</t>
         </is>
       </c>
       <c r="I26" s="26" t="inlineStr">
         <is>
-          <t>CORE, DISPATCH</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="J26" s="26" t="inlineStr">
@@ -13374,48 +13365,98 @@
     <row r="27">
       <c r="A27" s="28" t="inlineStr">
         <is>
+          <t>VAL-21</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="inlineStr">
+        <is>
+          <t>M-05</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>Validar el contexto de solicitud que Dispatch pide a Core</t>
+        </is>
+      </c>
+      <c r="D27" s="26" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+      <c r="E27" s="26" t="inlineStr">
+        <is>
+          <t>Implementado y sin validar. Comprobar que Dispatch obtiene zona, categoria y estado de la solicitud por HTTP a Core y no por SQL sobre tablas de Core (T1), que si Core no responde Dispatch devuelve 503 y no arma el contexto con logica local (T2), y que el contexto de una solicitud del tenant A nunca se entrega con el token del tenant B.</t>
+        </is>
+      </c>
+      <c r="F27" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" s="26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H27" s="26" t="inlineStr">
+        <is>
+          <t>TEC-02, TEC-10</t>
+        </is>
+      </c>
+      <c r="I27" s="26" t="inlineStr">
+        <is>
+          <t>CORE, DISPATCH</t>
+        </is>
+      </c>
+      <c r="J27" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="28" t="inlineStr">
+        <is>
           <t>VAL-22</t>
         </is>
       </c>
-      <c r="B27" s="26" t="inlineStr">
+      <c r="B28" s="26" t="inlineStr">
         <is>
           <t>M-05</t>
         </is>
       </c>
-      <c r="C27" s="26" t="inlineStr">
+      <c r="C28" s="26" t="inlineStr">
         <is>
           <t>Validar idempotencia de la creacion de solicitud y del despacho bajo reintento</t>
         </is>
       </c>
-      <c r="D27" s="26" t="inlineStr">
+      <c r="D28" s="26" t="inlineStr">
         <is>
           <t>Sistema</t>
         </is>
       </c>
-      <c r="E27" s="26" t="inlineStr">
+      <c r="E28" s="26" t="inlineStr">
         <is>
           <t>RNF-03 exige que las operaciones criticas resistan reintentos sin duplicar. Comprobar: reintento con la misma claveIdempotencia no crea una segunda solicitud; reintento de la orquestacion no duplica el broadcast; y tras un corte parcial del broadcast el reintento completa las ofertas que faltan en vez de congelarse, que es el defecto D-4. Requiere TEC-04 desplegado.</t>
         </is>
       </c>
-      <c r="F27" s="26" t="n">
+      <c r="F28" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="G27" s="26" t="inlineStr">
+      <c r="G28" s="26" t="inlineStr">
         <is>
           <t>Highest</t>
         </is>
       </c>
-      <c r="H27" s="26" t="inlineStr">
+      <c r="H28" s="26" t="inlineStr">
         <is>
           <t>TEC-04 (paginar y rehacer la guarda de idempotencia)</t>
         </is>
       </c>
-      <c r="I27" s="26" t="inlineStr">
+      <c r="I28" s="26" t="inlineStr">
         <is>
           <t>CORE, DISPATCH</t>
         </is>
       </c>
-      <c r="J27" s="26" t="inlineStr">
+      <c r="J28" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -13436,7 +13477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13520,7 +13561,7 @@
     <row r="5" ht="52" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>CONS-04</t>
+          <t>CONS-01</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -13530,17 +13571,17 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Recuperacion segura de contrasena</t>
+          <t>Inicio de sesion separado por tipo de usuario</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Cliente / Aliado</t>
+          <t>Todos los roles</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Solicitud de recuperacion, correo con enlace de un solo uso y vigencia limitada, y cambio efectivo. No revela si el correo existe.</t>
+          <t>Selector o rutas distintas por tipo (cliente PN, cliente empresa, aliado PN, aliado empresa, empleado directo, admin tenant, admin plataforma). El backend rechaza el cruce entre el tipo elegido y el rol del token. Mensaje de error que no revela si el correo existe.</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
@@ -13548,12 +13589,12 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Highest</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>CONS-03</t>
+          <t>VAL-01</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -13566,7 +13607,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>CONS-05</t>
+          <t>CONS-02</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -13576,30 +13617,30 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Registro de cliente empresa</t>
+          <t>Logout</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Cliente empresa</t>
+          <t>Todos los roles</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Alta de cuenta empresa con NIT y representante, separada de la administracion de sitios.</t>
+          <t>Accion de salir disponible desde el menu superior en todas las pantallas, limpieza de token y de estado, y retorno al login del tipo correspondiente.</t>
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Highest</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CONS-07 (menu superior)</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -13612,7 +13653,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>CONS-06</t>
+          <t>CONS-03</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -13622,30 +13663,30 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Registro de empleado directo</t>
+          <t>Autenticacion consumida desde la API y retiro de Supabase directo en el cliente</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Admin de tenant</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Tercer tipo de aliado, creado por el tenant, con los documentos que su configuracion exige.</t>
+          <t>El cliente Flutter no usa .rpc(), .from() ni .storage.from(); todo pasa por el Gateway. Las interfaces de domain/repositories no cambian (ADR-0027).</t>
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Highest</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>US-02.1.1-M3</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -13658,27 +13699,27 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>CONS-08</t>
+          <t>CONS-04</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>M-13</t>
+          <t>M-02</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Pantalla de inicio por tipo de usuario</t>
+          <t>Recuperacion segura de contrasena</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Todos los roles</t>
+          <t>Cliente / Aliado</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Inicio distinto por rol con los accesos y el resumen que cada uno necesita.</t>
+          <t>Solicitud de recuperacion, correo con enlace de un solo uso y vigencia limitada, y cambio efectivo. No revela si el correo existe.</t>
         </is>
       </c>
       <c r="F8" s="3" t="n">
@@ -13691,7 +13732,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>CONS-07</t>
+          <t>CONS-03</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -13704,40 +13745,40 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>CONS-09</t>
+          <t>CONS-05</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>M-13</t>
+          <t>M-02</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Enrutamiento por rol con guardas de sesion</t>
+          <t>Registro de cliente empresa</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Cliente empresa</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Rutas protegidas por rol, redireccion al login ante 401 y bloqueo de rutas que no corresponden al rol.</t>
+          <t>Alta de cuenta empresa con NIT y representante, separada de la administracion de sitios.</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>CONS-07</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -13750,17 +13791,17 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>CONS-14</t>
+          <t>CONS-06</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>M-04</t>
+          <t>M-02</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Activar y desactivar categoria sin afectar servicios en curso</t>
+          <t>Registro de empleado directo</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -13770,20 +13811,20 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Al desactivar, la categoria deja de ofrecerse pero los servicios en curso continuan y se pueden cerrar.</t>
+          <t>Tercer tipo de aliado, creado por el tenant, con los documentos que su configuracion exige.</t>
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>VAL-09</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -13796,27 +13837,27 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>CONS-15</t>
+          <t>CONS-07</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>M-03</t>
+          <t>M-13</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Aliado gestiona su disponibilidad y sus ausencias</t>
+          <t>Menu superior por rol con sesion visible</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Aliado</t>
+          <t>Todos los roles</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Pantalla sobre la tabla aliado_ausencia ya migrada (008), sin solapamientos, y efecto inmediato en la elegibilidad.</t>
+          <t>Menu persistente con las entradas que corresponden al rol, nombre del usuario y del tenant visibles, y acceso a logout. Usable en movil (RNF-08).</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
@@ -13824,12 +13865,12 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Highest</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>VAL-11</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -13842,40 +13883,40 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>CONS-16</t>
+          <t>CONS-08</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>M-03</t>
+          <t>M-13</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Cliente empresa administra multiples sitios de servicio</t>
+          <t>Pantalla de inicio por tipo de usuario</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Cliente empresa</t>
+          <t>Todos los roles</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Alta, edicion y baja de sitios, cada uno con zona obligatoria.</t>
+          <t>Inicio distinto por rol con los accesos y el resumen que cada uno necesita.</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>CONS-05</t>
+          <t>CONS-07</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -13888,40 +13929,40 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>CONS-17</t>
+          <t>CONS-09</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>M-03</t>
+          <t>M-13</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Reglas contextuales del sitio visibles al aliado antes de programar</t>
+          <t>Enrutamiento por rol con guardas de sesion</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Cliente / Aliado</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Reglas y condiciones del sitio mostradas en la oferta, antes de aceptar.</t>
+          <t>Rutas protegidas por rol, redireccion al login ante 401 y bloqueo de rutas que no corresponden al rol.</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>CONS-16</t>
+          <t>CONS-07</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -13934,45 +13975,45 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>CONS-18</t>
+          <t>CONS-10</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>M-05</t>
+          <t>M-13</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Orden del listado de aliados en el Rules Service</t>
+          <t>Dividir el front en modulos independientes por dominio</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Equipo de desarrollo</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Rules Service en Java con la regla del tenant (cobertura, calificacion o comision) y cliente HTTP en Dispatch que consume el orden. Cierra D-5. Incluye el repositorio, el Dockerfile, la ruta en el Gateway y el health.</t>
+          <t>Un feature por dominio, sin que profiles agrupe cobertura y verificacion ni services agrupe categorias y solicitudes. Sin cambios de comportamiento y con las pruebas existentes verdes.</t>
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Highest</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>P-1, TEC-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>RULES, DISPATCH</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr"/>
@@ -13980,31 +14021,31 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>CONS-19</t>
+          <t>CONS-11</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>M-05</t>
+          <t>M-13</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Priorizar solicitud por comision ofrecida</t>
+          <t>Dividir el Core por dominios internos</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Cliente / Admin de tenant</t>
+          <t>Equipo de desarrollo</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Criterio de comision dentro de la regla de ranking del tenant.</t>
+          <t>Dominios internos de identidad, directorio, catalogo, cobertura, disponibilidad, despacho y comunicacion, sin crear un servicio por CRUD (SAD §7.3, ADR-0022).</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -14013,12 +14054,12 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>CONS-18</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>RULES</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr"/>
@@ -14026,27 +14067,27 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>CONS-20</t>
+          <t>CONS-12</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>M-05</t>
+          <t>M-04</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Cancelar solicitud antes de la ejecucion</t>
+          <t>Barrios como nivel mas fino del catalogo de zonas</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Admin de tenant</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Cancelacion con motivo, estado final consistente y notificacion al aliado asignado. Respeta la decision de P-4 sobre el dueno del estado.</t>
+          <t>Alta de barrios bajo la zona padre, cobertura declarable por barrio y resolucion por ancestro en la elegibilidad. No se introduce radio ni distancia (REST-01).</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
@@ -14059,12 +14100,12 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>P-4</t>
+          <t>VAL-07</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>DISPATCH, CORE</t>
+          <t>CORE, DISPATCH</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr"/>
@@ -14072,40 +14113,40 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>CONS-21</t>
+          <t>CONS-13</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>M-06</t>
+          <t>M-04</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Cotizacion con mano de obra y materiales separados</t>
+          <t>Visualizacion en mapa de zonas, barrios y sitio de servicio</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Aliado</t>
+          <t>Cliente / Aliado</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Cotizacion con los dos renglones, total calculado y version persistida.</t>
+          <t>Mapa de solo lectura que ubica la zona, el barrio y el sitio. La seleccion sigue siendo por catalogo jerarquico, porque US-02.1.4-R1 retiro la seleccion libre en mapa.</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>VAL-13</t>
+          <t>CONS-12</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -14118,31 +14159,31 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>CONS-22</t>
+          <t>CONS-14</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>M-06</t>
+          <t>M-04</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Alerta de cotizacion fuera del rango del tarifario</t>
+          <t>Activar y desactivar categoria sin afectar servicios en curso</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Aliado</t>
+          <t>Admin de tenant</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Aviso bidireccional cuando el valor queda por encima o por debajo del rango del tenant, sin bloquear el envio.</t>
+          <t>Al desactivar, la categoria deja de ofrecerse pero los servicios en curso continuan y se pueden cerrar.</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
@@ -14151,12 +14192,12 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>CONS-18, CONS-27</t>
+          <t>VAL-09</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>RULES</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr"/>
@@ -14164,40 +14205,40 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>CONS-23</t>
+          <t>CONS-15</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>M-06</t>
+          <t>M-03</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Cliente acepta, rechaza o solicita ajuste de la cotizacion</t>
+          <t>Aliado gestiona su disponibilidad y sus ausencias</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Aliado</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Las tres transiciones con su efecto en el estado del servicio y su notificacion.</t>
+          <t>Pantalla sobre la tabla aliado_ausencia ya migrada (008), sin solapamientos, y efecto inmediato en la elegibilidad.</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>CONS-21</t>
+          <t>VAL-11</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -14210,40 +14251,40 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>CONS-24</t>
+          <t>CONS-16</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>M-07</t>
+          <t>M-03</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Marcar inicio y fin de la ejecucion</t>
+          <t>Cliente empresa administra multiples sitios de servicio</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Aliado</t>
+          <t>Cliente empresa</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Marcas con sello de tiempo del servidor y estado del servicio consistente.</t>
+          <t>Alta y edicion de sitios, cada uno con zona obligatoria. La baja queda pendiente de que la PO defina su semantica (estado o borrado logico), segun SCRUM-1387 (26-oct).</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>CONS-23</t>
+          <t>CONS-05</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -14256,40 +14297,40 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>CONS-25</t>
+          <t>CONS-17</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>M-07</t>
+          <t>M-03</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Registrar eventos y observaciones durante la ejecucion</t>
+          <t>Reglas contextuales del sitio visibles al aliado antes de programar</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Aliado</t>
+          <t>Cliente / Aliado</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Bitacora cronologica inmutable con autor y sello de tiempo. Recupera la migracion 0012_evento_servicio_evidencia.sql que quedo sin fusionar.</t>
+          <t>Reglas y condiciones del sitio visibles para el aliado asignado a una solicitud en ese sitio, antes de programar el servicio (criterio aprobado por la PO en SCRUM-1388 el 26-oct, tomado de SCRUM-853). Un aliado no asignado no las recibe.</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>CONS-24, TEC-08</t>
+          <t>CONS-16</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -14302,45 +14343,45 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>CONS-26</t>
+          <t>CONS-18</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>M-07</t>
+          <t>M-05</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Registrar evidencias sin conexion y sincronizarlas</t>
+          <t>Orden del listado de aliados en el Rules Service</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Aliado</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Captura en modo avion, cola local y sincronizacion idempotente al recuperar red, sin duplicar evidencias.</t>
+          <t>Rules Service en Java con la regla del tenant (cobertura, calificacion o comision) y cliente HTTP en Dispatch que consume el orden. Cierra D-5. Incluye el repositorio, el Dockerfile, la ruta en el Gateway y el health.</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Highest</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>CONS-25</t>
+          <t>P-1, TEC-15</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>RULES, DISPATCH</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr"/>
@@ -14348,27 +14389,27 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>CONS-27</t>
+          <t>CONS-19</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>M-10</t>
+          <t>M-05</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Cargar la tabla de tarifas por categoria</t>
+          <t>Priorizar solicitud por comision ofrecida</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Admin de tenant</t>
+          <t>Cliente / Admin de tenant</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Minimo, tipico y maximo por categoria y tenant, con validacion de orden de los tres valores.</t>
+          <t>Criterio de comision dentro de la regla de ranking del tenant.</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
@@ -14376,7 +14417,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -14386,7 +14427,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>RULES, CORE</t>
+          <t>RULES</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr"/>
@@ -14394,45 +14435,45 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>CONS-28</t>
+          <t>CONS-20</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>M-10</t>
+          <t>M-05</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Ver la tarifa de referencia al cotizar</t>
+          <t>Cancelar solicitud antes de la ejecucion</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Aliado</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Rango visible en la pantalla de cotizacion, resuelto por categoria y tenant.</t>
+          <t>Cancelacion con motivo, estado final consistente y notificacion al aliado asignado. Respeta la decision de P-4 sobre el dueno del estado.</t>
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>CONS-27</t>
+          <t>P-4</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>RULES</t>
+          <t>DISPATCH, CORE</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr"/>
@@ -14440,40 +14481,40 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>CONS-29</t>
+          <t>CONS-21</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>M-10</t>
+          <t>M-06</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Reporte de cotizaciones fuera de rango por periodo</t>
+          <t>Cotizacion con mano de obra y materiales separados</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Admin de tenant</t>
+          <t>Aliado</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Consulta por periodo con exportacion, calculada sobre datos reales del tenant.</t>
+          <t>Cotizacion con los dos renglones, total calculado y version persistida.</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>CONS-22</t>
+          <t>VAL-13</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -14486,31 +14527,31 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>CONS-30</t>
+          <t>CONS-22</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>M-08</t>
+          <t>M-06</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Calificacion bidireccional y cierre condicionado</t>
+          <t>Alerta de cotizacion fuera del rango del tarifario</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Cliente / Aliado</t>
+          <t>Aliado</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Ambas partes califican y el servicio no cierra hasta que las dos lo hayan hecho.</t>
+          <t>Aviso bidireccional cuando el valor queda por encima o por debajo del rango del tenant, sin bloquear el envio.</t>
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
@@ -14519,12 +14560,12 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>CONS-24</t>
+          <t>CONS-18, CONS-27</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>RULES</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr"/>
@@ -14532,17 +14573,17 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>CONS-31</t>
+          <t>CONS-23</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>M-08</t>
+          <t>M-06</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Calificacion agregada visible en el listado de aliados</t>
+          <t>Cliente acepta, rechaza o solicita ajuste de la cotizacion</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -14552,25 +14593,25 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Promedio y conteo por aliado, usados tambien como criterio de orden.</t>
+          <t>Las tres transiciones con su efecto en el estado del servicio y su notificacion.</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>CONS-30, CONS-18</t>
+          <t>CONS-21</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>CORE, RULES</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr"/>
@@ -14578,27 +14619,27 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>CONS-32</t>
+          <t>CONS-24</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>M-08</t>
+          <t>M-07</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Penalizacion por cancelacion tardia</t>
+          <t>Marcar inicio y fin de la ejecucion</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Aliado</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Regla configurable por tenant, aplicada segun el momento de la cancelacion.</t>
+          <t>Marcas con sello de tiempo del servidor y estado del servicio consistente.</t>
         </is>
       </c>
       <c r="F28" s="3" t="n">
@@ -14611,12 +14652,12 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>CONS-20, CONS-18</t>
+          <t>CONS-23</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>RULES</t>
+          <t>CORE</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr"/>
@@ -14624,40 +14665,40 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>CONS-33</t>
+          <t>CONS-25</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>M-08</t>
+          <t>M-07</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Historial de servicios del cliente y de trabajos del aliado</t>
+          <t>Registrar eventos y observaciones durante la ejecucion</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Cliente / Aliado</t>
+          <t>Aliado</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Listados paginados por usuario y tenant con filtro por estado.</t>
+          <t>Bitacora cronologica inmutable con autor y sello de tiempo. Recupera la migracion 0012_evento_servicio_evidencia.sql que quedo sin fusionar.</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>CONS-30</t>
+          <t>CONS-24, TEC-08</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -14670,27 +14711,27 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>CONS-34</t>
+          <t>CONS-26</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>M-09</t>
+          <t>M-07</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Mensajeria cliente-aliado por servicio</t>
+          <t>Registrar evidencias sin conexion y sincronizarlas</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Cliente / Aliado</t>
+          <t>Aliado</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Hilo por servicio, entrega casi en tiempo real cuando ambos estan conectados y persistencia del historial.</t>
+          <t>Captura en modo avion, cola local y sincronizacion idempotente al recuperar red, sin duplicar evidencias.</t>
         </is>
       </c>
       <c r="F30" s="3" t="n">
@@ -14703,7 +14744,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>VAL-13</t>
+          <t>CONS-25</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -14716,45 +14757,45 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>CONS-35</t>
+          <t>CONS-27</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>M-09</t>
+          <t>M-10</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Mock del proveedor de notificaciones push en el backend</t>
+          <t>Cargar la tabla de tarifas por categoria</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Admin de tenant</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Proveedor simulado detras de POST /notifications con bandeja consultable, para que el front exista sin FCM ni APNs reales. Conmutable por configuracion hacia el proveedor real (ADR-0014).</t>
+          <t>Minimo, tipico y maximo por categoria y tenant, con validacion de orden de los tres valores.</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Highest</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CONS-18</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>RULES, CORE</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr"/>
@@ -14762,31 +14803,31 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>CONS-36</t>
+          <t>CONS-28</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>M-09</t>
+          <t>M-10</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones de mensajes nuevos y del ciclo del servicio</t>
+          <t>Ver la tarifa de referencia al cotizar</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Cliente / Aliado</t>
+          <t>Aliado</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Notificacion cuando el destinatario no esta conectado, para mensajes y para los cuatro eventos del ciclo con el esquema v1 de ARQ-06.</t>
+          <t>Rango visible en la pantalla de cotizacion, resuelto por categoria y tenant.</t>
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
@@ -14795,12 +14836,12 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>CONS-34, CONS-35</t>
+          <t>CONS-27</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>CORE, DISPATCH</t>
+          <t>RULES</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr"/>
@@ -14808,17 +14849,17 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>CONS-37</t>
+          <t>CONS-29</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>M-09</t>
+          <t>M-10</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Consultar la conversacion para atender una queja</t>
+          <t>Reporte de cotizaciones fuera de rango por periodo</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -14828,7 +14869,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Acceso de solo lectura al hilo, acotado al tenant y registrado en auditoria.</t>
+          <t>Consulta por periodo con exportacion, calculada sobre datos reales del tenant.</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
@@ -14841,7 +14882,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>CONS-34</t>
+          <t>CONS-22</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -14854,27 +14895,27 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>CONS-38</t>
+          <t>CONS-30</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>M-11</t>
+          <t>M-08</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Mock de la pasarela de pagos</t>
+          <t>Calificacion bidireccional y cierre condicionado</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Cliente / Aliado</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Proveedor simulado con los tres desenlaces (aprobado, rechazado y pendiente), comprobante descargable de prueba y registro de la transaccion. Marcado como mock en la interfaz, sin datos reales de tarjeta y conmutable por configuracion.</t>
+          <t>Ambas partes califican y el servicio no cierra hasta que las dos lo hayan hecho.</t>
         </is>
       </c>
       <c r="F34" s="3" t="n">
@@ -14882,12 +14923,12 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Highest</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>CONS-23</t>
+          <t>CONS-24</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -14900,27 +14941,27 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>CONS-39</t>
+          <t>CONS-31</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>M-11</t>
+          <t>M-08</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Registro inmutable de transacciones</t>
+          <t>Calificacion agregada visible en el listado de aliados</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Audit log de transacciones sin actualizacion ni borrado, con correlacion al servicio.</t>
+          <t>Promedio y conteo por aliado, usados tambien como criterio de orden.</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
@@ -14933,12 +14974,12 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>CONS-38</t>
+          <t>CONS-30, CONS-18</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>CORE</t>
+          <t>CORE, RULES</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr"/>
@@ -14946,45 +14987,45 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>CONS-40</t>
+          <t>CONS-32</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>M-11</t>
+          <t>M-08</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Liquidacion al aliado con comision configurable</t>
+          <t>Penalizacion por cancelacion tardia</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Admin de tenant</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Calculo con la comision del tenant y detalle consultable por el aliado.</t>
+          <t>Regla configurable por tenant, aplicada segun el momento de la cancelacion.</t>
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>CONS-38, CONS-18</t>
+          <t>CONS-20, CONS-18</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>CORE, RULES</t>
+          <t>RULES</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr"/>
@@ -14992,31 +15033,31 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>CONS-41</t>
+          <t>CONS-33</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>M-12</t>
+          <t>M-08</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Registro y gestion de quejas</t>
+          <t>Historial de servicios del cliente y de trabajos del aliado</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Cliente / Admin de tenant</t>
+          <t>Cliente / Aliado</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Alta de la queja asociada al servicio y workflow de estados del tenant.</t>
+          <t>Listados paginados por usuario y tenant con filtro por estado.</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -15038,31 +15079,31 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>CONS-42</t>
+          <t>CONS-34</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>M-12</t>
+          <t>M-09</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Metricas operativas por tenant y endpoint /metrics</t>
+          <t>Mensajeria cliente-aliado por servicio</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Admin de tenant / plataforma</t>
+          <t>Cliente / Aliado</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Metricas de operacion por tenant y exposicion tecnica de /metrics con alertas minimas, que hoy no existen (SCRUM-1266 H-05).</t>
+          <t>Hilo por servicio, entrega casi en tiempo real cuando ambos estan conectados y persistencia del historial.</t>
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
@@ -15071,7 +15112,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VAL-13</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
@@ -15084,35 +15125,35 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>CONS-43</t>
+          <t>CONS-35</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>M-12</t>
+          <t>M-09</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Administrar el estado de los tenants</t>
+          <t>Mock del proveedor de notificaciones push en el backend</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Admin de plataforma</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Activar, suspender y reactivar un tenant, con efecto inmediato en el acceso de sus usuarios.</t>
+          <t>Proveedor simulado detras de POST /notifications con bandeja consultable, para que el front exista sin FCM ni APNs reales. Conmutable por configuracion hacia el proveedor real (ADR-0014).</t>
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Highest</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
@@ -15130,27 +15171,27 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>CONS-44</t>
+          <t>CONS-36</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>M-01</t>
+          <t>M-09</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Configuracion de reglas por tenant sin despliegue</t>
+          <t>Notificaciones de mensajes nuevos y del ciclo del servicio</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Admin de tenant</t>
+          <t>Cliente / Aliado</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Documentos exigidos por tipo de aliado, orden del listado, categorias y tarifas configurables desde la consola, sin desplegar codigo (RNF-02, RNF-10).</t>
+          <t>Notificacion cuando el destinatario no esta conectado, para mensajes y para los cuatro eventos del ciclo con el esquema v1 de ARQ-06.</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
@@ -15158,85 +15199,492 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>CONS-34, CONS-35</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>CORE, DISPATCH</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41" ht="40" customHeight="1">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>CONS-37</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>M-09</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Consultar la conversacion para atender una queja</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Admin de tenant</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Acceso de solo lectura al hilo, acotado al tenant y registrado en auditoria.</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>CONS-34</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42" ht="52" customHeight="1">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>CONS-38</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>M-11</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Mock de la pasarela de pagos</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Proveedor simulado con los tres desenlaces (aprobado, rechazado y pendiente), comprobante descargable de prueba y registro de la transaccion. Marcado como mock en la interfaz, sin datos reales de tarjeta y conmutable por configuracion.</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Highest</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>CONS-23</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43" ht="40" customHeight="1">
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t>CONS-39</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>M-11</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Registro inmutable de transacciones</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Audit log de transacciones sin actualizacion ni borrado, con correlacion al servicio.</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>CONS-38</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="40" customHeight="1">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>CONS-40</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>M-11</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Liquidacion al aliado con comision configurable</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Admin de tenant</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Calculo con la comision del tenant y detalle consultable por el aliado.</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>CONS-38, CONS-18</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>CORE, RULES</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45" ht="40" customHeight="1">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>CONS-41</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>M-12</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Registro y gestion de quejas</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Cliente / Admin de tenant</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Alta de la queja asociada al servicio y workflow de estados del tenant.</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>CONS-30</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46" ht="40" customHeight="1">
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>CONS-42</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>M-12</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Metricas operativas por tenant y endpoint /metrics</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Admin de tenant / plataforma</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Metricas de operacion por tenant y exposicion tecnica de /metrics con alertas minimas, que hoy no existen (SCRUM-1266 H-05).</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47" ht="40" customHeight="1">
+      <c r="A47" s="13" t="inlineStr">
+        <is>
+          <t>CONS-43</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>M-12</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Administrar el estado de los tenants</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Admin de plataforma</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Activar, suspender y reactivar un tenant, con efecto inmediato en el acceso de sus usuarios.</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48" ht="40" customHeight="1">
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>CONS-44</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>M-01</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Configuracion de reglas por tenant sin despliegue</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Admin de tenant</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Documentos exigidos por tipo de aliado, orden del listado, categorias y tarifas configurables desde la consola, sin desplegar codigo (RNF-02, RNF-10).</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
         <is>
           <t>CONS-18</t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr">
+      <c r="I48" s="3" t="inlineStr">
         <is>
           <t>RULES, CORE</t>
         </is>
       </c>
-      <c r="J40" s="3" t="inlineStr"/>
-    </row>
-    <row r="41" ht="40" customHeight="1"/>
-    <row r="42" ht="52" customHeight="1">
-      <c r="C42" s="12" t="inlineStr">
+      <c r="J48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49" ht="40" customHeight="1">
+      <c r="A49" s="13" t="inlineStr">
+        <is>
+          <t>CONS-45</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>M-02</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Cifrado y manejo de secretos verificado de punta a punta</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>TLS en el borde con redireccion 80 a 443, cifrado en reposo del KYC, prohibicion de registrar credenciales en logs y secretos fuera del control de versiones.</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>Highest</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>TEC-11, TEC-09</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="C51" s="12" t="inlineStr">
         <is>
           <t>Total: 45 historias · 269 story points</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="40" customHeight="1">
-      <c r="A43" s="28" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="28" t="inlineStr">
         <is>
           <t>CONS-46</t>
         </is>
       </c>
-      <c r="B43" s="26" t="inlineStr">
+      <c r="B52" s="26" t="inlineStr">
         <is>
           <t>M-01</t>
         </is>
       </c>
-      <c r="C43" s="26" t="inlineStr">
+      <c r="C52" s="26" t="inlineStr">
         <is>
           <t>Alta y administracion de tenants por el administrador de plataforma</t>
         </is>
       </c>
-      <c r="D43" s="26" t="inlineStr">
+      <c r="D52" s="26" t="inlineStr">
         <is>
           <t>Admin de plataforma</t>
         </is>
       </c>
-      <c r="E43" s="26" t="inlineStr">
+      <c r="E52" s="26" t="inlineStr">
         <is>
           <t>RF-01 es critico y hoy solo existe GET /api/v1/core/tenants: no hay forma de crear un tenant por la aplicacion. End to end desde cero: pantalla de administracion de plataforma, alta del tenant con su slug y sus datos, edicion, y consulta del listado. El alta crea el tenant aislado: sus tablas nacen con tenant_id y su politica por tenant en la misma migracion (T3). Solo el administrador de plataforma puede crear tenants; un admin de tenant que lo intente recibe 403. Queda registrado quien lo creo, cuando y con que correlationId (T10). No incluye el estado del tenant, que es CONS-43.</t>
         </is>
       </c>
-      <c r="F43" s="26" t="n">
+      <c r="F52" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="G43" s="26" t="inlineStr">
+      <c r="G52" s="26" t="inlineStr">
         <is>
           <t>Highest</t>
         </is>
       </c>
-      <c r="H43" s="26" t="inlineStr">
+      <c r="H52" s="26" t="inlineStr">
         <is>
           <t>CONS-07 (shell), TEC-10</t>
         </is>
       </c>
-      <c r="I43" s="26" t="inlineStr">
+      <c r="I52" s="26" t="inlineStr">
         <is>
           <t>CORE</t>
         </is>
       </c>
-      <c r="J43" s="26" t="inlineStr">
+      <c r="J52" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="40" customHeight="1"/>
-    <row r="45" ht="40" customHeight="1"/>
-    <row r="46" ht="40" customHeight="1"/>
-    <row r="47" ht="40" customHeight="1"/>
-    <row r="48" ht="40" customHeight="1"/>
-    <row r="49" ht="40" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
@@ -16227,7 +16675,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26">
       <c r="B26" s="12" t="inlineStr">
         <is>
@@ -16256,27 +16703,27 @@
           <t>BUG-SEC-02, R-09, R-06</t>
         </is>
       </c>
-      <c r="E27" s="26" t="inlineStr">
-        <is>
-          <t>MANI-Node, MANI-.NET</t>
-        </is>
+      <c r="E27" s="26" t="n">
+        <v>5</v>
       </c>
       <c r="F27" s="26" t="inlineStr">
         <is>
-          <t>Hoy Core usa service_role o postgres y Dispatch usa postgres, los tres con BYPASSRLS, asi que ninguna politica RLS se evalua y el aislamiento de RNF-01 descansa solo en el codigo. Cierra cuando: cada servicio conecta con un rol propio sin BYPASSRLS; las 15 politicas tenant_isolation_* dejan de estar TO public (R-06); y una prueba demuestra que, con el filtro de aplicacion desactivado a proposito, la politica sigue bloqueando el acceso cruzado. Sin esto, HU-M01-02 no demuestra aislamiento real sino aislamiento por codigo.</t>
-        </is>
-      </c>
-      <c r="G27" s="26" t="n">
-        <v>5</v>
+          <t>Highest</t>
+        </is>
+      </c>
+      <c r="G27" s="26" t="inlineStr">
+        <is>
+          <t>Core y DevOps</t>
+        </is>
       </c>
       <c r="H27" s="26" t="inlineStr">
         <is>
-          <t>Highest</t>
+          <t>TEC-13 (identidad de servicio)</t>
         </is>
       </c>
       <c r="I27" s="26" t="inlineStr">
         <is>
-          <t>TEC-13 (identidad de servicio)</t>
+          <t>Hoy Core usa service_role o postgres y Dispatch usa postgres, los tres con BYPASSRLS, asi que ninguna politica RLS se evalua y el aislamiento de RNF-01 descansa solo en el codigo. Cerrar: cada servicio conecta con un rol propio sin BYPASSRLS; las 15 politicas tenant_isolation_* dejan de estar TO public (R-06); y una prueba demuestra que, con el filtro de aplicacion desactivado a proposito, la politica sigue bloqueando el acceso cruzado. Sin esto, VAL-16 no demuestra aislamiento real sino aislamiento por codigo.</t>
         </is>
       </c>
     </row>
@@ -24431,5367 +24878,2518 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L92"/>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="6" customWidth="1" min="10" max="10"/>
-    <col width="46" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="54" customWidth="1" min="4" max="4"/>
+    <col width="104" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="inlineStr">
         <is>
-          <t>Sprint 5 · Una historia por funcionalidad, un modulo por persona</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="100" customHeight="1">
+          <t>Una subtarea de QA por historia: revisar y cerrar en Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="78" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>Una historia por cada funcionalidad del libro. Reparto por modulo completo y no por tarea, para que entre desarrolladores no haya tareas que se bloqueen: cada quien es dueno de sus modulos de punta a punta y las dependencias que quedan son de ambiente, concentradas en el bloque TEC. Quienes no programamos (Camila, Daniel, Santiago y Sara) llevamos un modulo cada uno, de validacion y verificacion; Daniel se ofrecio a llevar dos, M-01 y M-02. Trece historias de esos cinco modulos exigen codigo, asi que las ejecuta un desarrollador y el dueno del modulo las valida y acepta: son las unicas filas donde las dos columnas de persona no coinciden. Notificaciones (M-09) y pagos (M-11) entran como front contra mock, sin integracion real con el proveedor, porque el front tiene que existir completo. La visualizacion en mapa entra si o si. Cada historia lleva su subtarea de QA: Santiago revisa y es quien cierra en Done.</t>
+          <t>Acuerdo del 24-oct-2026: ninguna historia pasa a Done por si misma. Cada una lleva una subtarea de Santiago (QA) que revisa la evidencia contra los criterios de la historia y es quien la mueve a Done. QA decide el DoD (GOBIERNO_DEL_EQUIPO.md §2.3), asi que la subtarea es el punto de control: si la evidencia no cumple, la historia vuelve y no se cierra. Esto cierra el hueco del Sprint 4, donde 14 subtareas de QA existian pero tres historias (SCRUM-1063, 1066 y 1068) no tenian ninguna, pendiente PE4 de §6.5 del backlog.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>Subtarea</t>
         </is>
       </c>
       <c r="B4" s="25" t="inlineStr">
         <is>
-          <t>Func.</t>
+          <t>Historia</t>
         </is>
       </c>
       <c r="C4" s="25" t="inlineStr">
         <is>
-          <t>Modulo</t>
+          <t>Bloque</t>
         </is>
       </c>
       <c r="D4" s="25" t="inlineStr">
         <is>
-          <t>Funcionalidad</t>
+          <t>Titulo de la historia</t>
         </is>
       </c>
       <c r="E4" s="25" t="inlineStr">
         <is>
-          <t>RF / RNF</t>
-        </is>
-      </c>
-      <c r="F4" s="25" t="inlineStr">
-        <is>
-          <t>Tipo de trabajo</t>
-        </is>
-      </c>
-      <c r="G4" s="25" t="inlineStr">
-        <is>
-          <t>Estado hoy</t>
-        </is>
-      </c>
-      <c r="H4" s="25" t="inlineStr">
-        <is>
-          <t>Quien la ejecuta</t>
-        </is>
-      </c>
-      <c r="I4" s="25" t="inlineStr">
-        <is>
-          <t>Dueno del modulo (valida y acepta)</t>
-        </is>
-      </c>
-      <c r="J4" s="25" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="K4" s="25" t="inlineStr">
-        <is>
-          <t>En el Sprint 5</t>
-        </is>
-      </c>
-      <c r="L4" s="25" t="inlineStr">
-        <is>
-          <t>Subtarea de QA</t>
+          <t>Que revisa y cierra QA</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
-        <is>
-          <t>HU-M01-01</t>
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-01</t>
         </is>
       </c>
       <c r="B5" s="26" t="inlineStr">
         <is>
-          <t>M-01.1</t>
+          <t>VAL-01</t>
         </is>
       </c>
       <c r="C5" s="26" t="inlineStr">
         <is>
-          <t>M-01</t>
+          <t>Validacion</t>
         </is>
       </c>
       <c r="D5" s="26" t="inlineStr">
         <is>
-          <t>Registrar y administrar empresas (tenants)</t>
+          <t>Validar inicio de sesion con token real ES256 de extremo a extremo</t>
         </is>
       </c>
       <c r="E5" s="26" t="inlineStr">
         <is>
-          <t>RF-01</t>
-        </is>
-      </c>
-      <c r="F5" s="26" t="inlineStr">
-        <is>
-          <t>Correccion + validacion</t>
-        </is>
-      </c>
-      <c r="G5" s="26" t="inlineStr">
-        <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="H5" s="26" t="inlineStr">
-        <is>
-          <t>Daniel Avila</t>
-        </is>
-      </c>
-      <c r="I5" s="26" t="inlineStr">
-        <is>
-          <t>Daniel Avila</t>
-        </is>
-      </c>
-      <c r="J5" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K5" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L5" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M01-01</t>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="inlineStr">
-        <is>
-          <t>HU-M01-02</t>
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-02</t>
         </is>
       </c>
       <c r="B6" s="26" t="inlineStr">
         <is>
-          <t>M-01.2</t>
+          <t>VAL-02</t>
         </is>
       </c>
       <c r="C6" s="26" t="inlineStr">
         <is>
-          <t>M-01</t>
+          <t>Validacion</t>
         </is>
       </c>
       <c r="D6" s="26" t="inlineStr">
         <is>
-          <t>Aislamiento estricto de datos y archivos por tenant</t>
+          <t>Validar registro de aliado persona natural por el camino Gateway-Core</t>
         </is>
       </c>
       <c r="E6" s="26" t="inlineStr">
         <is>
-          <t>RNF-01 / REST-04</t>
-        </is>
-      </c>
-      <c r="F6" s="26" t="inlineStr">
-        <is>
-          <t>Correccion + validacion</t>
-        </is>
-      </c>
-      <c r="G6" s="26" t="inlineStr">
-        <is>
-          <t>Parcial con defecto abierto</t>
-        </is>
-      </c>
-      <c r="H6" s="26" t="inlineStr">
-        <is>
-          <t>Daniel Avila</t>
-        </is>
-      </c>
-      <c r="I6" s="26" t="inlineStr">
-        <is>
-          <t>Daniel Avila</t>
-        </is>
-      </c>
-      <c r="J6" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K6" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L6" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M01-02</t>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="31" t="inlineStr">
-        <is>
-          <t>HU-M01-03</t>
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-03</t>
         </is>
       </c>
       <c r="B7" s="26" t="inlineStr">
         <is>
-          <t>M-01.3</t>
+          <t>VAL-03</t>
         </is>
       </c>
       <c r="C7" s="26" t="inlineStr">
         <is>
-          <t>M-01</t>
+          <t>Validacion</t>
         </is>
       </c>
       <c r="D7" s="26" t="inlineStr">
         <is>
-          <t>Configurar reglas operativas propias por tenant</t>
+          <t>Validar registro de aliado empresa</t>
         </is>
       </c>
       <c r="E7" s="26" t="inlineStr">
         <is>
-          <t>RF-02 / RNF-02 / RNF-10 / REST-05</t>
-        </is>
-      </c>
-      <c r="F7" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G7" s="26" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H7" s="33" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="I7" s="26" t="inlineStr">
-        <is>
-          <t>Daniel Avila</t>
-        </is>
-      </c>
-      <c r="J7" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K7" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L7" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M01-03</t>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="inlineStr">
-        <is>
-          <t>HU-M01-04</t>
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-04</t>
         </is>
       </c>
       <c r="B8" s="26" t="inlineStr">
         <is>
-          <t>M-01.4</t>
+          <t>VAL-04</t>
         </is>
       </c>
       <c r="C8" s="26" t="inlineStr">
         <is>
-          <t>M-01</t>
+          <t>Validacion</t>
         </is>
       </c>
       <c r="D8" s="26" t="inlineStr">
         <is>
-          <t>Identificacion de tenant no falsificable (claim obligatorio)</t>
+          <t>Validar registro de cliente persona natural</t>
         </is>
       </c>
       <c r="E8" s="26" t="inlineStr">
         <is>
-          <t>RNF-01 / ADR-0018</t>
-        </is>
-      </c>
-      <c r="F8" s="26" t="inlineStr">
-        <is>
-          <t>Correccion + validacion</t>
-        </is>
-      </c>
-      <c r="G8" s="26" t="inlineStr">
-        <is>
-          <t>Implementado con defecto abierto</t>
-        </is>
-      </c>
-      <c r="H8" s="26" t="inlineStr">
-        <is>
-          <t>Daniel Avila</t>
-        </is>
-      </c>
-      <c r="I8" s="26" t="inlineStr">
-        <is>
-          <t>Daniel Avila</t>
-        </is>
-      </c>
-      <c r="J8" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K8" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L8" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M01-04</t>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="28" t="inlineStr">
         <is>
-          <t>HU-M01-05</t>
+          <t>QA-VAL-05</t>
         </is>
       </c>
       <c r="B9" s="26" t="inlineStr">
         <is>
-          <t>M-01.5</t>
+          <t>VAL-05</t>
         </is>
       </c>
       <c r="C9" s="26" t="inlineStr">
         <is>
-          <t>M-01</t>
+          <t>Validacion</t>
         </is>
       </c>
       <c r="D9" s="26" t="inlineStr">
         <is>
-          <t>Propiedad del esquema y de las migraciones en un solo servicio</t>
+          <t>Validar edicion del perfil propio</t>
         </is>
       </c>
       <c r="E9" s="26" t="inlineStr">
         <is>
-          <t>ADR-0030 §1</t>
-        </is>
-      </c>
-      <c r="F9" s="26" t="inlineStr">
-        <is>
-          <t>Validacion de lo implementado</t>
-        </is>
-      </c>
-      <c r="G9" s="26" t="inlineStr">
-        <is>
-          <t>Conforme</t>
-        </is>
-      </c>
-      <c r="H9" s="26" t="inlineStr">
-        <is>
-          <t>Daniel Avila</t>
-        </is>
-      </c>
-      <c r="I9" s="26" t="inlineStr">
-        <is>
-          <t>Daniel Avila</t>
-        </is>
-      </c>
-      <c r="J9" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="K9" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L9" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M01-05</t>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="28" t="inlineStr">
         <is>
-          <t>HU-M02-01</t>
+          <t>QA-VAL-06</t>
         </is>
       </c>
       <c r="B10" s="26" t="inlineStr">
         <is>
-          <t>M-02.1</t>
+          <t>VAL-06</t>
         </is>
       </c>
       <c r="C10" s="26" t="inlineStr">
         <is>
-          <t>M-02</t>
+          <t>Validacion</t>
         </is>
       </c>
       <c r="D10" s="26" t="inlineStr">
         <is>
-          <t>Inicio de sesion</t>
+          <t>Validar aprobacion y rechazo de aliado en la bandeja de verificacion</t>
         </is>
       </c>
       <c r="E10" s="26" t="inlineStr">
         <is>
-          <t>RF-03</t>
-        </is>
-      </c>
-      <c r="F10" s="26" t="inlineStr">
-        <is>
-          <t>Validacion de lo implementado</t>
-        </is>
-      </c>
-      <c r="G10" s="26" t="inlineStr">
-        <is>
-          <t>Implementado (solo HS256)</t>
-        </is>
-      </c>
-      <c r="H10" s="26" t="inlineStr">
-        <is>
-          <t>Daniel Avila</t>
-        </is>
-      </c>
-      <c r="I10" s="26" t="inlineStr">
-        <is>
-          <t>Daniel Avila</t>
-        </is>
-      </c>
-      <c r="J10" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L10" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M02-01</t>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="inlineStr">
-        <is>
-          <t>HU-M02-02</t>
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-07</t>
         </is>
       </c>
       <c r="B11" s="26" t="inlineStr">
         <is>
-          <t>M-02.2</t>
+          <t>VAL-07</t>
         </is>
       </c>
       <c r="C11" s="26" t="inlineStr">
         <is>
-          <t>M-02</t>
+          <t>Validacion</t>
         </is>
       </c>
       <c r="D11" s="26" t="inlineStr">
         <is>
-          <t>Inicio de sesion separado por tipo de usuario</t>
+          <t>Validar declaracion de cobertura por zonas del aliado</t>
         </is>
       </c>
       <c r="E11" s="26" t="inlineStr">
         <is>
-          <t>RF-03</t>
-        </is>
-      </c>
-      <c r="F11" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G11" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H11" s="33" t="inlineStr">
-        <is>
-          <t>Nicolas Leon</t>
-        </is>
-      </c>
-      <c r="I11" s="26" t="inlineStr">
-        <is>
-          <t>Daniel Avila</t>
-        </is>
-      </c>
-      <c r="J11" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K11" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L11" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M02-02</t>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="31" t="inlineStr">
-        <is>
-          <t>HU-M02-03</t>
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-08</t>
         </is>
       </c>
       <c r="B12" s="26" t="inlineStr">
         <is>
-          <t>M-02.3</t>
+          <t>VAL-08</t>
         </is>
       </c>
       <c r="C12" s="26" t="inlineStr">
         <is>
-          <t>M-02</t>
+          <t>Validacion</t>
         </is>
       </c>
       <c r="D12" s="26" t="inlineStr">
         <is>
-          <t>Logout</t>
+          <t>Validar que el aliado declara las categorias que atiende</t>
         </is>
       </c>
       <c r="E12" s="26" t="inlineStr">
         <is>
-          <t>RF-03</t>
-        </is>
-      </c>
-      <c r="F12" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G12" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H12" s="33" t="inlineStr">
-        <is>
-          <t>Nicolas Leon</t>
-        </is>
-      </c>
-      <c r="I12" s="26" t="inlineStr">
-        <is>
-          <t>Daniel Avila</t>
-        </is>
-      </c>
-      <c r="J12" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K12" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L12" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M02-03</t>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="28" t="inlineStr">
         <is>
-          <t>HU-M02-04</t>
+          <t>QA-VAL-09</t>
         </is>
       </c>
       <c r="B13" s="26" t="inlineStr">
         <is>
-          <t>M-02.4</t>
+          <t>VAL-09</t>
         </is>
       </c>
       <c r="C13" s="26" t="inlineStr">
         <is>
-          <t>M-02</t>
+          <t>Validacion</t>
         </is>
       </c>
       <c r="D13" s="26" t="inlineStr">
         <is>
-          <t>Registro de aliado persona natural con documentos KYC</t>
+          <t>Validar gestion de categorias del tenant</t>
         </is>
       </c>
       <c r="E13" s="26" t="inlineStr">
         <is>
-          <t>RF-05</t>
-        </is>
-      </c>
-      <c r="F13" s="26" t="inlineStr">
-        <is>
-          <t>Validacion de lo implementado</t>
-        </is>
-      </c>
-      <c r="G13" s="26" t="inlineStr">
-        <is>
-          <t>Done sin validar en arquitectura vigente</t>
-        </is>
-      </c>
-      <c r="H13" s="26" t="inlineStr">
-        <is>
-          <t>Daniel Avila</t>
-        </is>
-      </c>
-      <c r="I13" s="26" t="inlineStr">
-        <is>
-          <t>Daniel Avila</t>
-        </is>
-      </c>
-      <c r="J13" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="K13" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L13" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M02-04</t>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="28" t="inlineStr">
         <is>
-          <t>HU-M02-05</t>
+          <t>QA-VAL-10</t>
         </is>
       </c>
       <c r="B14" s="26" t="inlineStr">
         <is>
-          <t>M-02.5</t>
+          <t>VAL-10</t>
         </is>
       </c>
       <c r="C14" s="26" t="inlineStr">
         <is>
-          <t>M-02</t>
+          <t>Validacion</t>
         </is>
       </c>
       <c r="D14" s="26" t="inlineStr">
         <is>
-          <t>Registro de aliado empresa</t>
+          <t>Validar creacion de la solicitud en Core desde el front</t>
         </is>
       </c>
       <c r="E14" s="26" t="inlineStr">
         <is>
-          <t>RF-05</t>
-        </is>
-      </c>
-      <c r="F14" s="26" t="inlineStr">
-        <is>
-          <t>Validacion de lo implementado</t>
-        </is>
-      </c>
-      <c r="G14" s="26" t="inlineStr">
-        <is>
-          <t>Done sin validar en arquitectura vigente</t>
-        </is>
-      </c>
-      <c r="H14" s="26" t="inlineStr">
-        <is>
-          <t>Daniel Avila</t>
-        </is>
-      </c>
-      <c r="I14" s="26" t="inlineStr">
-        <is>
-          <t>Daniel Avila</t>
-        </is>
-      </c>
-      <c r="J14" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="K14" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L14" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M02-05</t>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="28" t="inlineStr">
         <is>
-          <t>HU-M02-06</t>
+          <t>QA-VAL-11</t>
         </is>
       </c>
       <c r="B15" s="26" t="inlineStr">
         <is>
-          <t>M-02.6</t>
+          <t>VAL-11</t>
         </is>
       </c>
       <c r="C15" s="26" t="inlineStr">
         <is>
-          <t>M-02</t>
+          <t>Validacion</t>
         </is>
       </c>
       <c r="D15" s="26" t="inlineStr">
         <is>
-          <t>Registro de cliente persona natural</t>
+          <t>Validar elegibilidad de aliados por categoria, zona, disponibilidad y rechazo previo</t>
         </is>
       </c>
       <c r="E15" s="26" t="inlineStr">
         <is>
-          <t>RF-08</t>
-        </is>
-      </c>
-      <c r="F15" s="26" t="inlineStr">
-        <is>
-          <t>Validacion de lo implementado</t>
-        </is>
-      </c>
-      <c r="G15" s="26" t="inlineStr">
-        <is>
-          <t>Done sin validar en arquitectura vigente</t>
-        </is>
-      </c>
-      <c r="H15" s="26" t="inlineStr">
-        <is>
-          <t>Daniel Avila</t>
-        </is>
-      </c>
-      <c r="I15" s="26" t="inlineStr">
-        <is>
-          <t>Daniel Avila</t>
-        </is>
-      </c>
-      <c r="J15" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="K15" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L15" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M02-06</t>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="31" t="inlineStr">
-        <is>
-          <t>HU-M02-07</t>
+      <c r="A16" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-12</t>
         </is>
       </c>
       <c r="B16" s="26" t="inlineStr">
         <is>
-          <t>M-02.7</t>
+          <t>VAL-12</t>
         </is>
       </c>
       <c r="C16" s="26" t="inlineStr">
         <is>
-          <t>M-02</t>
+          <t>Validacion</t>
         </is>
       </c>
       <c r="D16" s="26" t="inlineStr">
         <is>
-          <t>Registro de cliente empresa</t>
+          <t>Validar filtro por tipo de aliado</t>
         </is>
       </c>
       <c r="E16" s="26" t="inlineStr">
         <is>
-          <t>RF-08</t>
-        </is>
-      </c>
-      <c r="F16" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G16" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H16" s="33" t="inlineStr">
-        <is>
-          <t>Nicolas Leon</t>
-        </is>
-      </c>
-      <c r="I16" s="26" t="inlineStr">
-        <is>
-          <t>Daniel Avila</t>
-        </is>
-      </c>
-      <c r="J16" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K16" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L16" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M02-07</t>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="31" t="inlineStr">
-        <is>
-          <t>HU-M02-08</t>
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-13</t>
         </is>
       </c>
       <c r="B17" s="26" t="inlineStr">
         <is>
-          <t>M-02.8</t>
+          <t>VAL-13</t>
         </is>
       </c>
       <c r="C17" s="26" t="inlineStr">
         <is>
-          <t>M-02</t>
+          <t>Validacion</t>
         </is>
       </c>
       <c r="D17" s="26" t="inlineStr">
         <is>
-          <t>Registro de empleado directo</t>
+          <t>Validar aceptacion sin doble asignacion con dos aliados simultaneos</t>
         </is>
       </c>
       <c r="E17" s="26" t="inlineStr">
         <is>
-          <t>RF-05</t>
-        </is>
-      </c>
-      <c r="F17" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G17" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H17" s="33" t="inlineStr">
-        <is>
-          <t>Nicolas Leon</t>
-        </is>
-      </c>
-      <c r="I17" s="26" t="inlineStr">
-        <is>
-          <t>Daniel Avila</t>
-        </is>
-      </c>
-      <c r="J17" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K17" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L17" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M02-08</t>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="29" t="inlineStr">
-        <is>
-          <t>HU-M02-09</t>
+      <c r="A18" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-14</t>
         </is>
       </c>
       <c r="B18" s="26" t="inlineStr">
         <is>
-          <t>M-02.9</t>
+          <t>VAL-14</t>
         </is>
       </c>
       <c r="C18" s="26" t="inlineStr">
         <is>
-          <t>M-02</t>
+          <t>Validacion</t>
         </is>
       </c>
       <c r="D18" s="26" t="inlineStr">
         <is>
-          <t>Edicion del perfil propio</t>
+          <t>Validar rechazo de oferta</t>
         </is>
       </c>
       <c r="E18" s="26" t="inlineStr">
         <is>
-          <t>RF-30 / RF-05 / RF-08</t>
-        </is>
-      </c>
-      <c r="F18" s="26" t="inlineStr">
-        <is>
-          <t>Terminar + validacion</t>
-        </is>
-      </c>
-      <c r="G18" s="26" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="H18" s="26" t="inlineStr">
-        <is>
-          <t>Daniel Avila</t>
-        </is>
-      </c>
-      <c r="I18" s="26" t="inlineStr">
-        <is>
-          <t>Daniel Avila</t>
-        </is>
-      </c>
-      <c r="J18" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K18" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L18" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M02-09</t>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="31" t="inlineStr">
-        <is>
-          <t>HU-M02-10</t>
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-15</t>
         </is>
       </c>
       <c r="B19" s="26" t="inlineStr">
         <is>
-          <t>M-02.10</t>
+          <t>VAL-15</t>
         </is>
       </c>
       <c r="C19" s="26" t="inlineStr">
         <is>
-          <t>M-02</t>
+          <t>Validacion</t>
         </is>
       </c>
       <c r="D19" s="26" t="inlineStr">
         <is>
-          <t>Recuperacion segura de contrasena</t>
+          <t>Validar broadcast de ofertas y notificacion por la frontera de Core</t>
         </is>
       </c>
       <c r="E19" s="26" t="inlineStr">
         <is>
-          <t>RF-04</t>
-        </is>
-      </c>
-      <c r="F19" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G19" s="26" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="H19" s="33" t="inlineStr">
-        <is>
-          <t>Nicolas Leon</t>
-        </is>
-      </c>
-      <c r="I19" s="26" t="inlineStr">
-        <is>
-          <t>Daniel Avila</t>
-        </is>
-      </c>
-      <c r="J19" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K19" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L19" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M02-10</t>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="inlineStr">
-        <is>
-          <t>HU-M02-11</t>
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-16</t>
         </is>
       </c>
       <c r="B20" s="26" t="inlineStr">
         <is>
-          <t>M-02.11</t>
+          <t>VAL-16</t>
         </is>
       </c>
       <c r="C20" s="26" t="inlineStr">
         <is>
-          <t>M-02</t>
+          <t>Validacion</t>
         </is>
       </c>
       <c r="D20" s="26" t="inlineStr">
         <is>
-          <t>Aceptacion de Terminos y Condiciones</t>
+          <t>Validar aislamiento multi-tenant endpoint por endpoint</t>
         </is>
       </c>
       <c r="E20" s="26" t="inlineStr">
         <is>
-          <t>RF-31</t>
-        </is>
-      </c>
-      <c r="F20" s="26" t="inlineStr">
-        <is>
-          <t>Correccion + validacion</t>
-        </is>
-      </c>
-      <c r="G20" s="26" t="inlineStr">
-        <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="H20" s="26" t="inlineStr">
-        <is>
-          <t>Daniel Avila</t>
-        </is>
-      </c>
-      <c r="I20" s="26" t="inlineStr">
-        <is>
-          <t>Daniel Avila</t>
-        </is>
-      </c>
-      <c r="J20" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K20" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L20" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M02-11</t>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="29" t="inlineStr">
-        <is>
-          <t>HU-M02-12</t>
+      <c r="A21" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-17</t>
         </is>
       </c>
       <c r="B21" s="26" t="inlineStr">
         <is>
-          <t>M-02.12</t>
+          <t>VAL-17</t>
         </is>
       </c>
       <c r="C21" s="26" t="inlineStr">
         <is>
-          <t>M-02</t>
+          <t>Validacion</t>
         </is>
       </c>
       <c r="D21" s="26" t="inlineStr">
         <is>
-          <t>Autenticacion consumida desde la API y no desde Supabase directo en el cliente</t>
+          <t>Validar logout y expiracion de sesion</t>
         </is>
       </c>
       <c r="E21" s="26" t="inlineStr">
         <is>
-          <t>RF-03 / ADR-0027</t>
-        </is>
-      </c>
-      <c r="F21" s="26" t="inlineStr">
-        <is>
-          <t>Correccion + validacion</t>
-        </is>
-      </c>
-      <c r="G21" s="26" t="inlineStr">
-        <is>
-          <t>Parcial (migracion en curso)</t>
-        </is>
-      </c>
-      <c r="H21" s="26" t="inlineStr">
-        <is>
-          <t>Daniel Avila</t>
-        </is>
-      </c>
-      <c r="I21" s="26" t="inlineStr">
-        <is>
-          <t>Daniel Avila</t>
-        </is>
-      </c>
-      <c r="J21" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K21" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L21" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M02-12</t>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="29" t="inlineStr">
-        <is>
-          <t>HU-M02-13</t>
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-18</t>
         </is>
       </c>
       <c r="B22" s="26" t="inlineStr">
         <is>
-          <t>M-02.13</t>
+          <t>VAL-18</t>
         </is>
       </c>
       <c r="C22" s="26" t="inlineStr">
         <is>
-          <t>M-02</t>
+          <t>Validacion</t>
         </is>
       </c>
       <c r="D22" s="26" t="inlineStr">
         <is>
-          <t>Validacion perimetral del token y propagacion de claims</t>
+          <t>Ejecutar la regresion de seguridad de identidad (17 casos negativos y 1 positivo)</t>
         </is>
       </c>
       <c r="E22" s="26" t="inlineStr">
         <is>
-          <t>RF-03</t>
-        </is>
-      </c>
-      <c r="F22" s="26" t="inlineStr">
-        <is>
-          <t>Correccion + validacion</t>
-        </is>
-      </c>
-      <c r="G22" s="26" t="inlineStr">
-        <is>
-          <t>Implementado con defecto abierto</t>
-        </is>
-      </c>
-      <c r="H22" s="26" t="inlineStr">
-        <is>
-          <t>Daniel Avila</t>
-        </is>
-      </c>
-      <c r="I22" s="26" t="inlineStr">
-        <is>
-          <t>Daniel Avila</t>
-        </is>
-      </c>
-      <c r="J22" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K22" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L22" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M02-13</t>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="28" t="inlineStr">
         <is>
-          <t>HU-M02-14</t>
+          <t>QA-VAL-19</t>
         </is>
       </c>
       <c r="B23" s="26" t="inlineStr">
         <is>
-          <t>M-02.14</t>
+          <t>VAL-19</t>
         </is>
       </c>
       <c r="C23" s="26" t="inlineStr">
         <is>
-          <t>M-02</t>
+          <t>Validacion</t>
         </is>
       </c>
       <c r="D23" s="26" t="inlineStr">
         <is>
-          <t>Autorizacion por rol y tenant en cada peticion</t>
+          <t>Validar el contrato del perfil del aliado que consumen Dispatch y Rules</t>
         </is>
       </c>
       <c r="E23" s="26" t="inlineStr">
         <is>
-          <t>RF-03</t>
-        </is>
-      </c>
-      <c r="F23" s="26" t="inlineStr">
-        <is>
-          <t>Validacion de lo implementado</t>
-        </is>
-      </c>
-      <c r="G23" s="26" t="inlineStr">
-        <is>
-          <t>Implementado</t>
-        </is>
-      </c>
-      <c r="H23" s="26" t="inlineStr">
-        <is>
-          <t>Daniel Avila</t>
-        </is>
-      </c>
-      <c r="I23" s="26" t="inlineStr">
-        <is>
-          <t>Daniel Avila</t>
-        </is>
-      </c>
-      <c r="J23" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="K23" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L23" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M02-14</t>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="29" t="inlineStr">
-        <is>
-          <t>HU-M02-15</t>
+      <c r="A24" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-20</t>
         </is>
       </c>
       <c r="B24" s="26" t="inlineStr">
         <is>
-          <t>M-02.15</t>
+          <t>VAL-20</t>
         </is>
       </c>
       <c r="C24" s="26" t="inlineStr">
         <is>
-          <t>M-02</t>
+          <t>Validacion</t>
         </is>
       </c>
       <c r="D24" s="26" t="inlineStr">
         <is>
-          <t>Cifrado de credenciales y de datos sensibles</t>
+          <t>Validar que el catalogo responde solo las categorias y zonas del tenant del claim</t>
         </is>
       </c>
       <c r="E24" s="26" t="inlineStr">
         <is>
-          <t>RNF-01 / REST-02</t>
-        </is>
-      </c>
-      <c r="F24" s="26" t="inlineStr">
-        <is>
-          <t>Correccion + validacion</t>
-        </is>
-      </c>
-      <c r="G24" s="26" t="inlineStr">
-        <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="H24" s="26" t="inlineStr">
-        <is>
-          <t>Daniel Avila</t>
-        </is>
-      </c>
-      <c r="I24" s="26" t="inlineStr">
-        <is>
-          <t>Daniel Avila</t>
-        </is>
-      </c>
-      <c r="J24" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K24" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L24" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M02-15</t>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="28" t="inlineStr">
         <is>
-          <t>HU-M03-01</t>
+          <t>QA-VAL-21</t>
         </is>
       </c>
       <c r="B25" s="26" t="inlineStr">
         <is>
-          <t>M-03.1</t>
+          <t>VAL-21</t>
         </is>
       </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>M-03</t>
+          <t>Validacion</t>
         </is>
       </c>
       <c r="D25" s="26" t="inlineStr">
         <is>
-          <t>Bandeja de verificacion: aprobar o rechazar aliado</t>
+          <t>Validar el contexto de solicitud que Dispatch pide a Core</t>
         </is>
       </c>
       <c r="E25" s="26" t="inlineStr">
         <is>
-          <t>RF-06</t>
-        </is>
-      </c>
-      <c r="F25" s="26" t="inlineStr">
-        <is>
-          <t>Validacion de lo implementado</t>
-        </is>
-      </c>
-      <c r="G25" s="26" t="inlineStr">
-        <is>
-          <t>Done sin validar en arquitectura vigente</t>
-        </is>
-      </c>
-      <c r="H25" s="26" t="inlineStr">
-        <is>
-          <t>Camila Beltran (PO)</t>
-        </is>
-      </c>
-      <c r="I25" s="26" t="inlineStr">
-        <is>
-          <t>Camila Beltran (PO)</t>
-        </is>
-      </c>
-      <c r="J25" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="K25" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L25" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M03-01</t>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="29" t="inlineStr">
-        <is>
-          <t>HU-M03-02</t>
+      <c r="A26" s="28" t="inlineStr">
+        <is>
+          <t>QA-VAL-22</t>
         </is>
       </c>
       <c r="B26" s="26" t="inlineStr">
         <is>
-          <t>M-03.2</t>
+          <t>VAL-22</t>
         </is>
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>M-03</t>
+          <t>Validacion</t>
         </is>
       </c>
       <c r="D26" s="26" t="inlineStr">
         <is>
-          <t>Declarar zonas de cobertura del aliado</t>
+          <t>Validar idempotencia de la creacion de solicitud y del despacho bajo reintento</t>
         </is>
       </c>
       <c r="E26" s="26" t="inlineStr">
         <is>
-          <t>RF-07</t>
-        </is>
-      </c>
-      <c r="F26" s="26" t="inlineStr">
-        <is>
-          <t>Terminar + validacion</t>
-        </is>
-      </c>
-      <c r="G26" s="26" t="inlineStr">
-        <is>
-          <t>Reespecificada</t>
-        </is>
-      </c>
-      <c r="H26" s="26" t="inlineStr">
-        <is>
-          <t>Camila Beltran (PO)</t>
-        </is>
-      </c>
-      <c r="I26" s="26" t="inlineStr">
-        <is>
-          <t>Camila Beltran (PO)</t>
-        </is>
-      </c>
-      <c r="J26" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K26" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L26" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M03-02</t>
+          <t>Comprueba que el video existe, que se grabo desde el front y no desde Postman ni consola, que corre en QA por el Gateway, que el token es real ES256 y no dev-token, que se ve el usuario y el rol con el que entra, la accion completa y el resultado persistido al recargar, y que incluye el caso negativo de aislamiento. Duracion maxima 4 minutos sin cortes en el tramo de persistencia. Evidencia enlazada con el SHA desplegado y la fecha. Si falta cualquiera de estos, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="29" t="inlineStr">
-        <is>
-          <t>HU-M03-03</t>
+      <c r="A27" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-01</t>
         </is>
       </c>
       <c r="B27" s="26" t="inlineStr">
         <is>
-          <t>M-03.3</t>
+          <t>CONS-01</t>
         </is>
       </c>
       <c r="C27" s="26" t="inlineStr">
         <is>
-          <t>M-03</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D27" s="26" t="inlineStr">
         <is>
-          <t>Disponibilidad y ausencias del aliado</t>
+          <t>Inicio de sesion separado por tipo de usuario</t>
         </is>
       </c>
       <c r="E27" s="26" t="inlineStr">
         <is>
-          <t>RF-29 / RF-12 (soporte)</t>
-        </is>
-      </c>
-      <c r="F27" s="26" t="inlineStr">
-        <is>
-          <t>Correccion + validacion</t>
-        </is>
-      </c>
-      <c r="G27" s="26" t="inlineStr">
-        <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="H27" s="26" t="inlineStr">
-        <is>
-          <t>Camila Beltran (PO)</t>
-        </is>
-      </c>
-      <c r="I27" s="26" t="inlineStr">
-        <is>
-          <t>Camila Beltran (PO)</t>
-        </is>
-      </c>
-      <c r="J27" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K27" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L27" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M03-03</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="31" t="inlineStr">
         <is>
-          <t>HU-M03-04</t>
+          <t>QA-CONS-02</t>
         </is>
       </c>
       <c r="B28" s="26" t="inlineStr">
         <is>
-          <t>M-03.4</t>
+          <t>CONS-02</t>
         </is>
       </c>
       <c r="C28" s="26" t="inlineStr">
         <is>
-          <t>M-03</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D28" s="26" t="inlineStr">
         <is>
-          <t>Cliente empresa administra multiples sitios de servicio</t>
+          <t>Logout</t>
         </is>
       </c>
       <c r="E28" s="26" t="inlineStr">
         <is>
-          <t>RF-08</t>
-        </is>
-      </c>
-      <c r="F28" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G28" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H28" s="33" t="inlineStr">
-        <is>
-          <t>Jose Nicolas Alvarez</t>
-        </is>
-      </c>
-      <c r="I28" s="26" t="inlineStr">
-        <is>
-          <t>Camila Beltran (PO)</t>
-        </is>
-      </c>
-      <c r="J28" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K28" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L28" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M03-04</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="31" t="inlineStr">
         <is>
-          <t>HU-M03-05</t>
+          <t>QA-CONS-03</t>
         </is>
       </c>
       <c r="B29" s="26" t="inlineStr">
         <is>
-          <t>M-03.5</t>
+          <t>CONS-03</t>
         </is>
       </c>
       <c r="C29" s="26" t="inlineStr">
         <is>
-          <t>M-03</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D29" s="26" t="inlineStr">
         <is>
-          <t>Reglas contextuales del sitio visibles al aliado antes de programar</t>
+          <t>Autenticacion consumida desde la API y retiro de Supabase directo en el cliente</t>
         </is>
       </c>
       <c r="E29" s="26" t="inlineStr">
         <is>
-          <t>RF-09</t>
-        </is>
-      </c>
-      <c r="F29" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G29" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H29" s="33" t="inlineStr">
-        <is>
-          <t>Jose Nicolas Alvarez</t>
-        </is>
-      </c>
-      <c r="I29" s="26" t="inlineStr">
-        <is>
-          <t>Camila Beltran (PO)</t>
-        </is>
-      </c>
-      <c r="J29" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K29" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L29" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M03-05</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="28" t="inlineStr">
-        <is>
-          <t>HU-M03-06</t>
+      <c r="A30" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-04</t>
         </is>
       </c>
       <c r="B30" s="26" t="inlineStr">
         <is>
-          <t>M-03.6</t>
+          <t>CONS-04</t>
         </is>
       </c>
       <c r="C30" s="26" t="inlineStr">
         <is>
-          <t>M-03</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D30" s="26" t="inlineStr">
         <is>
-          <t>Perfil del aliado autenticado consumible por otros servicios</t>
+          <t>Recuperacion segura de contrasena</t>
         </is>
       </c>
       <c r="E30" s="26" t="inlineStr">
         <is>
-          <t>RF-30 / RF-05</t>
-        </is>
-      </c>
-      <c r="F30" s="26" t="inlineStr">
-        <is>
-          <t>Validacion de lo implementado</t>
-        </is>
-      </c>
-      <c r="G30" s="26" t="inlineStr">
-        <is>
-          <t>Implementado</t>
-        </is>
-      </c>
-      <c r="H30" s="26" t="inlineStr">
-        <is>
-          <t>Camila Beltran (PO)</t>
-        </is>
-      </c>
-      <c r="I30" s="26" t="inlineStr">
-        <is>
-          <t>Camila Beltran (PO)</t>
-        </is>
-      </c>
-      <c r="J30" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="K30" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L30" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M03-06</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="28" t="inlineStr">
-        <is>
-          <t>HU-M04-01</t>
+      <c r="A31" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-05</t>
         </is>
       </c>
       <c r="B31" s="26" t="inlineStr">
         <is>
-          <t>M-04.1</t>
+          <t>CONS-05</t>
         </is>
       </c>
       <c r="C31" s="26" t="inlineStr">
         <is>
-          <t>M-04</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D31" s="26" t="inlineStr">
         <is>
-          <t>Crear categoria de servicio con flujo operativo</t>
+          <t>Registro de cliente empresa</t>
         </is>
       </c>
       <c r="E31" s="26" t="inlineStr">
         <is>
-          <t>RF-10</t>
-        </is>
-      </c>
-      <c r="F31" s="26" t="inlineStr">
-        <is>
-          <t>Validacion de lo implementado</t>
-        </is>
-      </c>
-      <c r="G31" s="26" t="inlineStr">
-        <is>
-          <t>Done sin validar en arquitectura vigente</t>
-        </is>
-      </c>
-      <c r="H31" s="26" t="inlineStr">
-        <is>
-          <t>Sara Albarracin (SM)</t>
-        </is>
-      </c>
-      <c r="I31" s="26" t="inlineStr">
-        <is>
-          <t>Sara Albarracin (SM)</t>
-        </is>
-      </c>
-      <c r="J31" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="K31" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L31" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M04-01</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="31" t="inlineStr">
         <is>
-          <t>HU-M04-02</t>
+          <t>QA-CONS-06</t>
         </is>
       </c>
       <c r="B32" s="26" t="inlineStr">
         <is>
-          <t>M-04.2</t>
+          <t>CONS-06</t>
         </is>
       </c>
       <c r="C32" s="26" t="inlineStr">
         <is>
-          <t>M-04</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D32" s="26" t="inlineStr">
         <is>
-          <t>Activar y desactivar categoria sin afectar servicios en curso</t>
+          <t>Registro de empleado directo</t>
         </is>
       </c>
       <c r="E32" s="26" t="inlineStr">
         <is>
-          <t>RF-10</t>
-        </is>
-      </c>
-      <c r="F32" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G32" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H32" s="33" t="inlineStr">
-        <is>
-          <t>Jose Nicolas Alvarez</t>
-        </is>
-      </c>
-      <c r="I32" s="26" t="inlineStr">
-        <is>
-          <t>Sara Albarracin (SM)</t>
-        </is>
-      </c>
-      <c r="J32" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K32" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L32" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M04-02</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="29" t="inlineStr">
-        <is>
-          <t>HU-M04-03</t>
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-07</t>
         </is>
       </c>
       <c r="B33" s="26" t="inlineStr">
         <is>
-          <t>M-04.3</t>
+          <t>CONS-07</t>
         </is>
       </c>
       <c r="C33" s="26" t="inlineStr">
         <is>
-          <t>M-04</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D33" s="26" t="inlineStr">
         <is>
-          <t>Aliado declara las categorias que atiende</t>
+          <t>Menu superior por rol con sesion visible</t>
         </is>
       </c>
       <c r="E33" s="26" t="inlineStr">
         <is>
-          <t>RF-11</t>
-        </is>
-      </c>
-      <c r="F33" s="26" t="inlineStr">
-        <is>
-          <t>Terminar + validacion</t>
-        </is>
-      </c>
-      <c r="G33" s="26" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="H33" s="26" t="inlineStr">
-        <is>
-          <t>Sara Albarracin (SM)</t>
-        </is>
-      </c>
-      <c r="I33" s="26" t="inlineStr">
-        <is>
-          <t>Sara Albarracin (SM)</t>
-        </is>
-      </c>
-      <c r="J33" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K33" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L33" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M04-03</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="29" t="inlineStr">
-        <is>
-          <t>HU-M04-04</t>
+      <c r="A34" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-08</t>
         </is>
       </c>
       <c r="B34" s="26" t="inlineStr">
         <is>
-          <t>M-04.4</t>
+          <t>CONS-08</t>
         </is>
       </c>
       <c r="C34" s="26" t="inlineStr">
         <is>
-          <t>M-04</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D34" s="26" t="inlineStr">
         <is>
-          <t>Catalogo jerarquico de zonas geograficas</t>
+          <t>Pantalla de inicio por tipo de usuario</t>
         </is>
       </c>
       <c r="E34" s="26" t="inlineStr">
         <is>
-          <t>REST-01 / RNF-09</t>
-        </is>
-      </c>
-      <c r="F34" s="26" t="inlineStr">
-        <is>
-          <t>Correccion + validacion</t>
-        </is>
-      </c>
-      <c r="G34" s="26" t="inlineStr">
-        <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="H34" s="26" t="inlineStr">
-        <is>
-          <t>Sara Albarracin (SM)</t>
-        </is>
-      </c>
-      <c r="I34" s="26" t="inlineStr">
-        <is>
-          <t>Sara Albarracin (SM)</t>
-        </is>
-      </c>
-      <c r="J34" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K34" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L34" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M04-04</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="28" t="inlineStr">
-        <is>
-          <t>HU-M04-05</t>
+      <c r="A35" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-09</t>
         </is>
       </c>
       <c r="B35" s="26" t="inlineStr">
         <is>
-          <t>M-04.5</t>
+          <t>CONS-09</t>
         </is>
       </c>
       <c r="C35" s="26" t="inlineStr">
         <is>
-          <t>M-04</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D35" s="26" t="inlineStr">
         <is>
-          <t>Consulta del catalogo por tenant</t>
+          <t>Enrutamiento por rol con guardas de sesion</t>
         </is>
       </c>
       <c r="E35" s="26" t="inlineStr">
         <is>
-          <t>RF-10</t>
-        </is>
-      </c>
-      <c r="F35" s="26" t="inlineStr">
-        <is>
-          <t>Validacion de lo implementado</t>
-        </is>
-      </c>
-      <c r="G35" s="26" t="inlineStr">
-        <is>
-          <t>Implementado</t>
-        </is>
-      </c>
-      <c r="H35" s="26" t="inlineStr">
-        <is>
-          <t>Sara Albarracin (SM)</t>
-        </is>
-      </c>
-      <c r="I35" s="26" t="inlineStr">
-        <is>
-          <t>Sara Albarracin (SM)</t>
-        </is>
-      </c>
-      <c r="J35" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="K35" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L35" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M04-05</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="31" t="inlineStr">
         <is>
-          <t>HU-M04-06</t>
+          <t>QA-CONS-10</t>
         </is>
       </c>
       <c r="B36" s="26" t="inlineStr">
         <is>
-          <t>M-04.6</t>
+          <t>CONS-10</t>
         </is>
       </c>
       <c r="C36" s="26" t="inlineStr">
         <is>
-          <t>M-04</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D36" s="26" t="inlineStr">
         <is>
-          <t>Barrios como nivel mas fino de la jerarquia y cobertura por barrio</t>
+          <t>Dividir el front en modulos independientes por dominio</t>
         </is>
       </c>
       <c r="E36" s="26" t="inlineStr">
         <is>
-          <t>RF-07 / RNF-09</t>
-        </is>
-      </c>
-      <c r="F36" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G36" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H36" s="33" t="inlineStr">
-        <is>
-          <t>Jose Nicolas Alvarez</t>
-        </is>
-      </c>
-      <c r="I36" s="26" t="inlineStr">
-        <is>
-          <t>Sara Albarracin (SM)</t>
-        </is>
-      </c>
-      <c r="J36" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K36" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L36" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M04-06</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="31" t="inlineStr">
         <is>
-          <t>HU-M04-07</t>
+          <t>QA-CONS-11</t>
         </is>
       </c>
       <c r="B37" s="26" t="inlineStr">
         <is>
-          <t>M-04.7</t>
+          <t>CONS-11</t>
         </is>
       </c>
       <c r="C37" s="26" t="inlineStr">
         <is>
-          <t>M-04</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D37" s="26" t="inlineStr">
         <is>
-          <t>Visualizacion en mapa de zonas, barrios y del sitio de servicio</t>
+          <t>Dividir el Core por dominios internos</t>
         </is>
       </c>
       <c r="E37" s="26" t="inlineStr">
         <is>
-          <t>RNF-08</t>
-        </is>
-      </c>
-      <c r="F37" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G37" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H37" s="33" t="inlineStr">
-        <is>
-          <t>Jose Nicolas Alvarez</t>
-        </is>
-      </c>
-      <c r="I37" s="26" t="inlineStr">
-        <is>
-          <t>Sara Albarracin (SM)</t>
-        </is>
-      </c>
-      <c r="J37" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K37" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L37" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M04-07</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="28" t="inlineStr">
-        <is>
-          <t>HU-M05-01</t>
+      <c r="A38" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-12</t>
         </is>
       </c>
       <c r="B38" s="26" t="inlineStr">
         <is>
-          <t>M-05.1</t>
+          <t>CONS-12</t>
         </is>
       </c>
       <c r="C38" s="26" t="inlineStr">
         <is>
-          <t>M-05</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D38" s="26" t="inlineStr">
         <is>
-          <t>Crear y persistir la solicitud de servicio</t>
+          <t>Barrios como nivel mas fino del catalogo de zonas</t>
         </is>
       </c>
       <c r="E38" s="26" t="inlineStr">
         <is>
-          <t>RF-12</t>
-        </is>
-      </c>
-      <c r="F38" s="26" t="inlineStr">
-        <is>
-          <t>Validacion de lo implementado</t>
-        </is>
-      </c>
-      <c r="G38" s="26" t="inlineStr">
-        <is>
-          <t>Implementado en servicio, sin validar por el front</t>
-        </is>
-      </c>
-      <c r="H38" s="26" t="inlineStr">
-        <is>
-          <t>Santiago Hernandez (QA)</t>
-        </is>
-      </c>
-      <c r="I38" s="26" t="inlineStr">
-        <is>
-          <t>Santiago Hernandez (QA)</t>
-        </is>
-      </c>
-      <c r="J38" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="K38" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L38" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M05-01</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="28" t="inlineStr">
-        <is>
-          <t>HU-M05-02</t>
+      <c r="A39" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-13</t>
         </is>
       </c>
       <c r="B39" s="26" t="inlineStr">
         <is>
-          <t>M-05.2</t>
+          <t>CONS-13</t>
         </is>
       </c>
       <c r="C39" s="26" t="inlineStr">
         <is>
-          <t>M-05</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D39" s="26" t="inlineStr">
         <is>
-          <t>Elegibilidad: aliados validos por categoria, zona, disponibilidad y rechazo previo</t>
+          <t>Visualizacion en mapa de zonas, barrios y sitio de servicio</t>
         </is>
       </c>
       <c r="E39" s="26" t="inlineStr">
         <is>
-          <t>RF-12 / RNF-07</t>
-        </is>
-      </c>
-      <c r="F39" s="26" t="inlineStr">
-        <is>
-          <t>Validacion de lo implementado</t>
-        </is>
-      </c>
-      <c r="G39" s="26" t="inlineStr">
-        <is>
-          <t>Implementado en servicio, sin validar por el front</t>
-        </is>
-      </c>
-      <c r="H39" s="26" t="inlineStr">
-        <is>
-          <t>Santiago Hernandez (QA)</t>
-        </is>
-      </c>
-      <c r="I39" s="26" t="inlineStr">
-        <is>
-          <t>Santiago Hernandez (QA)</t>
-        </is>
-      </c>
-      <c r="J39" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="K39" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L39" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M05-02</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="28" t="inlineStr">
-        <is>
-          <t>HU-M05-03</t>
+      <c r="A40" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-14</t>
         </is>
       </c>
       <c r="B40" s="26" t="inlineStr">
         <is>
-          <t>M-05.3</t>
+          <t>CONS-14</t>
         </is>
       </c>
       <c r="C40" s="26" t="inlineStr">
         <is>
-          <t>M-05</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D40" s="26" t="inlineStr">
         <is>
-          <t>Contexto de la solicitud (zona, categoria, estado)</t>
+          <t>Activar y desactivar categoria sin afectar servicios en curso</t>
         </is>
       </c>
       <c r="E40" s="26" t="inlineStr">
         <is>
-          <t>RF-12</t>
-        </is>
-      </c>
-      <c r="F40" s="26" t="inlineStr">
-        <is>
-          <t>Validacion de lo implementado</t>
-        </is>
-      </c>
-      <c r="G40" s="26" t="inlineStr">
-        <is>
-          <t>Implementado</t>
-        </is>
-      </c>
-      <c r="H40" s="26" t="inlineStr">
-        <is>
-          <t>Santiago Hernandez (QA)</t>
-        </is>
-      </c>
-      <c r="I40" s="26" t="inlineStr">
-        <is>
-          <t>Santiago Hernandez (QA)</t>
-        </is>
-      </c>
-      <c r="J40" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="K40" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L40" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M05-03</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="28" t="inlineStr">
-        <is>
-          <t>HU-M05-04</t>
+      <c r="A41" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-15</t>
         </is>
       </c>
       <c r="B41" s="26" t="inlineStr">
         <is>
-          <t>M-05.4</t>
+          <t>CONS-15</t>
         </is>
       </c>
       <c r="C41" s="26" t="inlineStr">
         <is>
-          <t>M-05</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D41" s="26" t="inlineStr">
         <is>
-          <t>Filtrar aliados por tipo de aliado</t>
+          <t>Aliado gestiona su disponibilidad y sus ausencias</t>
         </is>
       </c>
       <c r="E41" s="26" t="inlineStr">
         <is>
-          <t>RF-12</t>
-        </is>
-      </c>
-      <c r="F41" s="26" t="inlineStr">
-        <is>
-          <t>Validacion de lo implementado</t>
-        </is>
-      </c>
-      <c r="G41" s="26" t="inlineStr">
-        <is>
-          <t>Implementado en servicio, sin validar por el front</t>
-        </is>
-      </c>
-      <c r="H41" s="26" t="inlineStr">
-        <is>
-          <t>Santiago Hernandez (QA)</t>
-        </is>
-      </c>
-      <c r="I41" s="26" t="inlineStr">
-        <is>
-          <t>Santiago Hernandez (QA)</t>
-        </is>
-      </c>
-      <c r="J41" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="K41" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L41" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M05-04</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="31" t="inlineStr">
         <is>
-          <t>HU-M05-05</t>
+          <t>QA-CONS-16</t>
         </is>
       </c>
       <c r="B42" s="26" t="inlineStr">
         <is>
-          <t>M-05.5</t>
+          <t>CONS-16</t>
         </is>
       </c>
       <c r="C42" s="26" t="inlineStr">
         <is>
-          <t>M-05</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D42" s="26" t="inlineStr">
         <is>
-          <t>Ordenar el listado de aliados segun la regla del tenant</t>
+          <t>Cliente empresa administra multiples sitios de servicio</t>
         </is>
       </c>
       <c r="E42" s="26" t="inlineStr">
         <is>
-          <t>RF-13</t>
-        </is>
-      </c>
-      <c r="F42" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G42" s="26" t="inlineStr">
-        <is>
-          <t>No implementado</t>
-        </is>
-      </c>
-      <c r="H42" s="33" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="I42" s="26" t="inlineStr">
-        <is>
-          <t>Santiago Hernandez (QA)</t>
-        </is>
-      </c>
-      <c r="J42" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K42" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L42" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M05-05</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="29" t="inlineStr">
-        <is>
-          <t>HU-M05-06</t>
+      <c r="A43" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-17</t>
         </is>
       </c>
       <c r="B43" s="26" t="inlineStr">
         <is>
-          <t>M-05.6</t>
+          <t>CONS-17</t>
         </is>
       </c>
       <c r="C43" s="26" t="inlineStr">
         <is>
-          <t>M-05</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D43" s="26" t="inlineStr">
         <is>
-          <t>Broadcast de ofertas a los aliados elegibles</t>
+          <t>Reglas contextuales del sitio visibles al aliado antes de programar</t>
         </is>
       </c>
       <c r="E43" s="26" t="inlineStr">
         <is>
-          <t>RF-14</t>
-        </is>
-      </c>
-      <c r="F43" s="26" t="inlineStr">
-        <is>
-          <t>Correccion + validacion</t>
-        </is>
-      </c>
-      <c r="G43" s="26" t="inlineStr">
-        <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="H43" s="26" t="inlineStr">
-        <is>
-          <t>Santiago Hernandez (QA)</t>
-        </is>
-      </c>
-      <c r="I43" s="26" t="inlineStr">
-        <is>
-          <t>Santiago Hernandez (QA)</t>
-        </is>
-      </c>
-      <c r="J43" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K43" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L43" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M05-06</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="29" t="inlineStr">
-        <is>
-          <t>HU-M05-07</t>
+      <c r="A44" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-18</t>
         </is>
       </c>
       <c r="B44" s="26" t="inlineStr">
         <is>
-          <t>M-05.7</t>
+          <t>CONS-18</t>
         </is>
       </c>
       <c r="C44" s="26" t="inlineStr">
         <is>
-          <t>M-05</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D44" s="26" t="inlineStr">
         <is>
-          <t>Aceptar solicitud sin doble asignacion</t>
+          <t>Orden del listado de aliados en el Rules Service</t>
         </is>
       </c>
       <c r="E44" s="26" t="inlineStr">
         <is>
-          <t>RF-14 / RNF-05 / RNF-07</t>
-        </is>
-      </c>
-      <c r="F44" s="26" t="inlineStr">
-        <is>
-          <t>Correccion + validacion</t>
-        </is>
-      </c>
-      <c r="G44" s="26" t="inlineStr">
-        <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="H44" s="26" t="inlineStr">
-        <is>
-          <t>Santiago Hernandez (QA)</t>
-        </is>
-      </c>
-      <c r="I44" s="26" t="inlineStr">
-        <is>
-          <t>Santiago Hernandez (QA)</t>
-        </is>
-      </c>
-      <c r="J44" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K44" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L44" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M05-07</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="29" t="inlineStr">
-        <is>
-          <t>HU-M05-08</t>
+      <c r="A45" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-19</t>
         </is>
       </c>
       <c r="B45" s="26" t="inlineStr">
         <is>
-          <t>M-05.8</t>
+          <t>CONS-19</t>
         </is>
       </c>
       <c r="C45" s="26" t="inlineStr">
         <is>
-          <t>M-05</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D45" s="26" t="inlineStr">
         <is>
-          <t>Rechazar oferta</t>
+          <t>Priorizar solicitud por comision ofrecida</t>
         </is>
       </c>
       <c r="E45" s="26" t="inlineStr">
         <is>
-          <t>RF-14</t>
-        </is>
-      </c>
-      <c r="F45" s="26" t="inlineStr">
-        <is>
-          <t>Correccion + validacion</t>
-        </is>
-      </c>
-      <c r="G45" s="26" t="inlineStr">
-        <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="H45" s="26" t="inlineStr">
-        <is>
-          <t>Santiago Hernandez (QA)</t>
-        </is>
-      </c>
-      <c r="I45" s="26" t="inlineStr">
-        <is>
-          <t>Santiago Hernandez (QA)</t>
-        </is>
-      </c>
-      <c r="J45" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K45" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L45" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M05-08</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="29" t="inlineStr">
-        <is>
-          <t>HU-M05-09</t>
+      <c r="A46" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-20</t>
         </is>
       </c>
       <c r="B46" s="26" t="inlineStr">
         <is>
-          <t>M-05.9</t>
+          <t>CONS-20</t>
         </is>
       </c>
       <c r="C46" s="26" t="inlineStr">
         <is>
-          <t>M-05</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D46" s="26" t="inlineStr">
         <is>
-          <t>Idempotencia de la creacion y del despacho</t>
+          <t>Cancelar solicitud antes de la ejecucion</t>
         </is>
       </c>
       <c r="E46" s="26" t="inlineStr">
         <is>
-          <t>RNF-03</t>
-        </is>
-      </c>
-      <c r="F46" s="26" t="inlineStr">
-        <is>
-          <t>Correccion + validacion</t>
-        </is>
-      </c>
-      <c r="G46" s="26" t="inlineStr">
-        <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="H46" s="26" t="inlineStr">
-        <is>
-          <t>Santiago Hernandez (QA)</t>
-        </is>
-      </c>
-      <c r="I46" s="26" t="inlineStr">
-        <is>
-          <t>Santiago Hernandez (QA)</t>
-        </is>
-      </c>
-      <c r="J46" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K46" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L46" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M05-09</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="31" t="inlineStr">
         <is>
-          <t>HU-M05-10</t>
+          <t>QA-CONS-21</t>
         </is>
       </c>
       <c r="B47" s="26" t="inlineStr">
         <is>
-          <t>M-05.10</t>
+          <t>CONS-21</t>
         </is>
       </c>
       <c r="C47" s="26" t="inlineStr">
         <is>
-          <t>M-05</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D47" s="26" t="inlineStr">
         <is>
-          <t>Cancelar solicitud antes de la ejecucion</t>
+          <t>Cotizacion con mano de obra y materiales separados</t>
         </is>
       </c>
       <c r="E47" s="26" t="inlineStr">
         <is>
-          <t>RF-32 / RF-14</t>
-        </is>
-      </c>
-      <c r="F47" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G47" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H47" s="33" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="I47" s="26" t="inlineStr">
-        <is>
-          <t>Santiago Hernandez (QA)</t>
-        </is>
-      </c>
-      <c r="J47" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K47" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L47" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M05-10</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="31" t="inlineStr">
         <is>
-          <t>HU-M06-01</t>
+          <t>QA-CONS-22</t>
         </is>
       </c>
       <c r="B48" s="26" t="inlineStr">
         <is>
-          <t>M-06.1</t>
+          <t>CONS-22</t>
         </is>
       </c>
       <c r="C48" s="26" t="inlineStr">
         <is>
-          <t>M-06</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D48" s="26" t="inlineStr">
         <is>
-          <t>Elaborar cotizacion separando mano de obra y materiales</t>
+          <t>Alerta de cotizacion fuera del rango del tarifario</t>
         </is>
       </c>
       <c r="E48" s="26" t="inlineStr">
         <is>
-          <t>RF-15</t>
-        </is>
-      </c>
-      <c r="F48" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G48" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H48" s="26" t="inlineStr">
-        <is>
-          <t>Jose Nicolas Alvarez</t>
-        </is>
-      </c>
-      <c r="I48" s="26" t="inlineStr">
-        <is>
-          <t>Jose Nicolas Alvarez</t>
-        </is>
-      </c>
-      <c r="J48" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K48" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L48" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M06-01</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="31" t="inlineStr">
         <is>
-          <t>HU-M06-02</t>
+          <t>QA-CONS-23</t>
         </is>
       </c>
       <c r="B49" s="26" t="inlineStr">
         <is>
-          <t>M-06.2</t>
+          <t>CONS-23</t>
         </is>
       </c>
       <c r="C49" s="26" t="inlineStr">
         <is>
-          <t>M-06</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D49" s="26" t="inlineStr">
         <is>
-          <t>Alerta de cotizacion fuera del rango del tarifario</t>
+          <t>Cliente acepta, rechaza o solicita ajuste de la cotizacion</t>
         </is>
       </c>
       <c r="E49" s="26" t="inlineStr">
         <is>
-          <t>RF-16</t>
-        </is>
-      </c>
-      <c r="F49" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G49" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H49" s="26" t="inlineStr">
-        <is>
-          <t>Jose Nicolas Alvarez</t>
-        </is>
-      </c>
-      <c r="I49" s="26" t="inlineStr">
-        <is>
-          <t>Jose Nicolas Alvarez</t>
-        </is>
-      </c>
-      <c r="J49" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K49" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L49" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M06-02</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="31" t="inlineStr">
         <is>
-          <t>HU-M06-03</t>
+          <t>QA-CONS-24</t>
         </is>
       </c>
       <c r="B50" s="26" t="inlineStr">
         <is>
-          <t>M-06.3</t>
+          <t>CONS-24</t>
         </is>
       </c>
       <c r="C50" s="26" t="inlineStr">
         <is>
-          <t>M-06</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D50" s="26" t="inlineStr">
         <is>
-          <t>Cliente acepta, rechaza o solicita ajuste de la cotizacion</t>
+          <t>Marcar inicio y fin de la ejecucion</t>
         </is>
       </c>
       <c r="E50" s="26" t="inlineStr">
         <is>
-          <t>RF-17</t>
-        </is>
-      </c>
-      <c r="F50" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G50" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H50" s="26" t="inlineStr">
-        <is>
-          <t>Jose Nicolas Alvarez</t>
-        </is>
-      </c>
-      <c r="I50" s="26" t="inlineStr">
-        <is>
-          <t>Jose Nicolas Alvarez</t>
-        </is>
-      </c>
-      <c r="J50" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K50" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L50" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M06-03</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="31" t="inlineStr">
         <is>
-          <t>HU-M07-01</t>
+          <t>QA-CONS-25</t>
         </is>
       </c>
       <c r="B51" s="26" t="inlineStr">
         <is>
-          <t>M-07.1</t>
+          <t>CONS-25</t>
         </is>
       </c>
       <c r="C51" s="26" t="inlineStr">
         <is>
-          <t>M-07</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D51" s="26" t="inlineStr">
         <is>
-          <t>Marcar inicio y fin de la ejecucion</t>
+          <t>Registrar eventos y observaciones durante la ejecucion</t>
         </is>
       </c>
       <c r="E51" s="26" t="inlineStr">
         <is>
-          <t>RF-18</t>
-        </is>
-      </c>
-      <c r="F51" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G51" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H51" s="26" t="inlineStr">
-        <is>
-          <t>Jose Nicolas Alvarez</t>
-        </is>
-      </c>
-      <c r="I51" s="26" t="inlineStr">
-        <is>
-          <t>Jose Nicolas Alvarez</t>
-        </is>
-      </c>
-      <c r="J51" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K51" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L51" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M07-01</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="31" t="inlineStr">
         <is>
-          <t>HU-M07-02</t>
+          <t>QA-CONS-26</t>
         </is>
       </c>
       <c r="B52" s="26" t="inlineStr">
         <is>
-          <t>M-07.2</t>
+          <t>CONS-26</t>
         </is>
       </c>
       <c r="C52" s="26" t="inlineStr">
         <is>
-          <t>M-07</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D52" s="26" t="inlineStr">
         <is>
-          <t>Registrar cronologicamente eventos y observaciones</t>
+          <t>Registrar evidencias sin conexion y sincronizarlas</t>
         </is>
       </c>
       <c r="E52" s="26" t="inlineStr">
         <is>
-          <t>RF-18 / RNF-04</t>
-        </is>
-      </c>
-      <c r="F52" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G52" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H52" s="26" t="inlineStr">
-        <is>
-          <t>Jose Nicolas Alvarez</t>
-        </is>
-      </c>
-      <c r="I52" s="26" t="inlineStr">
-        <is>
-          <t>Jose Nicolas Alvarez</t>
-        </is>
-      </c>
-      <c r="J52" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K52" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L52" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M07-02</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="31" t="inlineStr">
         <is>
-          <t>HU-M07-03</t>
+          <t>QA-CONS-27</t>
         </is>
       </c>
       <c r="B53" s="26" t="inlineStr">
         <is>
-          <t>M-07.3</t>
+          <t>CONS-27</t>
         </is>
       </c>
       <c r="C53" s="26" t="inlineStr">
         <is>
-          <t>M-07</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D53" s="26" t="inlineStr">
         <is>
-          <t>Cliente consulta el log del servicio</t>
+          <t>Cargar la tabla de tarifas por categoria</t>
         </is>
       </c>
       <c r="E53" s="26" t="inlineStr">
         <is>
-          <t>RF-18</t>
-        </is>
-      </c>
-      <c r="F53" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G53" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H53" s="26" t="inlineStr">
-        <is>
-          <t>Jose Nicolas Alvarez</t>
-        </is>
-      </c>
-      <c r="I53" s="26" t="inlineStr">
-        <is>
-          <t>Jose Nicolas Alvarez</t>
-        </is>
-      </c>
-      <c r="J53" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K53" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L53" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M07-03</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="31" t="inlineStr">
         <is>
-          <t>HU-M07-04</t>
+          <t>QA-CONS-28</t>
         </is>
       </c>
       <c r="B54" s="26" t="inlineStr">
         <is>
-          <t>M-07.4</t>
+          <t>CONS-28</t>
         </is>
       </c>
       <c r="C54" s="26" t="inlineStr">
         <is>
-          <t>M-07</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D54" s="26" t="inlineStr">
         <is>
-          <t>Cliente rastrea la ubicacion del aliado en vivo</t>
+          <t>Ver la tarifa de referencia al cotizar</t>
         </is>
       </c>
       <c r="E54" s="26" t="inlineStr">
         <is>
-          <t>RF-37</t>
-        </is>
-      </c>
-      <c r="F54" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G54" s="26" t="inlineStr">
-        <is>
-          <t>To Do (fuera de MVP)</t>
-        </is>
-      </c>
-      <c r="H54" s="26" t="inlineStr">
-        <is>
-          <t>Jose Nicolas Alvarez</t>
-        </is>
-      </c>
-      <c r="I54" s="26" t="inlineStr">
-        <is>
-          <t>Jose Nicolas Alvarez</t>
-        </is>
-      </c>
-      <c r="J54" s="26" t="n">
-        <v>8</v>
-      </c>
-      <c r="K54" s="26" t="inlineStr">
-        <is>
-          <t>Si — RF-37, creado el 24-oct-2026 al traerlo al sprint. Pendiente de confirmacion del PO: si lo revierte, la historia sale. La ubicacion es dato personal (Ley 1581 de 2012): permiso expreso del aliado, ventana limitada a la ejecucion y retencion configurable por tenant.</t>
-        </is>
-      </c>
-      <c r="L54" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M07-04</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="31" t="inlineStr">
         <is>
-          <t>HU-M07-05</t>
+          <t>QA-CONS-29</t>
         </is>
       </c>
       <c r="B55" s="26" t="inlineStr">
         <is>
-          <t>M-07.5</t>
+          <t>CONS-29</t>
         </is>
       </c>
       <c r="C55" s="26" t="inlineStr">
         <is>
-          <t>M-07</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D55" s="26" t="inlineStr">
         <is>
-          <t>Aliado solicita adicion por imprevisto</t>
+          <t>Reporte de cotizaciones fuera de rango por periodo</t>
         </is>
       </c>
       <c r="E55" s="26" t="inlineStr">
         <is>
-          <t>RF-34 / RF-15 / RF-17</t>
-        </is>
-      </c>
-      <c r="F55" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G55" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H55" s="26" t="inlineStr">
-        <is>
-          <t>Jose Nicolas Alvarez</t>
-        </is>
-      </c>
-      <c r="I55" s="26" t="inlineStr">
-        <is>
-          <t>Jose Nicolas Alvarez</t>
-        </is>
-      </c>
-      <c r="J55" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K55" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L55" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M07-05</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="31" t="inlineStr">
         <is>
-          <t>HU-M07-06</t>
+          <t>QA-CONS-30</t>
         </is>
       </c>
       <c r="B56" s="26" t="inlineStr">
         <is>
-          <t>M-07.6</t>
+          <t>CONS-30</t>
         </is>
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>M-07</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D56" s="26" t="inlineStr">
         <is>
-          <t>Registrar evidencias sin conexion</t>
+          <t>Calificacion bidireccional y cierre condicionado</t>
         </is>
       </c>
       <c r="E56" s="26" t="inlineStr">
         <is>
-          <t>RF-35 / RNF-03</t>
-        </is>
-      </c>
-      <c r="F56" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G56" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H56" s="26" t="inlineStr">
-        <is>
-          <t>Jose Nicolas Alvarez</t>
-        </is>
-      </c>
-      <c r="I56" s="26" t="inlineStr">
-        <is>
-          <t>Jose Nicolas Alvarez</t>
-        </is>
-      </c>
-      <c r="J56" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K56" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L56" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M07-06</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="31" t="inlineStr">
         <is>
-          <t>HU-M08-01</t>
+          <t>QA-CONS-31</t>
         </is>
       </c>
       <c r="B57" s="26" t="inlineStr">
         <is>
-          <t>M-08.1</t>
+          <t>CONS-31</t>
         </is>
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>M-08</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D57" s="26" t="inlineStr">
         <is>
-          <t>Cliente califica al aliado</t>
+          <t>Calificacion agregada visible en el listado de aliados</t>
         </is>
       </c>
       <c r="E57" s="26" t="inlineStr">
         <is>
-          <t>RF-19</t>
-        </is>
-      </c>
-      <c r="F57" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G57" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H57" s="26" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="I57" s="26" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="J57" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K57" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L57" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M08-01</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="31" t="inlineStr">
         <is>
-          <t>HU-M08-02</t>
+          <t>QA-CONS-32</t>
         </is>
       </c>
       <c r="B58" s="26" t="inlineStr">
         <is>
-          <t>M-08.2</t>
+          <t>CONS-32</t>
         </is>
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>M-08</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D58" s="26" t="inlineStr">
         <is>
-          <t>Aliado califica al cliente</t>
+          <t>Penalizacion por cancelacion tardia</t>
         </is>
       </c>
       <c r="E58" s="26" t="inlineStr">
         <is>
-          <t>RF-19</t>
-        </is>
-      </c>
-      <c r="F58" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G58" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H58" s="26" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="I58" s="26" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="J58" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K58" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L58" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M08-02</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="31" t="inlineStr">
         <is>
-          <t>HU-M08-03</t>
+          <t>QA-CONS-33</t>
         </is>
       </c>
       <c r="B59" s="26" t="inlineStr">
         <is>
-          <t>M-08.3</t>
+          <t>CONS-33</t>
         </is>
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>M-08</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D59" s="26" t="inlineStr">
         <is>
-          <t>Cierre condicionado a la calificacion bidireccional</t>
+          <t>Historial de servicios del cliente y de trabajos del aliado</t>
         </is>
       </c>
       <c r="E59" s="26" t="inlineStr">
         <is>
-          <t>RF-19</t>
-        </is>
-      </c>
-      <c r="F59" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G59" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H59" s="26" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="I59" s="26" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="J59" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K59" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L59" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M08-03</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="31" t="inlineStr">
         <is>
-          <t>HU-M08-04</t>
+          <t>QA-CONS-34</t>
         </is>
       </c>
       <c r="B60" s="26" t="inlineStr">
         <is>
-          <t>M-08.4</t>
+          <t>CONS-34</t>
         </is>
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>M-08</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D60" s="26" t="inlineStr">
         <is>
-          <t>Calificacion agregada visible en el listado</t>
+          <t>Mensajeria cliente-aliado por servicio</t>
         </is>
       </c>
       <c r="E60" s="26" t="inlineStr">
         <is>
-          <t>RF-13 / RF-19</t>
-        </is>
-      </c>
-      <c r="F60" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G60" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H60" s="26" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="I60" s="26" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="J60" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K60" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L60" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M08-04</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="31" t="inlineStr">
         <is>
-          <t>HU-M08-05</t>
+          <t>QA-CONS-35</t>
         </is>
       </c>
       <c r="B61" s="26" t="inlineStr">
         <is>
-          <t>M-08.5</t>
+          <t>CONS-35</t>
         </is>
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>M-08</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D61" s="26" t="inlineStr">
         <is>
-          <t>Penalizacion por cancelacion tardia</t>
+          <t>Mock del proveedor de notificaciones push en el backend</t>
         </is>
       </c>
       <c r="E61" s="26" t="inlineStr">
         <is>
-          <t>RF-33 / RF-02 / RNF-10</t>
-        </is>
-      </c>
-      <c r="F61" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G61" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H61" s="26" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="I61" s="26" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="J61" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K61" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L61" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M08-05</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="31" t="inlineStr">
         <is>
-          <t>HU-M08-06</t>
+          <t>QA-CONS-36</t>
         </is>
       </c>
       <c r="B62" s="26" t="inlineStr">
         <is>
-          <t>M-08.6</t>
+          <t>CONS-36</t>
         </is>
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>M-08</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D62" s="26" t="inlineStr">
         <is>
-          <t>Cliente consulta su historial de servicios</t>
+          <t>Notificaciones de mensajes nuevos y del ciclo del servicio</t>
         </is>
       </c>
       <c r="E62" s="26" t="inlineStr">
         <is>
-          <t>RF-36 / RF-18</t>
-        </is>
-      </c>
-      <c r="F62" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G62" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H62" s="26" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="I62" s="26" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="J62" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K62" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L62" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M08-06</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="31" t="inlineStr">
         <is>
-          <t>HU-M08-07</t>
+          <t>QA-CONS-37</t>
         </is>
       </c>
       <c r="B63" s="26" t="inlineStr">
         <is>
-          <t>M-08.7</t>
+          <t>CONS-37</t>
         </is>
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>M-08</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D63" s="26" t="inlineStr">
         <is>
-          <t>Aliado consulta su historial de trabajos</t>
+          <t>Consultar la conversacion para atender una queja</t>
         </is>
       </c>
       <c r="E63" s="26" t="inlineStr">
         <is>
-          <t>RF-36 / RF-18</t>
-        </is>
-      </c>
-      <c r="F63" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G63" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H63" s="26" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="I63" s="26" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="J63" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K63" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L63" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M08-07</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="30" t="inlineStr">
-        <is>
-          <t>HU-M09-01</t>
+      <c r="A64" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-38</t>
         </is>
       </c>
       <c r="B64" s="26" t="inlineStr">
         <is>
-          <t>M-09.1</t>
+          <t>CONS-38</t>
         </is>
       </c>
       <c r="C64" s="26" t="inlineStr">
         <is>
-          <t>M-09</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D64" s="26" t="inlineStr">
         <is>
-          <t>Frontera de notificacion del backend</t>
+          <t>Mock de la pasarela de pagos</t>
         </is>
       </c>
       <c r="E64" s="26" t="inlineStr">
         <is>
-          <t>RF-20</t>
-        </is>
-      </c>
-      <c r="F64" s="26" t="inlineStr">
-        <is>
-          <t>Front contra mock</t>
-        </is>
-      </c>
-      <c r="G64" s="26" t="inlineStr">
-        <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="H64" s="26" t="inlineStr">
-        <is>
-          <t>Nicolas Leon</t>
-        </is>
-      </c>
-      <c r="I64" s="26" t="inlineStr">
-        <is>
-          <t>Nicolas Leon</t>
-        </is>
-      </c>
-      <c r="J64" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K64" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L64" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M09-01</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="30" t="inlineStr">
-        <is>
-          <t>HU-M09-02</t>
+      <c r="A65" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-39</t>
         </is>
       </c>
       <c r="B65" s="26" t="inlineStr">
         <is>
-          <t>M-09.2</t>
+          <t>CONS-39</t>
         </is>
       </c>
       <c r="C65" s="26" t="inlineStr">
         <is>
-          <t>M-09</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D65" s="26" t="inlineStr">
         <is>
-          <t>Mensajeria cliente-aliado por servicio</t>
+          <t>Registro inmutable de transacciones</t>
         </is>
       </c>
       <c r="E65" s="26" t="inlineStr">
         <is>
-          <t>RF-20</t>
-        </is>
-      </c>
-      <c r="F65" s="26" t="inlineStr">
-        <is>
-          <t>Front contra mock</t>
-        </is>
-      </c>
-      <c r="G65" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H65" s="26" t="inlineStr">
-        <is>
-          <t>Nicolas Leon</t>
-        </is>
-      </c>
-      <c r="I65" s="26" t="inlineStr">
-        <is>
-          <t>Nicolas Leon</t>
-        </is>
-      </c>
-      <c r="J65" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K65" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L65" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M09-02</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="30" t="inlineStr">
-        <is>
-          <t>HU-M09-03</t>
+      <c r="A66" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-40</t>
         </is>
       </c>
       <c r="B66" s="26" t="inlineStr">
         <is>
-          <t>M-09.3</t>
+          <t>CONS-40</t>
         </is>
       </c>
       <c r="C66" s="26" t="inlineStr">
         <is>
-          <t>M-09</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D66" s="26" t="inlineStr">
         <is>
-          <t>Notificaciones de mensajes nuevos</t>
+          <t>Liquidacion al aliado con comision configurable</t>
         </is>
       </c>
       <c r="E66" s="26" t="inlineStr">
         <is>
-          <t>RF-20</t>
-        </is>
-      </c>
-      <c r="F66" s="26" t="inlineStr">
-        <is>
-          <t>Front contra mock</t>
-        </is>
-      </c>
-      <c r="G66" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H66" s="26" t="inlineStr">
-        <is>
-          <t>Nicolas Leon</t>
-        </is>
-      </c>
-      <c r="I66" s="26" t="inlineStr">
-        <is>
-          <t>Nicolas Leon</t>
-        </is>
-      </c>
-      <c r="J66" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K66" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L66" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M09-03</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="30" t="inlineStr">
-        <is>
-          <t>HU-M09-04</t>
+      <c r="A67" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-41</t>
         </is>
       </c>
       <c r="B67" s="26" t="inlineStr">
         <is>
-          <t>M-09.4</t>
+          <t>CONS-41</t>
         </is>
       </c>
       <c r="C67" s="26" t="inlineStr">
         <is>
-          <t>M-09</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D67" s="26" t="inlineStr">
         <is>
-          <t>Consultar la conversacion para atender una queja</t>
+          <t>Registro y gestion de quejas</t>
         </is>
       </c>
       <c r="E67" s="26" t="inlineStr">
         <is>
-          <t>RF-21</t>
-        </is>
-      </c>
-      <c r="F67" s="26" t="inlineStr">
-        <is>
-          <t>Front contra mock</t>
-        </is>
-      </c>
-      <c r="G67" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H67" s="26" t="inlineStr">
-        <is>
-          <t>Nicolas Leon</t>
-        </is>
-      </c>
-      <c r="I67" s="26" t="inlineStr">
-        <is>
-          <t>Nicolas Leon</t>
-        </is>
-      </c>
-      <c r="J67" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K67" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L67" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M09-04</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="30" t="inlineStr">
-        <is>
-          <t>HU-M09-05</t>
+      <c r="A68" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-42</t>
         </is>
       </c>
       <c r="B68" s="26" t="inlineStr">
         <is>
-          <t>M-09.5</t>
+          <t>CONS-42</t>
         </is>
       </c>
       <c r="C68" s="26" t="inlineStr">
         <is>
-          <t>M-09</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D68" s="26" t="inlineStr">
         <is>
-          <t>Notificaciones push de los eventos del ciclo del servicio</t>
+          <t>Metricas operativas por tenant y endpoint /metrics</t>
         </is>
       </c>
       <c r="E68" s="26" t="inlineStr">
         <is>
-          <t>RF-20</t>
-        </is>
-      </c>
-      <c r="F68" s="26" t="inlineStr">
-        <is>
-          <t>Front contra mock</t>
-        </is>
-      </c>
-      <c r="G68" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H68" s="26" t="inlineStr">
-        <is>
-          <t>Nicolas Leon</t>
-        </is>
-      </c>
-      <c r="I68" s="26" t="inlineStr">
-        <is>
-          <t>Nicolas Leon</t>
-        </is>
-      </c>
-      <c r="J68" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K68" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L68" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M09-05</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="30" t="inlineStr">
-        <is>
-          <t>HU-M09-06</t>
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>QA-CONS-43</t>
         </is>
       </c>
       <c r="B69" s="26" t="inlineStr">
         <is>
-          <t>M-09.6</t>
+          <t>CONS-43</t>
         </is>
       </c>
       <c r="C69" s="26" t="inlineStr">
         <is>
-          <t>M-09</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D69" s="26" t="inlineStr">
         <is>
-          <t>Mock del proveedor de notificaciones push en el backend</t>
+          <t>Administrar el estado de los tenants</t>
         </is>
       </c>
       <c r="E69" s="26" t="inlineStr">
         <is>
-          <t>RF-20</t>
-        </is>
-      </c>
-      <c r="F69" s="26" t="inlineStr">
-        <is>
-          <t>Front contra mock</t>
-        </is>
-      </c>
-      <c r="G69" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H69" s="26" t="inlineStr">
-        <is>
-          <t>Nicolas Leon</t>
-        </is>
-      </c>
-      <c r="I69" s="26" t="inlineStr">
-        <is>
-          <t>Nicolas Leon</t>
-        </is>
-      </c>
-      <c r="J69" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K69" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L69" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M09-06</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>HU-M10-01</t>
+          <t>QA-CONS-44</t>
         </is>
       </c>
       <c r="B70" s="26" t="inlineStr">
         <is>
-          <t>M-10.1</t>
+          <t>CONS-44</t>
         </is>
       </c>
       <c r="C70" s="26" t="inlineStr">
         <is>
-          <t>M-10</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D70" s="26" t="inlineStr">
         <is>
-          <t>Cargar la tabla de tarifas por categoria</t>
+          <t>Configuracion de reglas por tenant sin despliegue</t>
         </is>
       </c>
       <c r="E70" s="26" t="inlineStr">
         <is>
-          <t>RF-22</t>
-        </is>
-      </c>
-      <c r="F70" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G70" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H70" s="26" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="I70" s="26" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="J70" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K70" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L70" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M10-01</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>HU-M10-02</t>
+          <t>QA-CONS-45</t>
         </is>
       </c>
       <c r="B71" s="26" t="inlineStr">
         <is>
-          <t>M-10.2</t>
+          <t>CONS-45</t>
         </is>
       </c>
       <c r="C71" s="26" t="inlineStr">
         <is>
-          <t>M-10</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D71" s="26" t="inlineStr">
         <is>
-          <t>Ver la tarifa de referencia al cotizar</t>
+          <t>Cifrado y manejo de secretos verificado de punta a punta</t>
         </is>
       </c>
       <c r="E71" s="26" t="inlineStr">
         <is>
-          <t>RF-22 / RF-16</t>
-        </is>
-      </c>
-      <c r="F71" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G71" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H71" s="26" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="I71" s="26" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="J71" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K71" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L71" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M10-02</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>HU-M10-03</t>
+          <t>QA-CONS-46</t>
         </is>
       </c>
       <c r="B72" s="26" t="inlineStr">
         <is>
-          <t>M-10.3</t>
+          <t>CONS-46</t>
         </is>
       </c>
       <c r="C72" s="26" t="inlineStr">
         <is>
-          <t>M-10</t>
+          <t>Construccion</t>
         </is>
       </c>
       <c r="D72" s="26" t="inlineStr">
         <is>
-          <t>Reporte de cotizaciones fuera de rango por periodo</t>
+          <t>Alta y administracion de tenants por el administrador de plataforma</t>
         </is>
       </c>
       <c r="E72" s="26" t="inlineStr">
         <is>
-          <t>RF-23</t>
-        </is>
-      </c>
-      <c r="F72" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G72" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H72" s="26" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="I72" s="26" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="J72" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K72" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L72" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M10-03</t>
+          <t>Comprueba los criterios de aceptacion de la historia uno por uno, los criterios transversales T1 a T10 que le apliquen, las pruebas automatizadas nuevas en verde, el Quality Gate de SonarQube del repositorio tocado y la evidencia de la ejecucion en QA por el Gateway con token real. Verifica tambien que lo construido cumple el requisito del SRS que la historia dice cubrir, no solo que el codigo exista. Si algo falta, la historia no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="30" t="inlineStr">
-        <is>
-          <t>HU-M11-01</t>
+      <c r="A73" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-01</t>
         </is>
       </c>
       <c r="B73" s="26" t="inlineStr">
         <is>
-          <t>M-11.1</t>
+          <t>TEC-01</t>
         </is>
       </c>
       <c r="C73" s="26" t="inlineStr">
         <is>
-          <t>M-11</t>
+          <t>Tarea tecnica</t>
         </is>
       </c>
       <c r="D73" s="26" t="inlineStr">
         <is>
-          <t>Mock de la pasarela de pagos (sandbox simulado)</t>
+          <t>Cerrar la contradiccion documental sobre quien crea la solicitud</t>
         </is>
       </c>
       <c r="E73" s="26" t="inlineStr">
         <is>
-          <t>RF-24 / REST-03</t>
-        </is>
-      </c>
-      <c r="F73" s="26" t="inlineStr">
-        <is>
-          <t>Front contra mock</t>
-        </is>
-      </c>
-      <c r="G73" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H73" s="26" t="inlineStr">
-        <is>
-          <t>Nicolas Leon</t>
-        </is>
-      </c>
-      <c r="I73" s="26" t="inlineStr">
-        <is>
-          <t>Nicolas Leon</t>
-        </is>
-      </c>
-      <c r="J73" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K73" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L73" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M11-01</t>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="30" t="inlineStr">
-        <is>
-          <t>HU-M11-02</t>
+      <c r="A74" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-02</t>
         </is>
       </c>
       <c r="B74" s="26" t="inlineStr">
         <is>
-          <t>M-11.2</t>
+          <t>TEC-02</t>
         </is>
       </c>
       <c r="C74" s="26" t="inlineStr">
         <is>
-          <t>M-11</t>
+          <t>Tarea tecnica</t>
         </is>
       </c>
       <c r="D74" s="26" t="inlineStr">
         <is>
-          <t>Pago en linea al aceptar la cotizacion</t>
+          <t>Fijar el contexto de identidad en cada transaccion de Dispatch</t>
         </is>
       </c>
       <c r="E74" s="26" t="inlineStr">
         <is>
-          <t>RF-24 / RNF-06 / RNF-11 / REST-03</t>
-        </is>
-      </c>
-      <c r="F74" s="26" t="inlineStr">
-        <is>
-          <t>Front contra mock</t>
-        </is>
-      </c>
-      <c r="G74" s="26" t="inlineStr">
-        <is>
-          <t>To Do (2do incremento)</t>
-        </is>
-      </c>
-      <c r="H74" s="26" t="inlineStr">
-        <is>
-          <t>Nicolas Leon</t>
-        </is>
-      </c>
-      <c r="I74" s="26" t="inlineStr">
-        <is>
-          <t>Nicolas Leon</t>
-        </is>
-      </c>
-      <c r="J74" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K74" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L74" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M11-02</t>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="30" t="inlineStr">
-        <is>
-          <t>HU-M11-03</t>
+      <c r="A75" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-03</t>
         </is>
       </c>
       <c r="B75" s="26" t="inlineStr">
         <is>
-          <t>M-11.3</t>
+          <t>TEC-03</t>
         </is>
       </c>
       <c r="C75" s="26" t="inlineStr">
         <is>
-          <t>M-11</t>
+          <t>Tarea tecnica</t>
         </is>
       </c>
       <c r="D75" s="26" t="inlineStr">
         <is>
-          <t>Registro inmutable de transacciones</t>
+          <t>Corregir la politica de solicitud_rechazo</t>
         </is>
       </c>
       <c r="E75" s="26" t="inlineStr">
         <is>
-          <t>RF-24 / RNF-04</t>
-        </is>
-      </c>
-      <c r="F75" s="26" t="inlineStr">
-        <is>
-          <t>Front contra mock</t>
-        </is>
-      </c>
-      <c r="G75" s="26" t="inlineStr">
-        <is>
-          <t>To Do (2do incremento)</t>
-        </is>
-      </c>
-      <c r="H75" s="26" t="inlineStr">
-        <is>
-          <t>Nicolas Leon</t>
-        </is>
-      </c>
-      <c r="I75" s="26" t="inlineStr">
-        <is>
-          <t>Nicolas Leon</t>
-        </is>
-      </c>
-      <c r="J75" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K75" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L75" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M11-03</t>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="30" t="inlineStr">
-        <is>
-          <t>HU-M11-04</t>
+      <c r="A76" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-04</t>
         </is>
       </c>
       <c r="B76" s="26" t="inlineStr">
         <is>
-          <t>M-11.4</t>
+          <t>TEC-04</t>
         </is>
       </c>
       <c r="C76" s="26" t="inlineStr">
         <is>
-          <t>M-11</t>
+          <t>Tarea tecnica</t>
         </is>
       </c>
       <c r="D76" s="26" t="inlineStr">
         <is>
-          <t>Descargar soporte de pago</t>
+          <t>Paginar el broadcast y hacer idempotente el reintento parcial</t>
         </is>
       </c>
       <c r="E76" s="26" t="inlineStr">
         <is>
-          <t>RF-24</t>
-        </is>
-      </c>
-      <c r="F76" s="26" t="inlineStr">
-        <is>
-          <t>Front contra mock</t>
-        </is>
-      </c>
-      <c r="G76" s="26" t="inlineStr">
-        <is>
-          <t>To Do (2do incremento)</t>
-        </is>
-      </c>
-      <c r="H76" s="26" t="inlineStr">
-        <is>
-          <t>Nicolas Leon</t>
-        </is>
-      </c>
-      <c r="I76" s="26" t="inlineStr">
-        <is>
-          <t>Nicolas Leon</t>
-        </is>
-      </c>
-      <c r="J76" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K76" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L76" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M11-04</t>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="30" t="inlineStr">
-        <is>
-          <t>HU-M11-05</t>
+      <c r="A77" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-05</t>
         </is>
       </c>
       <c r="B77" s="26" t="inlineStr">
         <is>
-          <t>M-11.5</t>
+          <t>TEC-05</t>
         </is>
       </c>
       <c r="C77" s="26" t="inlineStr">
         <is>
-          <t>M-11</t>
+          <t>Tarea tecnica</t>
         </is>
       </c>
       <c r="D77" s="26" t="inlineStr">
         <is>
-          <t>Retencion de fondos en garantia (escrow)</t>
+          <t>Distinguir conflicto de asignacion de conflicto de estado</t>
         </is>
       </c>
       <c r="E77" s="26" t="inlineStr">
         <is>
-          <t>RF-24 / RNF-11</t>
-        </is>
-      </c>
-      <c r="F77" s="26" t="inlineStr">
-        <is>
-          <t>Front contra mock</t>
-        </is>
-      </c>
-      <c r="G77" s="26" t="inlineStr">
-        <is>
-          <t>To Do (2do incremento)</t>
-        </is>
-      </c>
-      <c r="H77" s="26" t="inlineStr">
-        <is>
-          <t>Nicolas Leon</t>
-        </is>
-      </c>
-      <c r="I77" s="26" t="inlineStr">
-        <is>
-          <t>Nicolas Leon</t>
-        </is>
-      </c>
-      <c r="J77" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K77" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L77" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M11-05</t>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>HU-M11-06</t>
+      <c r="A78" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-06</t>
         </is>
       </c>
       <c r="B78" s="26" t="inlineStr">
         <is>
-          <t>M-11.6</t>
+          <t>TEC-06</t>
         </is>
       </c>
       <c r="C78" s="26" t="inlineStr">
         <is>
-          <t>M-11</t>
+          <t>Tarea tecnica</t>
         </is>
       </c>
       <c r="D78" s="26" t="inlineStr">
         <is>
-          <t>Liberacion automatica de fondos</t>
+          <t>Declarar CORE_SERVICE_URL en manifiestos versionados</t>
         </is>
       </c>
       <c r="E78" s="26" t="inlineStr">
         <is>
-          <t>RF-24</t>
-        </is>
-      </c>
-      <c r="F78" s="26" t="inlineStr">
-        <is>
-          <t>Front contra mock</t>
-        </is>
-      </c>
-      <c r="G78" s="26" t="inlineStr">
-        <is>
-          <t>To Do (2do incremento)</t>
-        </is>
-      </c>
-      <c r="H78" s="26" t="inlineStr">
-        <is>
-          <t>Nicolas Leon</t>
-        </is>
-      </c>
-      <c r="I78" s="26" t="inlineStr">
-        <is>
-          <t>Nicolas Leon</t>
-        </is>
-      </c>
-      <c r="J78" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K78" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L78" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M11-06</t>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="30" t="inlineStr">
-        <is>
-          <t>HU-M11-07</t>
+      <c r="A79" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-07</t>
         </is>
       </c>
       <c r="B79" s="26" t="inlineStr">
         <is>
-          <t>M-11.7</t>
+          <t>TEC-07</t>
         </is>
       </c>
       <c r="C79" s="26" t="inlineStr">
         <is>
-          <t>M-11</t>
+          <t>Tarea tecnica</t>
         </is>
       </c>
       <c r="D79" s="26" t="inlineStr">
         <is>
-          <t>Liquidacion al aliado descontando comision configurable</t>
+          <t>Unificar la politica de token de Dispatch con la de Core</t>
         </is>
       </c>
       <c r="E79" s="26" t="inlineStr">
         <is>
-          <t>RF-25 / RNF-10 / REST-05</t>
-        </is>
-      </c>
-      <c r="F79" s="26" t="inlineStr">
-        <is>
-          <t>Front contra mock</t>
-        </is>
-      </c>
-      <c r="G79" s="26" t="inlineStr">
-        <is>
-          <t>To Do (2do incremento)</t>
-        </is>
-      </c>
-      <c r="H79" s="26" t="inlineStr">
-        <is>
-          <t>Nicolas Leon</t>
-        </is>
-      </c>
-      <c r="I79" s="26" t="inlineStr">
-        <is>
-          <t>Nicolas Leon</t>
-        </is>
-      </c>
-      <c r="J79" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K79" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L79" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M11-07</t>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="30" t="inlineStr">
-        <is>
-          <t>HU-M11-08</t>
+      <c r="A80" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-08</t>
         </is>
       </c>
       <c r="B80" s="26" t="inlineStr">
         <is>
-          <t>M-11.8</t>
+          <t>TEC-08</t>
         </is>
       </c>
       <c r="C80" s="26" t="inlineStr">
         <is>
-          <t>M-11</t>
+          <t>Tarea tecnica</t>
         </is>
       </c>
       <c r="D80" s="26" t="inlineStr">
         <is>
-          <t>Aliado consulta el detalle de sus pagos</t>
+          <t>Documentar el salto de numeracion de migraciones y recuperar 0012</t>
         </is>
       </c>
       <c r="E80" s="26" t="inlineStr">
         <is>
-          <t>RF-25</t>
-        </is>
-      </c>
-      <c r="F80" s="26" t="inlineStr">
-        <is>
-          <t>Front contra mock</t>
-        </is>
-      </c>
-      <c r="G80" s="26" t="inlineStr">
-        <is>
-          <t>To Do (2do incremento)</t>
-        </is>
-      </c>
-      <c r="H80" s="26" t="inlineStr">
-        <is>
-          <t>Nicolas Leon</t>
-        </is>
-      </c>
-      <c r="I80" s="26" t="inlineStr">
-        <is>
-          <t>Nicolas Leon</t>
-        </is>
-      </c>
-      <c r="J80" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K80" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L80" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M11-08</t>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="31" t="inlineStr">
-        <is>
-          <t>HU-M12-01</t>
+      <c r="A81" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-09</t>
         </is>
       </c>
       <c r="B81" s="26" t="inlineStr">
         <is>
-          <t>M-12.1</t>
+          <t>TEC-09</t>
         </is>
       </c>
       <c r="C81" s="26" t="inlineStr">
         <is>
-          <t>M-12</t>
+          <t>Tarea tecnica</t>
         </is>
       </c>
       <c r="D81" s="26" t="inlineStr">
         <is>
-          <t>Cliente registra una queja</t>
+          <t>Cerrar dev-token y la ruta publica de validate-token en el Gateway, y rotar secretos</t>
         </is>
       </c>
       <c r="E81" s="26" t="inlineStr">
         <is>
-          <t>RF-26</t>
-        </is>
-      </c>
-      <c r="F81" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G81" s="26" t="inlineStr">
-        <is>
-          <t>To Do (2do incremento)</t>
-        </is>
-      </c>
-      <c r="H81" s="26" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="I81" s="26" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="J81" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K81" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L81" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M12-01</t>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="31" t="inlineStr">
-        <is>
-          <t>HU-M12-02</t>
+      <c r="A82" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-10</t>
         </is>
       </c>
       <c r="B82" s="26" t="inlineStr">
         <is>
-          <t>M-12.2</t>
+          <t>TEC-10</t>
         </is>
       </c>
       <c r="C82" s="26" t="inlineStr">
         <is>
-          <t>M-12</t>
+          <t>Tarea tecnica</t>
         </is>
       </c>
       <c r="D82" s="26" t="inlineStr">
         <is>
-          <t>Tenant gestiona el estado de las quejas</t>
+          <t>Un solo validador de token, con ES256, iss y aud</t>
         </is>
       </c>
       <c r="E82" s="26" t="inlineStr">
         <is>
-          <t>RF-26</t>
-        </is>
-      </c>
-      <c r="F82" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G82" s="26" t="inlineStr">
-        <is>
-          <t>To Do (2do incremento)</t>
-        </is>
-      </c>
-      <c r="H82" s="26" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="I82" s="26" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="J82" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K82" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L82" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M12-02</t>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="32" t="inlineStr">
-        <is>
-          <t>HU-M12-03</t>
+      <c r="A83" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-11</t>
         </is>
       </c>
       <c r="B83" s="26" t="inlineStr">
         <is>
-          <t>M-12.3</t>
+          <t>TEC-11</t>
         </is>
       </c>
       <c r="C83" s="26" t="inlineStr">
         <is>
-          <t>M-12</t>
+          <t>Tarea tecnica</t>
         </is>
       </c>
       <c r="D83" s="26" t="inlineStr">
         <is>
-          <t>Resolucion de disputa financiera</t>
+          <t>Confirmar o montar TLS en el borde</t>
         </is>
       </c>
       <c r="E83" s="26" t="inlineStr">
         <is>
-          <t>RF-26 / RF-24</t>
-        </is>
-      </c>
-      <c r="F83" s="26" t="inlineStr">
-        <is>
-          <t>Fuera de alcance</t>
-        </is>
-      </c>
-      <c r="G83" s="26" t="inlineStr">
-        <is>
-          <t>To Do (2do incremento)</t>
-        </is>
-      </c>
-      <c r="H83" s="26" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="I83" s="26" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="J83" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" s="26" t="inlineStr">
-        <is>
-          <t>Fuera: 2.o incremento</t>
-        </is>
-      </c>
-      <c r="L83" s="26" t="inlineStr"/>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" s="32" t="inlineStr">
-        <is>
-          <t>HU-M12-04</t>
+      <c r="A84" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-12</t>
         </is>
       </c>
       <c r="B84" s="26" t="inlineStr">
         <is>
-          <t>M-12.4</t>
+          <t>TEC-12</t>
         </is>
       </c>
       <c r="C84" s="26" t="inlineStr">
         <is>
-          <t>M-12</t>
+          <t>Tarea tecnica</t>
         </is>
       </c>
       <c r="D84" s="26" t="inlineStr">
         <is>
-          <t>Publicar contenido en redes conectadas</t>
+          <t>Ratificar ADR-0030 y ADR-0016 en Mesa</t>
         </is>
       </c>
       <c r="E84" s="26" t="inlineStr">
         <is>
-          <t>RF-27</t>
-        </is>
-      </c>
-      <c r="F84" s="26" t="inlineStr">
-        <is>
-          <t>Fuera de alcance</t>
-        </is>
-      </c>
-      <c r="G84" s="26" t="inlineStr">
-        <is>
-          <t>To Do (2do incremento)</t>
-        </is>
-      </c>
-      <c r="H84" s="26" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="I84" s="26" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="J84" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" s="26" t="inlineStr">
-        <is>
-          <t>Fuera: 2.o incremento</t>
-        </is>
-      </c>
-      <c r="L84" s="26" t="inlineStr"/>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" s="32" t="inlineStr">
-        <is>
-          <t>HU-M12-05</t>
+      <c r="A85" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-13</t>
         </is>
       </c>
       <c r="B85" s="26" t="inlineStr">
         <is>
-          <t>M-12.5</t>
+          <t>TEC-13</t>
         </is>
       </c>
       <c r="C85" s="26" t="inlineStr">
         <is>
-          <t>M-12</t>
+          <t>Tarea tecnica</t>
         </is>
       </c>
       <c r="D85" s="26" t="inlineStr">
         <is>
-          <t>Registrar campanas y ver su desempeno</t>
+          <t>Definir identidad de servicio entre Dispatch y Core</t>
         </is>
       </c>
       <c r="E85" s="26" t="inlineStr">
         <is>
-          <t>RF-27</t>
-        </is>
-      </c>
-      <c r="F85" s="26" t="inlineStr">
-        <is>
-          <t>Fuera de alcance</t>
-        </is>
-      </c>
-      <c r="G85" s="26" t="inlineStr">
-        <is>
-          <t>To Do (2do incremento)</t>
-        </is>
-      </c>
-      <c r="H85" s="26" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="I85" s="26" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="J85" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" s="26" t="inlineStr">
-        <is>
-          <t>Fuera: 2.o incremento</t>
-        </is>
-      </c>
-      <c r="L85" s="26" t="inlineStr"/>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" s="31" t="inlineStr">
-        <is>
-          <t>HU-M12-06</t>
+      <c r="A86" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-14</t>
         </is>
       </c>
       <c r="B86" s="26" t="inlineStr">
         <is>
-          <t>M-12.6</t>
+          <t>TEC-14</t>
         </is>
       </c>
       <c r="C86" s="26" t="inlineStr">
         <is>
-          <t>M-12</t>
+          <t>Tarea tecnica</t>
         </is>
       </c>
       <c r="D86" s="26" t="inlineStr">
         <is>
-          <t>Metricas operativas por tenant</t>
+          <t>Observabilidad minima de autenticacion</t>
         </is>
       </c>
       <c r="E86" s="26" t="inlineStr">
         <is>
-          <t>RF-28</t>
-        </is>
-      </c>
-      <c r="F86" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G86" s="26" t="inlineStr">
-        <is>
-          <t>To Do (2do incremento)</t>
-        </is>
-      </c>
-      <c r="H86" s="26" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="I86" s="26" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="J86" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K86" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L86" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M12-06</t>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="31" t="inlineStr">
-        <is>
-          <t>HU-M12-07</t>
+      <c r="A87" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-15</t>
         </is>
       </c>
       <c r="B87" s="26" t="inlineStr">
         <is>
-          <t>M-12.7</t>
+          <t>TEC-15</t>
         </is>
       </c>
       <c r="C87" s="26" t="inlineStr">
         <is>
-          <t>M-12</t>
+          <t>Tarea tecnica</t>
         </is>
       </c>
       <c r="D87" s="26" t="inlineStr">
         <is>
-          <t>Administrar el estado de los tenants</t>
+          <t>Crear el repositorio del Rules Service</t>
         </is>
       </c>
       <c r="E87" s="26" t="inlineStr">
         <is>
-          <t>RF-28 / RF-01</t>
-        </is>
-      </c>
-      <c r="F87" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G87" s="26" t="inlineStr">
-        <is>
-          <t>To Do (2do incremento)</t>
-        </is>
-      </c>
-      <c r="H87" s="26" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="I87" s="26" t="inlineStr">
-        <is>
-          <t>Juan Sebastian Alvarez</t>
-        </is>
-      </c>
-      <c r="J87" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K87" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L87" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M12-07</t>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="31" t="inlineStr">
-        <is>
-          <t>HU-M13-01</t>
+      <c r="A88" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-16</t>
         </is>
       </c>
       <c r="B88" s="26" t="inlineStr">
         <is>
-          <t>M-13.1</t>
+          <t>TEC-16</t>
         </is>
       </c>
       <c r="C88" s="26" t="inlineStr">
         <is>
-          <t>M-13</t>
+          <t>Tarea tecnica</t>
         </is>
       </c>
       <c r="D88" s="26" t="inlineStr">
         <is>
-          <t>Menu superior por rol, con sesion visible y logout accesible</t>
+          <t>Preparar el ambiente QA y los datos sembrados del sprint de validacion</t>
         </is>
       </c>
       <c r="E88" s="26" t="inlineStr">
         <is>
-          <t>RNF-08</t>
-        </is>
-      </c>
-      <c r="F88" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G88" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H88" s="26" t="inlineStr">
-        <is>
-          <t>Jose Nicolas Alvarez</t>
-        </is>
-      </c>
-      <c r="I88" s="26" t="inlineStr">
-        <is>
-          <t>Jose Nicolas Alvarez</t>
-        </is>
-      </c>
-      <c r="J88" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K88" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L88" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M13-01</t>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="29" t="inlineStr">
         <is>
-          <t>HU-M13-02</t>
+          <t>QA-TEC-17</t>
         </is>
       </c>
       <c r="B89" s="26" t="inlineStr">
         <is>
-          <t>M-13.2</t>
+          <t>TEC-17</t>
         </is>
       </c>
       <c r="C89" s="26" t="inlineStr">
         <is>
-          <t>M-13</t>
+          <t>Tarea tecnica</t>
         </is>
       </c>
       <c r="D89" s="26" t="inlineStr">
         <is>
-          <t>Enrutamiento por rol con guardas de sesion y expiracion</t>
+          <t>Guia de grabacion y repositorio de videos</t>
         </is>
       </c>
       <c r="E89" s="26" t="inlineStr">
         <is>
-          <t>RF-03</t>
-        </is>
-      </c>
-      <c r="F89" s="26" t="inlineStr">
-        <is>
-          <t>Correccion + validacion</t>
-        </is>
-      </c>
-      <c r="G89" s="26" t="inlineStr">
-        <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="H89" s="26" t="inlineStr">
-        <is>
-          <t>Jose Nicolas Alvarez</t>
-        </is>
-      </c>
-      <c r="I89" s="26" t="inlineStr">
-        <is>
-          <t>Jose Nicolas Alvarez</t>
-        </is>
-      </c>
-      <c r="J89" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K89" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L89" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M13-02</t>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="31" t="inlineStr">
-        <is>
-          <t>HU-M13-03</t>
+      <c r="A90" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-18</t>
         </is>
       </c>
       <c r="B90" s="26" t="inlineStr">
         <is>
-          <t>M-13.3</t>
+          <t>TEC-18</t>
         </is>
       </c>
       <c r="C90" s="26" t="inlineStr">
         <is>
-          <t>M-13</t>
+          <t>Tarea tecnica</t>
         </is>
       </c>
       <c r="D90" s="26" t="inlineStr">
         <is>
-          <t>Pantalla de inicio por tipo de usuario</t>
+          <t>Migrar el front de solicitudes y asignacion al camino Gateway-Core</t>
         </is>
       </c>
       <c r="E90" s="26" t="inlineStr">
         <is>
-          <t>RNF-08</t>
-        </is>
-      </c>
-      <c r="F90" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G90" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H90" s="26" t="inlineStr">
-        <is>
-          <t>Jose Nicolas Alvarez</t>
-        </is>
-      </c>
-      <c r="I90" s="26" t="inlineStr">
-        <is>
-          <t>Jose Nicolas Alvarez</t>
-        </is>
-      </c>
-      <c r="J90" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="K90" s="26" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L90" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M13-03</t>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="32" t="inlineStr">
-        <is>
-          <t>HU-M13-04</t>
+      <c r="A91" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-19</t>
         </is>
       </c>
       <c r="B91" s="26" t="inlineStr">
         <is>
-          <t>M-13.4</t>
+          <t>TEC-19</t>
         </is>
       </c>
       <c r="C91" s="26" t="inlineStr">
         <is>
-          <t>M-13</t>
+          <t>Tarea tecnica</t>
         </is>
       </c>
       <c r="D91" s="26" t="inlineStr">
         <is>
-          <t>Dividir el front en modulos independientes por dominio</t>
+          <t>Migracion de usuario para direccion y foto de perfil</t>
         </is>
       </c>
       <c r="E91" s="26" t="inlineStr">
         <is>
-          <t>PROY-05 / RNF-02</t>
-        </is>
-      </c>
-      <c r="F91" s="26" t="inlineStr">
-        <is>
-          <t>Fuera de alcance</t>
-        </is>
-      </c>
-      <c r="G91" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H91" s="26" t="inlineStr">
-        <is>
-          <t>Jose Nicolas Alvarez</t>
-        </is>
-      </c>
-      <c r="I91" s="26" t="inlineStr">
-        <is>
-          <t>Jose Nicolas Alvarez</t>
-        </is>
-      </c>
-      <c r="J91" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" s="26" t="inlineStr">
-        <is>
-          <t>Fuera: dividir el front se queda fuera por decision del 24-oct-2026. El choque es menor que en Core porque cada modulo tiende a su propia pantalla. Se asume conflicto en lib/features.</t>
-        </is>
-      </c>
-      <c r="L91" s="26" t="inlineStr"/>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" s="31" t="inlineStr">
-        <is>
-          <t>HU-M13-05</t>
+      <c r="A92" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-20</t>
         </is>
       </c>
       <c r="B92" s="26" t="inlineStr">
         <is>
-          <t>M-13.5</t>
+          <t>TEC-20</t>
         </is>
       </c>
       <c r="C92" s="26" t="inlineStr">
         <is>
-          <t>M-13</t>
+          <t>Tarea tecnica</t>
         </is>
       </c>
       <c r="D92" s="26" t="inlineStr">
         <is>
-          <t>Dividir el Core por dominios internos sin crear un servicio por CRUD</t>
+          <t>Persistir verificado_por en el adaptador real</t>
         </is>
       </c>
       <c r="E92" s="26" t="inlineStr">
         <is>
-          <t>RNF-02 / ADR-0022</t>
-        </is>
-      </c>
-      <c r="F92" s="26" t="inlineStr">
-        <is>
-          <t>Construccion desde 0</t>
-        </is>
-      </c>
-      <c r="G92" s="26" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H92" s="26" t="inlineStr">
-        <is>
-          <t>Jose Nicolas Alvarez</t>
-        </is>
-      </c>
-      <c r="I92" s="26" t="inlineStr">
-        <is>
-          <t>Jose Nicolas Alvarez</t>
-        </is>
-      </c>
-      <c r="J92" s="26" t="n">
-        <v>8</v>
-      </c>
-      <c r="K92" s="26" t="inlineStr">
-        <is>
-          <t>Si — PRERREQUISITO. Entra los primeros dias del sprint, junto a las TEC de ambiente, porque los 13 modulos convergen en Core y sin dividirlo siete personas editan el mismo servicio. Nadie construye sobre Core hasta que esta division este fusionada.</t>
-        </is>
-      </c>
-      <c r="L92" s="26" t="inlineStr">
-        <is>
-          <t>QA-HU-M13-05</t>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="29" t="inlineStr">
+        <is>
+          <t>QA-TEC-21</t>
+        </is>
+      </c>
+      <c r="B93" s="26" t="inlineStr">
+        <is>
+          <t>TEC-21</t>
+        </is>
+      </c>
+      <c r="C93" s="26" t="inlineStr">
+        <is>
+          <t>Tarea tecnica</t>
+        </is>
+      </c>
+      <c r="D93" s="26" t="inlineStr">
+        <is>
+          <t>Retirar BYPASSRLS: Core y Dispatch conectan con un rol de servicio sin privilegio de salto</t>
+        </is>
+      </c>
+      <c r="E93" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el hallazgo que la tarea dice cerrar ya no se reproduce en QA, con la corrida adjunta como evidencia, y que la correccion no rompio la regresion existente. Para las tareas de seguridad, comprueba ademas el caso negativo: que el vector cerrado efectivamente falla. Si el hallazgo sigue reproduciendose, la tarea no pasa a Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="30" t="inlineStr">
+        <is>
+          <t>QA-SM-01</t>
+        </is>
+      </c>
+      <c r="B94" s="26" t="inlineStr">
+        <is>
+          <t>SM-01</t>
+        </is>
+      </c>
+      <c r="C94" s="26" t="inlineStr">
+        <is>
+          <t>Gestion</t>
+        </is>
+      </c>
+      <c r="D94" s="26" t="inlineStr">
+        <is>
+          <t>Sara Albarracin (Scrum Master)</t>
+        </is>
+      </c>
+      <c r="E94" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el registro existe y es verificable: para SM-01, que las ceremonias, los impedimentos y los indicadores estan publicados y que ningun item se declaro terminado sin su subtarea de QA cerrada; para PO-01, que el acta de aceptacion lista explicitamente lo aceptado, lo rechazado y lo que queda fuera del incremento con su causa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="30" t="inlineStr">
+        <is>
+          <t>QA-PO-01</t>
+        </is>
+      </c>
+      <c r="B95" s="26" t="inlineStr">
+        <is>
+          <t>PO-01</t>
+        </is>
+      </c>
+      <c r="C95" s="26" t="inlineStr">
+        <is>
+          <t>Gestion</t>
+        </is>
+      </c>
+      <c r="D95" s="26" t="inlineStr">
+        <is>
+          <t>Camila Beltran (Product Owner)</t>
+        </is>
+      </c>
+      <c r="E95" s="26" t="inlineStr">
+        <is>
+          <t>Comprueba que el registro existe y es verificable: para SM-01, que las ceremonias, los impedimentos y los indicadores estan publicados y que ningun item se declaro terminado sin su subtarea de QA cerrada; para PO-01, que el acta de aceptacion lista explicitamente lo aceptado, lo rechazado y lo que queda fuera del incremento con su causa.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
